--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_tone.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_tone.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1110">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -106,6 +106,9 @@
     <t xml:space="preserve">네</t>
   </si>
   <si>
+    <t xml:space="preserve">구나</t>
+  </si>
+  <si>
     <t xml:space="preserve">만이야</t>
   </si>
   <si>
@@ -148,6 +151,12 @@
     <t xml:space="preserve">좋아</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑해</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리자</t>
+  </si>
+  <si>
     <t xml:space="preserve">하다</t>
   </si>
   <si>
@@ -163,6 +172,9 @@
     <t xml:space="preserve">했겠다</t>
   </si>
   <si>
+    <t xml:space="preserve">하자</t>
+  </si>
+  <si>
     <t xml:space="preserve">돼</t>
   </si>
   <si>
@@ -271,6 +283,18 @@
     <t xml:space="preserve">무서워</t>
   </si>
   <si>
+    <t xml:space="preserve">기뻐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하해</t>
+  </si>
+  <si>
+    <t xml:space="preserve">살아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울려</t>
+  </si>
+  <si>
     <t xml:space="preserve">default</t>
   </si>
   <si>
@@ -304,6 +328,9 @@
     <t xml:space="preserve">싶다,싶어</t>
   </si>
   <si>
+    <t xml:space="preserve">구나,구만</t>
+  </si>
+  <si>
     <t xml:space="preserve">는가,어</t>
   </si>
   <si>
@@ -362,6 +389,9 @@
   </si>
   <si>
     <t xml:space="preserve">낳아라,낳아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기뻐,정말 기뻐</t>
   </si>
   <si>
     <t xml:space="preserve">polite</t>
@@ -453,6 +483,9 @@
 군요</t>
   </si>
   <si>
+    <t xml:space="preserve">군요</t>
+  </si>
+  <si>
     <t xml:space="preserve">만입니다
 만이에요</t>
   </si>
@@ -504,6 +537,14 @@
     <t xml:space="preserve">좋습니다,좋아요</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑합니다,사랑해요
+사랑해요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올립시다,올려요
+올려요</t>
+  </si>
+  <si>
     <t xml:space="preserve">합니다
 해요</t>
   </si>
@@ -518,6 +559,10 @@
   <si>
     <t xml:space="preserve">하시는군요
 하시네요,하시는군요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합시다,해요
+해요</t>
   </si>
   <si>
     <t xml:space="preserve">됩니다
@@ -757,6 +802,22 @@
 무서워요,두려워요</t>
   </si>
   <si>
+    <t xml:space="preserve">기쁩니다,기뻐요,정말 기쁩니다,정말 기뻐요
+기뻐요,정말 기뻐요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하합니다,축하드립니다
+축하해요,축하드려요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사세요,사십시오
+사세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울립니다,어울려요
+어울려요</t>
+  </si>
+  <si>
     <t xml:space="preserve">rude</t>
   </si>
   <si>
@@ -827,6 +888,10 @@
   <si>
     <t xml:space="preserve">네,군
 네</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구나,구만
+구나</t>
   </si>
   <si>
     <t xml:space="preserve">만이야,만이다
@@ -1109,6 +1174,20 @@
     <t xml:space="preserve">무서워,겁나</t>
   </si>
   <si>
+    <t xml:space="preserve">기뻐,진짜 기뻐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">살아,살아라
+살아</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울려,어울린다
+어울려</t>
+  </si>
+  <si>
     <t xml:space="preserve">friendly</t>
   </si>
   <si>
@@ -1332,11 +1411,21 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">~,</t>
+      <t xml:space="preserve">,</t>
     </r>
     <r>
       <rPr>
@@ -1360,6 +1449,29 @@
   </si>
   <si>
     <t xml:space="preserve">낳아</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">축하해
+축하해,축하해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">shy</t>
@@ -1474,6 +1586,28 @@
   <si>
     <t xml:space="preserve">네…
 네…</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">구나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">만이야…
@@ -1636,6 +1770,50 @@
     <t xml:space="preserve">좋아…</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">사랑해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">올리자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">해…</t>
   </si>
   <si>
@@ -1670,6 +1848,28 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">했겠다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">하자</t>
     </r>
     <r>
       <rPr>
@@ -2088,6 +2288,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">낳아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">무서워</t>
     </r>
     <r>
@@ -2102,6 +2324,94 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">기뻐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…,정말 기뻐…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">축하해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">살아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">어울려</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">VIP</t>
   </si>
   <si>
@@ -2171,9 +2481,6 @@
     <t xml:space="preserve">싶구나</t>
   </si>
   <si>
-    <t xml:space="preserve">구나</t>
-  </si>
-  <si>
     <t xml:space="preserve">만이다</t>
   </si>
   <si>
@@ -2202,6 +2509,12 @@
   </si>
   <si>
     <t xml:space="preserve">좋다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사랑한다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리자꾸나</t>
   </si>
   <si>
     <t xml:space="preserve">하느니라,하도다</t>
@@ -2453,6 +2766,18 @@
     <t xml:space="preserve">두렵도다</t>
   </si>
   <si>
+    <t xml:space="preserve">기쁘구나,매우 기쁘구나,참으로 기쁘구나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하하마,치하하마,경하하마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">살거라,살도록 해라</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울리는구나,어울리도다</t>
+  </si>
+  <si>
     <t xml:space="preserve">bushi</t>
   </si>
   <si>
@@ -2613,6 +2938,14 @@
 좋사옵니다</t>
   </si>
   <si>
+    <t xml:space="preserve">사모하오,사랑하오
+사모하옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올립시다
+올립시다</t>
+  </si>
+  <si>
     <t xml:space="preserve">하오
 하옵니다</t>
   </si>
@@ -2627,6 +2960,10 @@
   <si>
     <t xml:space="preserve">하시는구려,하시는구료
 하시는군요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하는 게 어떻소
+하시는 게 어떻사옵니까</t>
   </si>
   <si>
     <t xml:space="preserve">되오
@@ -2814,6 +3151,22 @@
 두렵사옵니다</t>
   </si>
   <si>
+    <t xml:space="preserve">기쁘오,기쁘구려,실로 기쁘오,실로 기쁘구려
+기쁘옵니다,황송하옵니다,정말 기쁘옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하하오,축하드리오
+축하드리옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사시오,사시구려
+사세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울리오
+어울리옵니다</t>
+  </si>
+  <si>
     <t xml:space="preserve">su</t>
   </si>
   <si>
@@ -2859,6 +3212,9 @@
     <t xml:space="preserve">네요</t>
   </si>
   <si>
+    <t xml:space="preserve">구만요</t>
+  </si>
+  <si>
     <t xml:space="preserve">만임다</t>
   </si>
   <si>
@@ -2898,6 +3254,12 @@
     <t xml:space="preserve">좋슴다</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑함다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리죠</t>
+  </si>
+  <si>
     <t xml:space="preserve">함다</t>
   </si>
   <si>
@@ -2910,6 +3272,9 @@
     <t xml:space="preserve">하셨지 말임다</t>
   </si>
   <si>
+    <t xml:space="preserve">합쇼</t>
+  </si>
+  <si>
     <t xml:space="preserve">됨다</t>
   </si>
   <si>
@@ -2979,7 +3344,36 @@
     <t xml:space="preserve">외롭슴다,쓸쓸함다</t>
   </si>
   <si>
-    <t xml:space="preserve">아리베데르치,그럼,수고하셨~슴다,잘 가십쇼</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">아리베데르치,그럼,수고하셨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">슴다,잘 가십쇼</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">고맙슴다,감삼다</t>
@@ -3000,6 +3394,18 @@
     <t xml:space="preserve">쫄림다,겁남다</t>
   </si>
   <si>
+    <t xml:space="preserve">기쁨다,진짜 기쁨다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하함다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사십쇼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울림다</t>
+  </si>
+  <si>
     <t xml:space="preserve">cat</t>
   </si>
   <si>
@@ -3078,6 +3484,9 @@
     <t xml:space="preserve">녜,구냐</t>
   </si>
   <si>
+    <t xml:space="preserve">구냐-</t>
+  </si>
+  <si>
     <t xml:space="preserve">먄이다냐,먄이야냐</t>
   </si>
   <si>
@@ -3115,6 +3524,12 @@
   </si>
   <si>
     <t xml:space="preserve">좋다냐앙,좋다먀-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사랑해냐-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리자냐아</t>
   </si>
   <si>
     <t xml:space="preserve">하다냐,하다냐아,하다먀</t>
@@ -3228,6 +3643,9 @@
   </si>
   <si>
     <t xml:space="preserve">했겠다냐-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하자냐-</t>
   </si>
   <si>
     <r>
@@ -4276,6 +4694,18 @@
     <t xml:space="preserve">무서워냐</t>
   </si>
   <si>
+    <t xml:space="preserve">기쁘다냐-,너무 기쁘다냐-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하해냐아-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">살아라냐-,살아냐-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울려냐,어울린다냐-</t>
+  </si>
+  <si>
     <t xml:space="preserve">nano</t>
   </si>
   <si>
@@ -4348,6 +4778,12 @@
     <t xml:space="preserve">좋은 것이에요</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑해요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리는 것이에요</t>
+  </si>
+  <si>
     <t xml:space="preserve">한 것이에요</t>
   </si>
   <si>
@@ -4360,6 +4796,9 @@
     <t xml:space="preserve">하시네요</t>
   </si>
   <si>
+    <t xml:space="preserve">해요</t>
+  </si>
+  <si>
     <t xml:space="preserve">되는 것이에요</t>
   </si>
   <si>
@@ -4442,6 +4881,18 @@
   </si>
   <si>
     <t xml:space="preserve">무서운 것이에요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기뻐요,너무 기뻐요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하드리는 것이에요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사세요,사시는 것이에요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울리는 것이에요</t>
   </si>
   <si>
     <t xml:space="preserve">noble</t>
@@ -4562,6 +5013,14 @@
 좋사와요</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑합니다
+사랑해요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올립시다
+올리는 것이와요</t>
+  </si>
+  <si>
     <t xml:space="preserve">합니다
 한 것이와요</t>
   </si>
@@ -4576,6 +5035,10 @@
   <si>
     <t xml:space="preserve">하시는군요
 하시네요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">합시다
+하시와요</t>
   </si>
   <si>
     <t xml:space="preserve">됩니다
@@ -4754,6 +5217,22 @@
 무서워요,두렵사와요</t>
   </si>
   <si>
+    <t xml:space="preserve">기쁩니다,정말 기쁩니다
+기뻐요,정말 기뻐요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축하드립니다
+축하드리와요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사십시오
+사시와요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울립니다
+어울리어요</t>
+  </si>
+  <si>
     <t xml:space="preserve">peko</t>
   </si>
   <si>
@@ -4826,6 +5305,9 @@
     <t xml:space="preserve">구나페코,페코네</t>
   </si>
   <si>
+    <t xml:space="preserve">구나페코</t>
+  </si>
+  <si>
     <t xml:space="preserve">페코만이야,만페코야</t>
   </si>
   <si>
@@ -4865,6 +5347,12 @@
     <t xml:space="preserve">좋다페코</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑해페코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리자페코</t>
+  </si>
+  <si>
     <t xml:space="preserve">하다페코,해페코</t>
   </si>
   <si>
@@ -4878,6 +5366,9 @@
   </si>
   <si>
     <t xml:space="preserve">했겠다페코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">하자페코</t>
   </si>
   <si>
     <t xml:space="preserve">된다페코</t>
@@ -4995,6 +5486,37 @@
     <t xml:space="preserve">무섭다페코</t>
   </si>
   <si>
+    <t xml:space="preserve">기뻐페코,진짜 기뻐페코</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">축하페코</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">살아페코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울려페코</t>
+  </si>
+  <si>
     <t xml:space="preserve">VIP2</t>
   </si>
   <si>
@@ -5143,7 +5665,7 @@
     <t xml:space="preserve">좋아요</t>
   </si>
   <si>
-    <t xml:space="preserve">해요</t>
+    <t xml:space="preserve">올려요</t>
   </si>
   <si>
     <t xml:space="preserve">하셰요</t>
@@ -5246,6 +5768,18 @@
     <t xml:space="preserve">무서워요,겁나요</t>
   </si>
   <si>
+    <t xml:space="preserve">기뼈요,너무 기뼈요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">축햐드려요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사셰요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울려요</t>
+  </si>
+  <si>
     <t xml:space="preserve">princess</t>
   </si>
   <si>
@@ -5340,6 +5874,28 @@
     <t xml:space="preserve">낳아,낳아라-,낳아라아-</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">축하해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">nyu</t>
   </si>
   <si>
@@ -5409,6 +5965,9 @@
     <t xml:space="preserve">뉴,뉴-</t>
   </si>
   <si>
+    <t xml:space="preserve">구뉴</t>
+  </si>
+  <si>
     <t xml:space="preserve">만이야뉴</t>
   </si>
   <si>
@@ -5448,6 +6007,12 @@
     <t xml:space="preserve">뉴우-,뉴-</t>
   </si>
   <si>
+    <t xml:space="preserve">사랑해뉴우</t>
+  </si>
+  <si>
+    <t xml:space="preserve">올리자뉴</t>
+  </si>
+  <si>
     <t xml:space="preserve">뉴</t>
   </si>
   <si>
@@ -5463,6 +6028,9 @@
     <t xml:space="preserve">했겠다뉴-</t>
   </si>
   <si>
+    <t xml:space="preserve">하쟈뉴-</t>
+  </si>
+  <si>
     <t xml:space="preserve">된다뉴우</t>
   </si>
   <si>
@@ -5557,6 +6125,37 @@
   </si>
   <si>
     <t xml:space="preserve">무서워뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기뻐뉴,정말 기뻐뉴-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">축하해뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">살아라뉴-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어울려뉴-</t>
   </si>
 </sst>
 </file>
@@ -5645,6 +6244,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="MS PGothic"/>
       <family val="0"/>
       <charset val="129"/>
@@ -5690,13 +6296,6 @@
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -5761,7 +6360,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5806,23 +6405,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5834,11 +6437,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5850,7 +6453,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5878,37 +6481,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -6047,7 +6650,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CE1000"/>
+  <dimension ref="A1:CM1000"/>
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.57"/>
@@ -6057,13 +6660,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="6" style="1" width="30.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="16" style="1" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="67" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="73" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="75" min="75" style="1" width="35.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="76" style="1" width="39.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="77" min="77" style="1" width="44.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="78" min="78" style="1" width="38.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="16" style="1" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="71" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="78" min="77" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="79" style="1" width="35.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="80" min="80" style="1" width="39.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="81" min="81" style="1" width="44.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="1" width="38.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6301,20 +6904,44 @@
       <c r="BZ1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" s="5" t="s">
         <v>81</v>
       </c>
       <c r="CE1" s="1" t="s">
         <v>82</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6396,6 +7023,10 @@
       <c r="BX2" s="6"/>
       <c r="BY2" s="6"/>
       <c r="BZ2" s="6"/>
+      <c r="CA2" s="6"/>
+      <c r="CB2" s="6"/>
+      <c r="CC2" s="6"/>
+      <c r="CD2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
@@ -6476,6 +7107,10 @@
       <c r="BX3" s="6"/>
       <c r="BY3" s="6"/>
       <c r="BZ3" s="6"/>
+      <c r="CA3" s="6"/>
+      <c r="CB3" s="6"/>
+      <c r="CC3" s="6"/>
+      <c r="CD3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -6556,23 +7191,27 @@
       <c r="BX4" s="6"/>
       <c r="BY4" s="6"/>
       <c r="BZ4" s="6"/>
+      <c r="CA4" s="6"/>
+      <c r="CB4" s="6"/>
+      <c r="CC4" s="6"/>
+      <c r="CD4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>6</v>
@@ -6587,7 +7226,7 @@
         <v>9</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>11</v>
@@ -6602,7 +7241,7 @@
         <v>14</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>16</v>
@@ -6626,28 +7265,28 @@
         <v>22</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="AB5" s="5" t="s">
         <v>27</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="AE5" s="5" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="AF5" s="5" t="s">
         <v>31</v>
@@ -6671,10 +7310,10 @@
         <v>37</v>
       </c>
       <c r="AM5" s="5" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AN5" s="5" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="AO5" s="5" t="s">
         <v>40</v>
@@ -6683,25 +7322,25 @@
         <v>41</v>
       </c>
       <c r="AQ5" s="5" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="AR5" s="5" t="s">
         <v>43</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AU5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="AV5" s="5" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="AW5" s="5" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="AX5" s="5" t="s">
         <v>49</v>
@@ -6722,7 +7361,7 @@
         <v>54</v>
       </c>
       <c r="BD5" s="5" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="BE5" s="5" t="s">
         <v>56</v>
@@ -6734,10 +7373,10 @@
         <v>58</v>
       </c>
       <c r="BH5" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="BI5" s="5" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="BJ5" s="5" t="s">
         <v>61</v>
@@ -6746,10 +7385,10 @@
         <v>62</v>
       </c>
       <c r="BL5" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="BM5" s="5" t="s">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="BN5" s="5" t="s">
         <v>65</v>
@@ -6758,7 +7397,7 @@
         <v>66</v>
       </c>
       <c r="BP5" s="5" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="BQ5" s="5" t="s">
         <v>68</v>
@@ -6770,346 +7409,394 @@
         <v>70</v>
       </c>
       <c r="BT5" s="5" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="BU5" s="5" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="BV5" s="5" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="BW5" s="5" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="BX5" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="BY5" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BZ5" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="CA5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="CB5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="CC5" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="CD5" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="CA5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="CB5" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="CC5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="CD5" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="CE5" s="1" t="s">
-        <v>82</v>
+        <v>119</v>
+      </c>
+      <c r="CF5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="CG5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="CH5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="CI5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ5" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="CK5" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL5" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM5" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="AE6" s="4" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="AF6" s="4" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="AH6" s="4" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AJ6" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="AK6" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="AL6" s="4" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM6" s="4" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="AN6" s="4" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="AO6" s="4" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="AP6" s="4" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="AQ6" s="4" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="AR6" s="4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="AS6" s="4" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AT6" s="4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AU6" s="4" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="AV6" s="4" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="AW6" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AX6" s="4" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AY6" s="4" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AZ6" s="4" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="BA6" s="4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="BB6" s="4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="BC6" s="4" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="BD6" s="4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="BE6" s="4" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="BF6" s="4" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="BG6" s="4" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BH6" s="4" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="BI6" s="4" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="BJ6" s="4" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="BK6" s="4" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="BL6" s="4" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="BM6" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="BN6" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="BO6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP6" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="BQ6" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="BR6" s="5" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="BO6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="BP6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="BQ6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="BR6" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="BS6" s="5" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="BT6" s="5" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="BU6" s="5" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="BV6" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="BW6" s="4" t="s">
-        <v>185</v>
+        <v>194</v>
+      </c>
+      <c r="BW6" s="5" t="s">
+        <v>195</v>
       </c>
       <c r="BX6" s="5" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="BY6" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="BZ6" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="CA6" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="CB6" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="CC6" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="CD6" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="CE6" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="BZ6" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="CA6" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="CB6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="CC6" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="CD6" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="CE6" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="CF6" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="CG6" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="CH6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="CI6" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="CJ6" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="CK6" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="CL6" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="CM6" s="11" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="9" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="T7" s="4" t="s">
         <v>19</v>
@@ -7124,202 +7811,226 @@
         <v>22</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>31</v>
+        <v>235</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>217</v>
+        <v>33</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>34</v>
+        <v>236</v>
       </c>
       <c r="AJ7" s="4" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="AK7" s="4" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="AM7" s="4" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="AN7" s="4" t="s">
-        <v>39</v>
+        <v>240</v>
       </c>
       <c r="AO7" s="4" t="s">
-        <v>222</v>
+        <v>40</v>
       </c>
       <c r="AP7" s="4" t="s">
-        <v>41</v>
+        <v>241</v>
       </c>
       <c r="AQ7" s="4" t="s">
-        <v>223</v>
+        <v>42</v>
       </c>
       <c r="AR7" s="4" t="s">
         <v>43</v>
       </c>
       <c r="AS7" s="4" t="s">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AU7" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="AU7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AV7" s="4" t="s">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="AW7" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="AX7" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AX7" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="AY7" s="4" t="s">
-        <v>226</v>
+      <c r="AY7" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="AZ7" s="4" t="s">
-        <v>227</v>
+        <v>51</v>
       </c>
       <c r="BA7" s="4" t="s">
-        <v>52</v>
+        <v>244</v>
       </c>
       <c r="BB7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="BC7" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="BD7" s="4" t="s">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="BE7" s="4" t="s">
-        <v>229</v>
+        <v>56</v>
       </c>
       <c r="BF7" s="4" t="s">
-        <v>230</v>
+        <v>57</v>
       </c>
       <c r="BG7" s="4" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="BH7" s="4" t="s">
-        <v>231</v>
+        <v>108</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="BJ7" s="4" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="BK7" s="4" t="s">
-        <v>234</v>
+        <v>62</v>
       </c>
       <c r="BL7" s="4" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="BN7" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="BO7" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="BP7" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="BQ7" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="BR7" s="5" t="s">
-        <v>69</v>
+        <v>252</v>
+      </c>
+      <c r="BO7" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="BP7" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="BQ7" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="BR7" s="4" t="s">
+        <v>256</v>
       </c>
       <c r="BS7" s="5" t="s">
-        <v>70</v>
+        <v>257</v>
       </c>
       <c r="BT7" s="5" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="BU7" s="5" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="BV7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="BW7" s="4" t="s">
-        <v>244</v>
+        <v>73</v>
+      </c>
+      <c r="BW7" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="BX7" s="5" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="BY7" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="BZ7" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="CA7" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="CB7" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="CC7" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="CD7" s="1" t="s">
-        <v>113</v>
+        <v>261</v>
+      </c>
+      <c r="BZ7" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="CA7" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="CB7" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="CC7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="CD7" s="4" t="s">
+        <v>266</v>
       </c>
       <c r="CE7" s="1" t="s">
-        <v>251</v>
+        <v>267</v>
+      </c>
+      <c r="CF7" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="CG7" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="CH7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="CI7" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="CJ7" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="CK7" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="CL7" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="CM7" s="11" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="9" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
@@ -7334,28 +8045,28 @@
         <v>9</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>18</v>
@@ -7373,55 +8084,55 @@
         <v>22</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="AC8" s="4" t="s">
-        <v>266</v>
+        <v>28</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>31</v>
+        <v>291</v>
       </c>
       <c r="AG8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>269</v>
+        <v>33</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="AJ8" s="4" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AM8" s="4" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="AN8" s="4" t="s">
-        <v>39</v>
+        <v>295</v>
       </c>
       <c r="AO8" s="4" t="s">
         <v>40</v>
@@ -7430,30 +8141,30 @@
         <v>41</v>
       </c>
       <c r="AQ8" s="4" t="s">
-        <v>273</v>
+        <v>42</v>
       </c>
       <c r="AR8" s="4" t="s">
-        <v>273</v>
+        <v>43</v>
       </c>
       <c r="AS8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AT8" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="AU8" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="AU8" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="AV8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="AV8" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="AW8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX8" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="AX8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="AY8" s="4" t="s">
+      <c r="AY8" s="12" t="s">
         <v>50</v>
       </c>
       <c r="AZ8" s="4" t="s">
@@ -7469,7 +8180,7 @@
         <v>54</v>
       </c>
       <c r="BD8" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BE8" s="4" t="s">
         <v>56</v>
@@ -7481,10 +8192,10 @@
         <v>58</v>
       </c>
       <c r="BH8" s="4" t="s">
-        <v>275</v>
+        <v>58</v>
       </c>
       <c r="BI8" s="4" t="s">
-        <v>276</v>
+        <v>60</v>
       </c>
       <c r="BJ8" s="4" t="s">
         <v>61</v>
@@ -7493,82 +8204,106 @@
         <v>62</v>
       </c>
       <c r="BL8" s="4" t="s">
-        <v>102</v>
+        <v>298</v>
       </c>
       <c r="BM8" s="4" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="BN8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="BO8" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="BP8" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="BQ8" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="BR8" s="5" t="s">
-        <v>281</v>
+      <c r="BO8" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ8" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="BR8" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="BS8" s="5" t="s">
-        <v>70</v>
+        <v>301</v>
       </c>
       <c r="BT8" s="5" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="BU8" s="5" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="BV8" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="BW8" s="4" t="s">
-        <v>285</v>
+        <v>304</v>
+      </c>
+      <c r="BW8" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="BX8" s="5" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="BY8" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="BZ8" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="CA8" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="CB8" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="CC8" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="CD8" s="1" t="s">
-        <v>292</v>
+        <v>306</v>
+      </c>
+      <c r="BZ8" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="CA8" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="CB8" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="CC8" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="CD8" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="CE8" s="1" t="s">
-        <v>82</v>
+        <v>312</v>
+      </c>
+      <c r="CF8" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="CG8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="CH8" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="CI8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ8" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="CK8" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="CL8" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM8" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>6</v>
@@ -7579,11 +8314,11 @@
       <c r="I9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="13" t="s">
         <v>9</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>11</v>
@@ -7595,274 +8330,298 @@
         <v>13</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="X9" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="Y9" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z9" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="AA9" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="AB9" s="14" t="s">
-        <v>309</v>
-      </c>
-      <c r="AC9" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="AD9" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="AE9" s="14" t="s">
-        <v>312</v>
-      </c>
-      <c r="AF9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG9" s="13" t="s">
-        <v>313</v>
+        <v>328</v>
+      </c>
+      <c r="X9" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y9" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="Z9" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="AA9" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="AB9" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="AC9" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="AD9" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="AE9" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="AF9" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="AG9" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="AH9" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="AI9" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="AJ9" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="AK9" s="13" t="s">
-        <v>317</v>
+        <v>338</v>
+      </c>
+      <c r="AI9" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="AK9" s="14" t="s">
+        <v>341</v>
       </c>
       <c r="AL9" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="AM9" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="AN9" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="AO9" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="AP9" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="AQ9" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="AR9" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="AS9" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="AT9" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="AU9" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="AV9" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="AW9" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="AX9" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="AY9" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="AZ9" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="BA9" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="BB9" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="BC9" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="BD9" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="BE9" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="BF9" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="BG9" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="BH9" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="BI9" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="BJ9" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="BK9" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="BL9" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="BM9" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="BN9" s="13" t="s">
+      <c r="AM9" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="BO9" s="5" t="s">
+      <c r="AN9" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="BP9" s="5" t="s">
+      <c r="AO9" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="BQ9" s="5" t="s">
+      <c r="AP9" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="BR9" s="5" t="s">
+      <c r="AQ9" s="14" t="s">
         <v>347</v>
       </c>
+      <c r="AR9" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="AS9" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="AT9" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="AU9" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="AV9" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="AW9" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="AX9" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="AY9" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="AZ9" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="BA9" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="BB9" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="BC9" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="BD9" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="BE9" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="BF9" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="BG9" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="BH9" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="BI9" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="BJ9" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="BK9" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="BL9" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="BM9" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="BN9" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="BO9" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="BP9" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="BQ9" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="BR9" s="14" t="s">
+        <v>371</v>
+      </c>
       <c r="BS9" s="5" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="BT9" s="5" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="BU9" s="5" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="BV9" s="5" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="BW9" s="5" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="BX9" s="5" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="BY9" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="BZ9" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="CA9" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="CB9" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="CC9" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="CD9" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="CE9" s="1" t="s">
-        <v>359</v>
+        <v>378</v>
+      </c>
+      <c r="BZ9" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="CA9" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="CB9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="CC9" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="CD9" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="CE9" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="CF9" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="CG9" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="CH9" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="CI9" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="CJ9" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="CK9" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="CL9" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="CM9" s="0" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="9" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>367</v>
+        <v>400</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>370</v>
+        <v>403</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>372</v>
+        <v>405</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>376</v>
+        <v>409</v>
       </c>
       <c r="V10" s="5" t="s">
         <v>21</v>
@@ -7871,451 +8630,499 @@
         <v>22</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>377</v>
+        <v>410</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>379</v>
+        <v>412</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>381</v>
+        <v>28</v>
       </c>
       <c r="AC10" s="5" t="s">
-        <v>382</v>
+        <v>28</v>
       </c>
       <c r="AD10" s="5" t="s">
-        <v>29</v>
+        <v>414</v>
       </c>
       <c r="AE10" s="5" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>31</v>
+        <v>415</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>384</v>
+        <v>32</v>
       </c>
       <c r="AH10" s="5" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="AI10" s="5" t="s">
-        <v>386</v>
+        <v>417</v>
       </c>
       <c r="AJ10" s="5" t="s">
-        <v>35</v>
+        <v>418</v>
       </c>
       <c r="AK10" s="5" t="s">
-        <v>387</v>
+        <v>36</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="AM10" s="5" t="s">
-        <v>389</v>
+        <v>420</v>
       </c>
       <c r="AN10" s="5" t="s">
-        <v>39</v>
+        <v>421</v>
       </c>
       <c r="AO10" s="5" t="s">
-        <v>390</v>
+        <v>40</v>
       </c>
       <c r="AP10" s="5" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="AQ10" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="AR10" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="AS10" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="AT10" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="AU10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV10" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="AW10" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="AX10" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="AY10" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="AZ10" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="BA10" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="BB10" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC10" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="BD10" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="BE10" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="BF10" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="BG10" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="BH10" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="BI10" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="BJ10" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="BK10" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="BL10" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="BM10" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="BN10" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="BO10" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="BP10" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="BQ10" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="BR10" s="5" t="s">
-        <v>415</v>
+        <v>423</v>
+      </c>
+      <c r="AR10" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="AS10" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="AT10" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="AU10" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="AV10" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="AW10" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="AX10" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ10" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="BA10" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="BB10" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="BC10" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="BD10" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="BE10" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="BF10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG10" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="BH10" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="BI10" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="BJ10" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="BK10" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="BL10" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="BM10" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="BN10" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="BO10" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="BP10" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="BQ10" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="BR10" s="16" t="s">
+        <v>445</v>
       </c>
       <c r="BS10" s="5" t="s">
-        <v>416</v>
+        <v>446</v>
       </c>
       <c r="BT10" s="5" t="s">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="BU10" s="5" t="s">
-        <v>418</v>
+        <v>448</v>
       </c>
       <c r="BV10" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="BW10" s="4" t="s">
-        <v>420</v>
+        <v>449</v>
+      </c>
+      <c r="BW10" s="5" t="s">
+        <v>450</v>
       </c>
       <c r="BX10" s="5" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="BY10" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="BZ10" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="CA10" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="CB10" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="CC10" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="CD10" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="CE10" s="1" t="s">
-        <v>428</v>
+        <v>452</v>
+      </c>
+      <c r="BZ10" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="CA10" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="CB10" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="CC10" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="CD10" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="CE10" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="CF10" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="CG10" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="CH10" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="CI10" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="CJ10" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="CK10" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="CL10" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="CM10" s="0" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>429</v>
+        <v>467</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="9" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>432</v>
+        <v>470</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>433</v>
+        <v>471</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>434</v>
+        <v>472</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>435</v>
+        <v>473</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>436</v>
+        <v>474</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>437</v>
+        <v>475</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>439</v>
+        <v>477</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>441</v>
+        <v>479</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>442</v>
+        <v>480</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>443</v>
+        <v>481</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>444</v>
+        <v>482</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>446</v>
+        <v>484</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>447</v>
+        <v>485</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>449</v>
+        <v>487</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>453</v>
+        <v>491</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>455</v>
+        <v>493</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="AG11" s="4" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="AH11" s="4" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="AK11" s="4" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="AL11" s="4" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AM11" s="4" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="AN11" s="4" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="AO11" s="4" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="AP11" s="4" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="AQ11" s="4" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="AR11" s="4" t="s">
-        <v>470</v>
+        <v>508</v>
       </c>
       <c r="AS11" s="4" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="AT11" s="4" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="AU11" s="4" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="AV11" s="4" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="AW11" s="4" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="AX11" s="4" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="AY11" s="4" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="AZ11" s="4" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="BA11" s="4" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="BB11" s="4" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="BC11" s="4" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="BD11" s="4" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="BE11" s="4" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="BF11" s="4" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="BG11" s="4" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="BH11" s="4" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="BI11" s="4" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="BJ11" s="4" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="BK11" s="4" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="BL11" s="4" t="s">
-        <v>455</v>
+        <v>527</v>
       </c>
       <c r="BM11" s="4" t="s">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="BN11" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="BO11" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="BP11" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="BO11" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="BP11" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="BQ11" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="BR11" s="5" t="s">
-        <v>495</v>
+      <c r="BQ11" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="BR11" s="4" t="s">
+        <v>532</v>
       </c>
       <c r="BS11" s="5" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="BT11" s="5" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="BU11" s="5" t="s">
-        <v>72</v>
+        <v>535</v>
       </c>
       <c r="BV11" s="5" t="s">
-        <v>498</v>
+        <v>536</v>
       </c>
       <c r="BW11" s="5" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="BX11" s="5" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="BY11" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="BZ11" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="CA11" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="CB11" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="CC11" s="10" t="s">
-        <v>505</v>
-      </c>
-      <c r="CD11" s="10" t="s">
-        <v>506</v>
+        <v>76</v>
+      </c>
+      <c r="BZ11" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="CA11" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="CB11" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="CC11" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="CD11" s="4" t="s">
+        <v>543</v>
       </c>
       <c r="CE11" s="10" t="s">
-        <v>507</v>
+        <v>544</v>
+      </c>
+      <c r="CF11" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="CG11" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="CH11" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="CI11" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="CJ11" s="11" t="s">
+        <v>549</v>
+      </c>
+      <c r="CK11" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="CL11" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="CM11" s="11" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>508</v>
+        <v>553</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>509</v>
+        <v>554</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="9" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>6</v>
@@ -8330,1008 +9137,1104 @@
         <v>9</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>511</v>
+        <v>556</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>513</v>
+        <v>558</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>514</v>
+        <v>559</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>515</v>
+        <v>560</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>516</v>
+        <v>561</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>517</v>
+        <v>562</v>
       </c>
       <c r="V12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="W12" s="5" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>518</v>
+        <v>563</v>
       </c>
       <c r="Y12" s="5" t="s">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>521</v>
+        <v>566</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="AC12" s="5" t="s">
-        <v>523</v>
+        <v>568</v>
       </c>
       <c r="AD12" s="5" t="s">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="AE12" s="5" t="s">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>31</v>
+        <v>571</v>
       </c>
       <c r="AG12" s="5" t="s">
-        <v>526</v>
+        <v>32</v>
       </c>
       <c r="AH12" s="5" t="s">
-        <v>527</v>
+        <v>572</v>
       </c>
       <c r="AI12" s="5" t="s">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="AJ12" s="5" t="s">
-        <v>529</v>
+        <v>574</v>
       </c>
       <c r="AK12" s="5" t="s">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>531</v>
+        <v>576</v>
       </c>
       <c r="AM12" s="5" t="s">
-        <v>532</v>
+        <v>577</v>
       </c>
       <c r="AN12" s="5" t="s">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="AP12" s="5" t="s">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="AQ12" s="5" t="s">
-        <v>536</v>
+        <v>581</v>
       </c>
       <c r="AR12" s="5" t="s">
-        <v>536</v>
+        <v>582</v>
       </c>
       <c r="AS12" s="5" t="s">
-        <v>537</v>
+        <v>583</v>
       </c>
       <c r="AT12" s="5" t="s">
-        <v>538</v>
+        <v>584</v>
       </c>
       <c r="AU12" s="5" t="s">
-        <v>539</v>
+        <v>584</v>
       </c>
       <c r="AV12" s="5" t="s">
-        <v>540</v>
+        <v>585</v>
       </c>
       <c r="AW12" s="5" t="s">
-        <v>541</v>
+        <v>586</v>
       </c>
       <c r="AX12" s="5" t="s">
-        <v>542</v>
+        <v>587</v>
       </c>
       <c r="AY12" s="5" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
       <c r="AZ12" s="5" t="s">
-        <v>543</v>
+        <v>589</v>
       </c>
       <c r="BA12" s="5" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="BB12" s="5" t="s">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="BC12" s="5" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="BD12" s="5" t="s">
-        <v>547</v>
+        <v>592</v>
       </c>
       <c r="BE12" s="5" t="s">
-        <v>548</v>
+        <v>593</v>
       </c>
       <c r="BF12" s="5" t="s">
-        <v>549</v>
+        <v>594</v>
       </c>
       <c r="BG12" s="5" t="s">
-        <v>550</v>
+        <v>595</v>
       </c>
       <c r="BH12" s="5" t="s">
-        <v>551</v>
+        <v>596</v>
       </c>
       <c r="BI12" s="5" t="s">
-        <v>552</v>
+        <v>597</v>
       </c>
       <c r="BJ12" s="5" t="s">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="BK12" s="5" t="s">
-        <v>554</v>
+        <v>599</v>
       </c>
       <c r="BL12" s="5" t="s">
-        <v>63</v>
+        <v>600</v>
       </c>
       <c r="BM12" s="5" t="s">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="BN12" s="5" t="s">
-        <v>556</v>
+        <v>602</v>
       </c>
       <c r="BO12" s="5" t="s">
-        <v>557</v>
+        <v>603</v>
       </c>
       <c r="BP12" s="5" t="s">
-        <v>558</v>
+        <v>67</v>
       </c>
       <c r="BQ12" s="5" t="s">
-        <v>559</v>
+        <v>604</v>
       </c>
       <c r="BR12" s="5" t="s">
-        <v>560</v>
+        <v>605</v>
       </c>
       <c r="BS12" s="5" t="s">
-        <v>561</v>
+        <v>606</v>
       </c>
       <c r="BT12" s="5" t="s">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="BU12" s="5" t="s">
-        <v>242</v>
+        <v>608</v>
       </c>
       <c r="BV12" s="5" t="s">
-        <v>243</v>
+        <v>609</v>
       </c>
       <c r="BW12" s="5" t="s">
-        <v>563</v>
+        <v>610</v>
       </c>
       <c r="BX12" s="5" t="s">
-        <v>245</v>
+        <v>611</v>
       </c>
       <c r="BY12" s="5" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="BZ12" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="CA12" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="CB12" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="CC12" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="CD12" s="1" t="s">
-        <v>568</v>
+        <v>262</v>
+      </c>
+      <c r="CA12" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="CB12" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="CC12" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="CD12" s="5" t="s">
+        <v>613</v>
       </c>
       <c r="CE12" s="1" t="s">
-        <v>569</v>
+        <v>614</v>
+      </c>
+      <c r="CF12" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="CG12" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="CH12" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="CI12" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="CJ12" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="CK12" s="0" t="s">
+        <v>620</v>
+      </c>
+      <c r="CL12" s="0" t="s">
+        <v>621</v>
+      </c>
+      <c r="CM12" s="0" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>570</v>
+        <v>623</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="9" t="s">
-        <v>510</v>
+        <v>555</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>572</v>
+        <v>625</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>574</v>
+        <v>627</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>576</v>
+        <v>629</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>577</v>
+        <v>630</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>578</v>
+        <v>631</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>579</v>
+        <v>632</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>580</v>
+        <v>633</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>582</v>
+        <v>635</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>583</v>
+        <v>636</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>584</v>
+        <v>637</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>585</v>
+        <v>638</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>586</v>
+        <v>639</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>587</v>
+        <v>640</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>588</v>
+        <v>641</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>589</v>
+        <v>642</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>590</v>
+        <v>643</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>591</v>
+        <v>644</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>592</v>
+        <v>645</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>593</v>
+        <v>646</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>594</v>
+        <v>647</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>595</v>
+        <v>648</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>596</v>
+        <v>649</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>597</v>
+        <v>650</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>598</v>
+        <v>651</v>
       </c>
       <c r="AF13" s="4" t="s">
-        <v>31</v>
+        <v>652</v>
       </c>
       <c r="AG13" s="4" t="s">
-        <v>599</v>
+        <v>32</v>
       </c>
       <c r="AH13" s="4" t="s">
-        <v>600</v>
+        <v>653</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>601</v>
+        <v>654</v>
       </c>
       <c r="AJ13" s="4" t="s">
-        <v>602</v>
+        <v>655</v>
       </c>
       <c r="AK13" s="4" t="s">
-        <v>603</v>
+        <v>656</v>
       </c>
       <c r="AL13" s="4" t="s">
-        <v>604</v>
+        <v>657</v>
       </c>
       <c r="AM13" s="4" t="s">
-        <v>605</v>
+        <v>658</v>
       </c>
       <c r="AN13" s="4" t="s">
-        <v>606</v>
+        <v>659</v>
       </c>
       <c r="AO13" s="4" t="s">
-        <v>607</v>
+        <v>660</v>
       </c>
       <c r="AP13" s="4" t="s">
-        <v>608</v>
+        <v>661</v>
       </c>
       <c r="AQ13" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="AR13" s="13" t="s">
-        <v>610</v>
-      </c>
-      <c r="AS13" s="13" t="s">
-        <v>611</v>
-      </c>
-      <c r="AT13" s="13" t="s">
-        <v>612</v>
-      </c>
-      <c r="AU13" s="13" t="s">
-        <v>613</v>
-      </c>
-      <c r="AV13" s="13" t="s">
-        <v>614</v>
-      </c>
-      <c r="AW13" s="13" t="s">
-        <v>615</v>
-      </c>
-      <c r="AX13" s="13" t="s">
-        <v>616</v>
-      </c>
-      <c r="AY13" s="13" t="s">
-        <v>617</v>
-      </c>
-      <c r="AZ13" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="BA13" s="13" t="s">
-        <v>619</v>
-      </c>
-      <c r="BB13" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC13" s="13" t="s">
-        <v>620</v>
-      </c>
-      <c r="BD13" s="13" t="s">
-        <v>621</v>
-      </c>
-      <c r="BE13" s="13" t="s">
-        <v>622</v>
-      </c>
-      <c r="BF13" s="13" t="s">
-        <v>623</v>
-      </c>
-      <c r="BG13" s="13" t="s">
-        <v>624</v>
-      </c>
-      <c r="BH13" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="BI13" s="13" t="s">
-        <v>626</v>
-      </c>
-      <c r="BJ13" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="BK13" s="13" t="s">
-        <v>628</v>
-      </c>
-      <c r="BL13" s="13" t="s">
-        <v>629</v>
-      </c>
-      <c r="BM13" s="13" t="s">
-        <v>630</v>
-      </c>
-      <c r="BN13" s="13" t="s">
-        <v>631</v>
-      </c>
-      <c r="BO13" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="BP13" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="BQ13" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="BR13" s="5" t="s">
-        <v>635</v>
+        <v>662</v>
+      </c>
+      <c r="AR13" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="AS13" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="AT13" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="AU13" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="AV13" s="14" t="s">
+        <v>667</v>
+      </c>
+      <c r="AW13" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="AX13" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="AY13" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="AZ13" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="BA13" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="BB13" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="BC13" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="BD13" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="BE13" s="14" t="s">
+        <v>676</v>
+      </c>
+      <c r="BF13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG13" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="BH13" s="14" t="s">
+        <v>678</v>
+      </c>
+      <c r="BI13" s="14" t="s">
+        <v>679</v>
+      </c>
+      <c r="BJ13" s="14" t="s">
+        <v>680</v>
+      </c>
+      <c r="BK13" s="14" t="s">
+        <v>681</v>
+      </c>
+      <c r="BL13" s="14" t="s">
+        <v>682</v>
+      </c>
+      <c r="BM13" s="14" t="s">
+        <v>683</v>
+      </c>
+      <c r="BN13" s="14" t="s">
+        <v>684</v>
+      </c>
+      <c r="BO13" s="14" t="s">
+        <v>685</v>
+      </c>
+      <c r="BP13" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="BQ13" s="14" t="s">
+        <v>687</v>
+      </c>
+      <c r="BR13" s="14" t="s">
+        <v>688</v>
       </c>
       <c r="BS13" s="5" t="s">
-        <v>636</v>
+        <v>689</v>
       </c>
       <c r="BT13" s="5" t="s">
-        <v>637</v>
+        <v>690</v>
       </c>
       <c r="BU13" s="5" t="s">
-        <v>638</v>
+        <v>691</v>
       </c>
       <c r="BV13" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="BW13" s="4" t="s">
-        <v>640</v>
+        <v>692</v>
+      </c>
+      <c r="BW13" s="5" t="s">
+        <v>693</v>
       </c>
       <c r="BX13" s="5" t="s">
-        <v>641</v>
+        <v>694</v>
       </c>
       <c r="BY13" s="5" t="s">
-        <v>642</v>
+        <v>695</v>
       </c>
       <c r="BZ13" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="CA13" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="CB13" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="CC13" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="CD13" s="1" t="s">
-        <v>647</v>
+        <v>696</v>
+      </c>
+      <c r="CA13" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="CB13" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="CC13" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="CD13" s="5" t="s">
+        <v>700</v>
       </c>
       <c r="CE13" s="1" t="s">
-        <v>648</v>
+        <v>701</v>
+      </c>
+      <c r="CF13" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="CG13" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="CH13" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="CI13" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="CJ13" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="CK13" s="0" t="s">
+        <v>707</v>
+      </c>
+      <c r="CL13" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="CM13" s="0" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>650</v>
+        <v>710</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>711</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="18" t="s">
-        <v>651</v>
+      <c r="D14" s="19" t="s">
+        <v>712</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>652</v>
+        <v>713</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>653</v>
+        <v>714</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>653</v>
+        <v>714</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>654</v>
+        <v>715</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>655</v>
+        <v>716</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>656</v>
+        <v>717</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>516</v>
+        <v>561</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>657</v>
+        <v>718</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>658</v>
+        <v>719</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>659</v>
+        <v>720</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>660</v>
+        <v>721</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>661</v>
+        <v>151</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>662</v>
+        <v>722</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>663</v>
+        <v>723</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>31</v>
+        <v>724</v>
       </c>
       <c r="AG14" s="4" t="s">
-        <v>664</v>
+        <v>32</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>665</v>
+        <v>725</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>666</v>
+        <v>726</v>
       </c>
       <c r="AJ14" s="4" t="s">
-        <v>667</v>
+        <v>727</v>
       </c>
       <c r="AK14" s="4" t="s">
-        <v>668</v>
+        <v>728</v>
       </c>
       <c r="AL14" s="4" t="s">
-        <v>669</v>
+        <v>729</v>
       </c>
       <c r="AM14" s="4" t="s">
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="AN14" s="4" t="s">
-        <v>533</v>
+        <v>731</v>
       </c>
       <c r="AO14" s="4" t="s">
-        <v>671</v>
+        <v>579</v>
       </c>
       <c r="AP14" s="4" t="s">
-        <v>672</v>
+        <v>732</v>
       </c>
       <c r="AQ14" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="AR14" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="AS14" s="4" t="s">
-        <v>674</v>
+        <v>733</v>
+      </c>
+      <c r="AR14" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="AS14" s="12" t="s">
+        <v>735</v>
       </c>
       <c r="AT14" s="4" t="s">
-        <v>675</v>
+        <v>736</v>
       </c>
       <c r="AU14" s="4" t="s">
-        <v>676</v>
+        <v>736</v>
       </c>
       <c r="AV14" s="4" t="s">
-        <v>677</v>
+        <v>737</v>
       </c>
       <c r="AW14" s="4" t="s">
-        <v>678</v>
+        <v>738</v>
       </c>
       <c r="AX14" s="4" t="s">
-        <v>662</v>
+        <v>739</v>
       </c>
       <c r="AY14" s="4" t="s">
-        <v>679</v>
+        <v>740</v>
       </c>
       <c r="AZ14" s="4" t="s">
-        <v>680</v>
+        <v>741</v>
       </c>
       <c r="BA14" s="4" t="s">
-        <v>681</v>
+        <v>742</v>
       </c>
       <c r="BB14" s="4" t="s">
-        <v>53</v>
+        <v>723</v>
       </c>
       <c r="BC14" s="4" t="s">
-        <v>682</v>
+        <v>743</v>
       </c>
       <c r="BD14" s="4" t="s">
-        <v>683</v>
+        <v>744</v>
       </c>
       <c r="BE14" s="4" t="s">
-        <v>684</v>
+        <v>745</v>
       </c>
       <c r="BF14" s="4" t="s">
-        <v>685</v>
+        <v>57</v>
       </c>
       <c r="BG14" s="4" t="s">
-        <v>686</v>
+        <v>746</v>
       </c>
       <c r="BH14" s="4" t="s">
-        <v>687</v>
+        <v>747</v>
       </c>
       <c r="BI14" s="4" t="s">
-        <v>688</v>
+        <v>748</v>
       </c>
       <c r="BJ14" s="4" t="s">
-        <v>664</v>
+        <v>749</v>
       </c>
       <c r="BK14" s="4" t="s">
-        <v>689</v>
+        <v>750</v>
       </c>
       <c r="BL14" s="4" t="s">
-        <v>682</v>
+        <v>751</v>
       </c>
       <c r="BM14" s="4" t="s">
-        <v>690</v>
+        <v>752</v>
       </c>
       <c r="BN14" s="4" t="s">
-        <v>691</v>
+        <v>725</v>
       </c>
       <c r="BO14" s="4" t="s">
-        <v>66</v>
+        <v>753</v>
       </c>
       <c r="BP14" s="4" t="s">
-        <v>692</v>
+        <v>746</v>
       </c>
       <c r="BQ14" s="4" t="s">
-        <v>693</v>
+        <v>754</v>
       </c>
       <c r="BR14" s="4" t="s">
-        <v>694</v>
+        <v>755</v>
       </c>
       <c r="BS14" s="4" t="s">
-        <v>695</v>
+        <v>70</v>
       </c>
       <c r="BT14" s="4" t="s">
-        <v>696</v>
+        <v>756</v>
       </c>
       <c r="BU14" s="4" t="s">
-        <v>697</v>
+        <v>757</v>
       </c>
       <c r="BV14" s="4" t="s">
-        <v>698</v>
+        <v>758</v>
       </c>
       <c r="BW14" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="BX14" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="BY14" s="5" t="s">
-        <v>187</v>
+        <v>759</v>
+      </c>
+      <c r="BX14" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="BY14" s="4" t="s">
+        <v>761</v>
       </c>
       <c r="BZ14" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="CA14" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="CB14" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="CC14" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="CD14" s="1" t="s">
-        <v>192</v>
+        <v>762</v>
+      </c>
+      <c r="CA14" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="CB14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="CC14" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="CD14" s="4" t="s">
+        <v>764</v>
       </c>
       <c r="CE14" s="1" t="s">
-        <v>704</v>
+        <v>765</v>
+      </c>
+      <c r="CF14" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="CG14" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="CH14" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="CI14" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="CJ14" s="0" t="s">
+        <v>769</v>
+      </c>
+      <c r="CK14" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="CL14" s="0" t="s">
+        <v>771</v>
+      </c>
+      <c r="CM14" s="0" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>705</v>
+        <v>773</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>706</v>
+        <v>774</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="9" t="s">
-        <v>651</v>
+        <v>712</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>707</v>
+        <v>775</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>708</v>
+        <v>776</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>709</v>
+        <v>777</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>710</v>
+        <v>778</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>711</v>
+        <v>779</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>712</v>
+        <v>780</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>713</v>
+        <v>781</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>714</v>
+        <v>782</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>715</v>
+        <v>783</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>716</v>
+        <v>784</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>717</v>
+        <v>785</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>718</v>
+        <v>786</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>719</v>
+        <v>787</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>720</v>
+        <v>788</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>721</v>
+        <v>789</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>722</v>
+        <v>790</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AC15" s="4" t="s">
-        <v>723</v>
+        <v>151</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>724</v>
+        <v>791</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>725</v>
+        <v>792</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>144</v>
+        <v>793</v>
       </c>
       <c r="AG15" s="4" t="s">
-        <v>726</v>
+        <v>155</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>727</v>
+        <v>794</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>728</v>
+        <v>795</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>729</v>
+        <v>796</v>
       </c>
       <c r="AK15" s="4" t="s">
-        <v>730</v>
+        <v>797</v>
       </c>
       <c r="AL15" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="AM15" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="AN15" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="AM15" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="AN15" s="4" t="s">
-        <v>732</v>
-      </c>
       <c r="AO15" s="4" t="s">
-        <v>733</v>
+        <v>800</v>
       </c>
       <c r="AP15" s="4" t="s">
-        <v>734</v>
+        <v>801</v>
       </c>
       <c r="AQ15" s="4" t="s">
-        <v>735</v>
+        <v>802</v>
       </c>
       <c r="AR15" s="4" t="s">
-        <v>735</v>
+        <v>803</v>
       </c>
       <c r="AS15" s="4" t="s">
-        <v>736</v>
+        <v>804</v>
       </c>
       <c r="AT15" s="4" t="s">
-        <v>737</v>
+        <v>805</v>
       </c>
       <c r="AU15" s="4" t="s">
-        <v>738</v>
+        <v>805</v>
       </c>
       <c r="AV15" s="4" t="s">
-        <v>739</v>
+        <v>806</v>
       </c>
       <c r="AW15" s="4" t="s">
-        <v>740</v>
+        <v>807</v>
       </c>
       <c r="AX15" s="4" t="s">
-        <v>741</v>
+        <v>808</v>
       </c>
       <c r="AY15" s="4" t="s">
-        <v>742</v>
+        <v>809</v>
       </c>
       <c r="AZ15" s="4" t="s">
-        <v>743</v>
+        <v>810</v>
       </c>
       <c r="BA15" s="4" t="s">
-        <v>744</v>
+        <v>811</v>
       </c>
       <c r="BB15" s="4" t="s">
-        <v>53</v>
+        <v>812</v>
       </c>
       <c r="BC15" s="4" t="s">
-        <v>745</v>
+        <v>813</v>
       </c>
       <c r="BD15" s="4" t="s">
-        <v>746</v>
+        <v>814</v>
       </c>
       <c r="BE15" s="4" t="s">
-        <v>747</v>
+        <v>815</v>
       </c>
       <c r="BF15" s="4" t="s">
-        <v>748</v>
+        <v>57</v>
       </c>
       <c r="BG15" s="4" t="s">
-        <v>749</v>
+        <v>816</v>
       </c>
       <c r="BH15" s="4" t="s">
-        <v>750</v>
+        <v>817</v>
       </c>
       <c r="BI15" s="4" t="s">
-        <v>751</v>
+        <v>818</v>
       </c>
       <c r="BJ15" s="4" t="s">
-        <v>752</v>
+        <v>819</v>
       </c>
       <c r="BK15" s="4" t="s">
-        <v>753</v>
+        <v>820</v>
       </c>
       <c r="BL15" s="4" t="s">
-        <v>754</v>
+        <v>821</v>
       </c>
       <c r="BM15" s="4" t="s">
-        <v>755</v>
+        <v>822</v>
       </c>
       <c r="BN15" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="BO15" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP15" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="BQ15" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="BR15" s="5" t="s">
-        <v>759</v>
+        <v>823</v>
+      </c>
+      <c r="BO15" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="BP15" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="BQ15" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="BR15" s="4" t="s">
+        <v>827</v>
       </c>
       <c r="BS15" s="5" t="s">
-        <v>760</v>
+        <v>70</v>
       </c>
       <c r="BT15" s="5" t="s">
-        <v>761</v>
+        <v>828</v>
       </c>
       <c r="BU15" s="5" t="s">
-        <v>762</v>
+        <v>829</v>
       </c>
       <c r="BV15" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="BW15" s="4" t="s">
-        <v>764</v>
+        <v>830</v>
+      </c>
+      <c r="BW15" s="5" t="s">
+        <v>831</v>
       </c>
       <c r="BX15" s="5" t="s">
-        <v>186</v>
+        <v>832</v>
       </c>
       <c r="BY15" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="BZ15" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="CA15" s="10" t="s">
-        <v>766</v>
-      </c>
-      <c r="CB15" s="10" t="s">
-        <v>767</v>
-      </c>
-      <c r="CC15" s="10" t="s">
-        <v>768</v>
-      </c>
-      <c r="CD15" s="10" t="s">
-        <v>769</v>
+        <v>833</v>
+      </c>
+      <c r="BZ15" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="CA15" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="CB15" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="CC15" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="CD15" s="4" t="s">
+        <v>836</v>
       </c>
       <c r="CE15" s="10" t="s">
-        <v>770</v>
+        <v>837</v>
+      </c>
+      <c r="CF15" s="10" t="s">
+        <v>838</v>
+      </c>
+      <c r="CG15" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="CH15" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="CI15" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="CJ15" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="CK15" s="11" t="s">
+        <v>843</v>
+      </c>
+      <c r="CL15" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="CM15" s="11" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>771</v>
+        <v>846</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>772</v>
+        <v>847</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>774</v>
+        <v>848</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>849</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>775</v>
+        <v>850</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>776</v>
+        <v>851</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>777</v>
+        <v>852</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>778</v>
+        <v>853</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>778</v>
+        <v>853</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>779</v>
+        <v>854</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>780</v>
+        <v>855</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>12</v>
@@ -9340,351 +10243,375 @@
         <v>13</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>781</v>
+        <v>856</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>782</v>
+        <v>857</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>783</v>
+        <v>858</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>784</v>
+        <v>859</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>785</v>
+        <v>860</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>786</v>
+        <v>861</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>787</v>
+        <v>862</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>788</v>
+        <v>863</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>789</v>
+        <v>864</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>790</v>
+        <v>865</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>791</v>
+        <v>866</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>792</v>
+        <v>867</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>793</v>
+        <v>868</v>
       </c>
       <c r="AB16" s="6" t="s">
-        <v>794</v>
+        <v>869</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>795</v>
+        <v>870</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>796</v>
+        <v>871</v>
       </c>
       <c r="AE16" s="6" t="s">
-        <v>797</v>
+        <v>872</v>
       </c>
       <c r="AF16" s="6" t="s">
-        <v>31</v>
+        <v>873</v>
       </c>
       <c r="AG16" s="6" t="s">
-        <v>798</v>
+        <v>32</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>799</v>
+        <v>874</v>
       </c>
       <c r="AI16" s="6" t="s">
-        <v>800</v>
+        <v>875</v>
       </c>
       <c r="AJ16" s="6" t="s">
-        <v>801</v>
+        <v>876</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>802</v>
+        <v>877</v>
       </c>
       <c r="AL16" s="6" t="s">
-        <v>803</v>
+        <v>878</v>
       </c>
       <c r="AM16" s="6" t="s">
-        <v>804</v>
+        <v>879</v>
       </c>
       <c r="AN16" s="6" t="s">
-        <v>805</v>
+        <v>880</v>
       </c>
       <c r="AO16" s="6" t="s">
-        <v>806</v>
+        <v>881</v>
       </c>
       <c r="AP16" s="6" t="s">
-        <v>807</v>
+        <v>882</v>
       </c>
       <c r="AQ16" s="6" t="s">
-        <v>808</v>
+        <v>883</v>
       </c>
       <c r="AR16" s="6" t="s">
-        <v>809</v>
+        <v>884</v>
       </c>
       <c r="AS16" s="6" t="s">
-        <v>810</v>
+        <v>885</v>
       </c>
       <c r="AT16" s="6" t="s">
-        <v>811</v>
+        <v>886</v>
       </c>
       <c r="AU16" s="6" t="s">
-        <v>812</v>
+        <v>887</v>
       </c>
       <c r="AV16" s="6" t="s">
-        <v>813</v>
+        <v>888</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>814</v>
+        <v>889</v>
       </c>
       <c r="AX16" s="6" t="s">
-        <v>815</v>
+        <v>890</v>
       </c>
       <c r="AY16" s="6" t="s">
-        <v>816</v>
+        <v>891</v>
       </c>
       <c r="AZ16" s="6" t="s">
-        <v>817</v>
+        <v>892</v>
       </c>
       <c r="BA16" s="6" t="s">
-        <v>818</v>
+        <v>893</v>
       </c>
       <c r="BB16" s="6" t="s">
-        <v>53</v>
+        <v>894</v>
       </c>
       <c r="BC16" s="6" t="s">
-        <v>819</v>
+        <v>895</v>
       </c>
       <c r="BD16" s="6" t="s">
-        <v>820</v>
+        <v>896</v>
       </c>
       <c r="BE16" s="6" t="s">
-        <v>821</v>
+        <v>897</v>
       </c>
       <c r="BF16" s="6" t="s">
-        <v>822</v>
+        <v>57</v>
       </c>
       <c r="BG16" s="6" t="s">
-        <v>823</v>
+        <v>898</v>
       </c>
       <c r="BH16" s="6" t="s">
-        <v>824</v>
+        <v>899</v>
       </c>
       <c r="BI16" s="6" t="s">
-        <v>825</v>
+        <v>900</v>
       </c>
       <c r="BJ16" s="6" t="s">
-        <v>826</v>
+        <v>901</v>
       </c>
       <c r="BK16" s="6" t="s">
-        <v>827</v>
+        <v>902</v>
       </c>
       <c r="BL16" s="6" t="s">
-        <v>828</v>
+        <v>903</v>
       </c>
       <c r="BM16" s="6" t="s">
-        <v>829</v>
+        <v>904</v>
       </c>
       <c r="BN16" s="6" t="s">
-        <v>830</v>
-      </c>
-      <c r="BO16" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP16" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="BQ16" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="BR16" s="5" t="s">
-        <v>833</v>
+        <v>905</v>
+      </c>
+      <c r="BO16" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="BP16" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="BQ16" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="BR16" s="6" t="s">
+        <v>909</v>
       </c>
       <c r="BS16" s="5" t="s">
-        <v>834</v>
+        <v>70</v>
       </c>
       <c r="BT16" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="BU16" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="BV16" s="4" t="s">
-        <v>836</v>
-      </c>
-      <c r="BW16" s="6" t="s">
-        <v>837</v>
+        <v>910</v>
+      </c>
+      <c r="BU16" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="BV16" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="BW16" s="5" t="s">
+        <v>913</v>
       </c>
       <c r="BX16" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="BY16" s="6" t="s">
-        <v>838</v>
-      </c>
-      <c r="BZ16" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="CA16" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="CB16" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="CC16" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="CD16" s="1" t="s">
-        <v>843</v>
+        <v>914</v>
+      </c>
+      <c r="BY16" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="BZ16" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="CA16" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="CB16" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="CC16" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="CD16" s="6" t="s">
+        <v>918</v>
       </c>
       <c r="CE16" s="1" t="s">
-        <v>844</v>
+        <v>919</v>
+      </c>
+      <c r="CF16" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="CG16" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="CH16" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="CI16" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="CJ16" s="0" t="s">
+        <v>924</v>
+      </c>
+      <c r="CK16" s="0" t="s">
+        <v>925</v>
+      </c>
+      <c r="CL16" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="CM16" s="0" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>845</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>845</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>773</v>
+        <v>928</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>928</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>848</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>846</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>847</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="G17" s="20" t="s">
+        <v>929</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>930</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="G17" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="21" t="s">
-        <v>848</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>849</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>849</v>
-      </c>
-      <c r="K17" s="21" t="s">
-        <v>850</v>
-      </c>
-      <c r="L17" s="21" t="s">
-        <v>851</v>
-      </c>
-      <c r="M17" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="N17" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="O17" s="18" t="s">
+      <c r="H17" s="22" t="s">
+        <v>931</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>932</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>932</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>933</v>
+      </c>
+      <c r="L17" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="M17" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="O17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q17" s="20" t="s">
+      <c r="P17" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q17" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="S17" s="20" t="s">
+      <c r="R17" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="S17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="T17" s="20" t="s">
+      <c r="T17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="U17" s="20" t="s">
+      <c r="U17" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="20" t="s">
+      <c r="V17" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="W17" s="20" t="s">
+      <c r="W17" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="X17" s="20" t="s">
+      <c r="X17" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="Y17" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z17" s="18" t="s">
+      <c r="Y17" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z17" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="AA17" s="20" t="s">
-        <v>852</v>
-      </c>
-      <c r="AB17" s="20" t="s">
+      <c r="AA17" s="21" t="s">
+        <v>935</v>
+      </c>
+      <c r="AB17" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AC17" s="20" t="s">
+      <c r="AC17" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AD17" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE17" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF17" s="20" t="s">
+      <c r="AD17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE17" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF17" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AG17" s="20" t="s">
+      <c r="AG17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AH17" s="20" t="s">
+      <c r="AH17" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="AI17" s="20" t="s">
+      <c r="AI17" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="AJ17" s="1" t="s">
-        <v>33</v>
+      <c r="AJ17" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="AO17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP17" s="20" t="s">
+      <c r="AP17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ17" s="1" t="s">
+      <c r="AQ17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR17" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AR17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS17" s="1" t="s">
+      <c r="AS17" s="21" t="s">
         <v>44</v>
       </c>
       <c r="AT17" s="1" t="s">
-        <v>274</v>
+        <v>46</v>
       </c>
       <c r="AU17" s="1" t="s">
         <v>46</v>
@@ -9693,7 +10620,7 @@
         <v>47</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>48</v>
+        <v>297</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>49</v>
@@ -9726,7 +10653,7 @@
         <v>58</v>
       </c>
       <c r="BH17" s="1" t="s">
-        <v>275</v>
+        <v>59</v>
       </c>
       <c r="BI17" s="1" t="s">
         <v>60</v>
@@ -9738,7 +10665,7 @@
         <v>62</v>
       </c>
       <c r="BL17" s="1" t="s">
-        <v>63</v>
+        <v>298</v>
       </c>
       <c r="BM17" s="1" t="s">
         <v>64</v>
@@ -9746,456 +10673,504 @@
       <c r="BN17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO17" s="20" t="s">
-        <v>853</v>
+      <c r="BO17" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="BP17" s="1" t="s">
         <v>67</v>
       </c>
       <c r="BQ17" s="1" t="s">
-        <v>240</v>
+        <v>68</v>
       </c>
       <c r="BR17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS17" s="1" t="s">
-        <v>70</v>
+      <c r="BS17" s="21" t="s">
+        <v>936</v>
       </c>
       <c r="BT17" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="BU17" s="20" t="s">
-        <v>855</v>
+        <v>71</v>
+      </c>
+      <c r="BU17" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="BV17" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="BW17" s="20" t="s">
-        <v>857</v>
-      </c>
-      <c r="BX17" s="20" t="s">
-        <v>858</v>
-      </c>
-      <c r="BY17" s="20" t="s">
-        <v>859</v>
-      </c>
-      <c r="BZ17" s="20" t="s">
-        <v>860</v>
-      </c>
-      <c r="CA17" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="CB17" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="CC17" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="CD17" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="BW17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX17" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="BY17" s="21" t="s">
+        <v>938</v>
+      </c>
+      <c r="BZ17" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="CA17" s="21" t="s">
+        <v>940</v>
+      </c>
+      <c r="CB17" s="21" t="s">
+        <v>941</v>
+      </c>
+      <c r="CC17" s="21" t="s">
+        <v>942</v>
+      </c>
+      <c r="CD17" s="21" t="s">
+        <v>943</v>
       </c>
       <c r="CE17" s="1" t="s">
-        <v>82</v>
+        <v>944</v>
+      </c>
+      <c r="CF17" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="CG17" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="CH17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ17" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="CK17" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL17" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM17" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>863</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>864</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>773</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>846</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>865</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>866</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>867</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>867</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>868</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>869</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="N18" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="O18" s="19" t="s">
-        <v>870</v>
-      </c>
-      <c r="P18" s="19" t="s">
-        <v>871</v>
-      </c>
-      <c r="Q18" s="19" t="s">
-        <v>872</v>
-      </c>
-      <c r="R18" s="19" t="s">
-        <v>873</v>
-      </c>
-      <c r="S18" s="19" t="s">
-        <v>656</v>
-      </c>
-      <c r="T18" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="U18" s="19" t="s">
-        <v>874</v>
-      </c>
-      <c r="V18" s="19" t="s">
-        <v>875</v>
-      </c>
-      <c r="W18" s="19" t="s">
+      <c r="A18" s="20" t="s">
+        <v>946</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>947</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>848</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>929</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>948</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>949</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>950</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>950</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>951</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>952</v>
+      </c>
+      <c r="M18" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="X18" s="19" t="s">
-        <v>876</v>
-      </c>
-      <c r="Y18" s="19" t="s">
-        <v>658</v>
-      </c>
-      <c r="Z18" s="19" t="s">
-        <v>877</v>
-      </c>
-      <c r="AA18" s="19" t="s">
-        <v>878</v>
-      </c>
-      <c r="AB18" s="19" t="s">
-        <v>522</v>
-      </c>
-      <c r="AC18" s="19" t="s">
-        <v>879</v>
+      <c r="N18" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>953</v>
+      </c>
+      <c r="P18" s="20" t="s">
+        <v>954</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>955</v>
+      </c>
+      <c r="R18" s="20" t="s">
+        <v>956</v>
+      </c>
+      <c r="S18" s="20" t="s">
+        <v>717</v>
+      </c>
+      <c r="T18" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="U18" s="20" t="s">
+        <v>957</v>
+      </c>
+      <c r="V18" s="20" t="s">
+        <v>958</v>
+      </c>
+      <c r="W18" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="X18" s="20" t="s">
+        <v>959</v>
+      </c>
+      <c r="Y18" s="20" t="s">
+        <v>719</v>
+      </c>
+      <c r="Z18" s="20" t="s">
+        <v>960</v>
+      </c>
+      <c r="AA18" s="20" t="s">
+        <v>961</v>
+      </c>
+      <c r="AB18" s="20" t="s">
+        <v>567</v>
+      </c>
+      <c r="AC18" s="20" t="s">
+        <v>151</v>
       </c>
       <c r="AD18" s="20" t="s">
-        <v>662</v>
-      </c>
-      <c r="AE18" s="19" t="s">
-        <v>880</v>
+        <v>962</v>
+      </c>
+      <c r="AE18" s="21" t="s">
+        <v>723</v>
       </c>
       <c r="AF18" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG18" s="19" t="s">
-        <v>881</v>
-      </c>
-      <c r="AH18" s="19" t="s">
-        <v>882</v>
-      </c>
-      <c r="AI18" s="19" t="s">
-        <v>883</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>667</v>
+        <v>963</v>
+      </c>
+      <c r="AG18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH18" s="20" t="s">
+        <v>964</v>
+      </c>
+      <c r="AI18" s="20" t="s">
+        <v>965</v>
+      </c>
+      <c r="AJ18" s="20" t="s">
+        <v>966</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>884</v>
+        <v>728</v>
       </c>
       <c r="AL18" s="1" t="s">
-        <v>885</v>
+        <v>967</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>532</v>
+        <v>968</v>
       </c>
       <c r="AN18" s="1" t="s">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="AO18" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="AP18" s="19" t="s">
-        <v>887</v>
-      </c>
-      <c r="AQ18" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="AR18" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="AS18" s="1" t="s">
-        <v>889</v>
+        <v>579</v>
+      </c>
+      <c r="AP18" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="AQ18" s="20" t="s">
+        <v>970</v>
+      </c>
+      <c r="AR18" s="20" t="s">
+        <v>734</v>
+      </c>
+      <c r="AS18" s="20" t="s">
+        <v>971</v>
       </c>
       <c r="AT18" s="1" t="s">
-        <v>890</v>
+        <v>740</v>
       </c>
       <c r="AU18" s="1" t="s">
-        <v>676</v>
+        <v>740</v>
       </c>
       <c r="AV18" s="1" t="s">
-        <v>891</v>
+        <v>972</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>892</v>
+        <v>973</v>
       </c>
       <c r="AX18" s="1" t="s">
-        <v>662</v>
+        <v>739</v>
       </c>
       <c r="AY18" s="1" t="s">
-        <v>679</v>
+        <v>740</v>
       </c>
       <c r="AZ18" s="1" t="s">
-        <v>893</v>
+        <v>974</v>
       </c>
       <c r="BA18" s="1" t="s">
-        <v>544</v>
+        <v>975</v>
       </c>
       <c r="BB18" s="1" t="s">
-        <v>894</v>
+        <v>723</v>
       </c>
       <c r="BC18" s="1" t="s">
-        <v>895</v>
+        <v>743</v>
       </c>
       <c r="BD18" s="1" t="s">
-        <v>895</v>
+        <v>976</v>
       </c>
       <c r="BE18" s="1" t="s">
-        <v>896</v>
+        <v>593</v>
       </c>
       <c r="BF18" s="1" t="s">
-        <v>685</v>
+        <v>977</v>
       </c>
       <c r="BG18" s="1" t="s">
-        <v>686</v>
+        <v>978</v>
       </c>
       <c r="BH18" s="1" t="s">
-        <v>897</v>
+        <v>978</v>
       </c>
       <c r="BI18" s="1" t="s">
-        <v>898</v>
+        <v>979</v>
       </c>
       <c r="BJ18" s="1" t="s">
-        <v>899</v>
+        <v>749</v>
       </c>
       <c r="BK18" s="1" t="s">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="BL18" s="1" t="s">
-        <v>901</v>
+        <v>980</v>
       </c>
       <c r="BM18" s="1" t="s">
-        <v>64</v>
+        <v>981</v>
       </c>
       <c r="BN18" s="1" t="s">
-        <v>902</v>
-      </c>
-      <c r="BO18" s="20" t="s">
-        <v>66</v>
+        <v>982</v>
+      </c>
+      <c r="BO18" s="1" t="s">
+        <v>983</v>
       </c>
       <c r="BP18" s="1" t="s">
-        <v>903</v>
+        <v>984</v>
       </c>
       <c r="BQ18" s="1" t="s">
-        <v>904</v>
+        <v>68</v>
       </c>
       <c r="BR18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS18" s="1" t="s">
-        <v>905</v>
+        <v>985</v>
+      </c>
+      <c r="BS18" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="BT18" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="BU18" s="19" t="s">
-        <v>907</v>
+        <v>986</v>
+      </c>
+      <c r="BU18" s="1" t="s">
+        <v>987</v>
       </c>
       <c r="BV18" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="BW18" s="19" t="s">
-        <v>908</v>
-      </c>
-      <c r="BX18" s="19" t="s">
-        <v>909</v>
-      </c>
-      <c r="BY18" s="19" t="s">
-        <v>910</v>
-      </c>
-      <c r="BZ18" s="19" t="s">
-        <v>911</v>
-      </c>
-      <c r="CA18" s="1" t="s">
-        <v>912</v>
-      </c>
-      <c r="CB18" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="CC18" s="1" t="s">
-        <v>914</v>
-      </c>
-      <c r="CD18" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="BW18" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="BX18" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="BY18" s="20" t="s">
+        <v>990</v>
+      </c>
+      <c r="BZ18" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="CA18" s="20" t="s">
+        <v>991</v>
+      </c>
+      <c r="CB18" s="20" t="s">
+        <v>992</v>
+      </c>
+      <c r="CC18" s="20" t="s">
+        <v>993</v>
+      </c>
+      <c r="CD18" s="20" t="s">
+        <v>994</v>
       </c>
       <c r="CE18" s="1" t="s">
-        <v>915</v>
+        <v>995</v>
+      </c>
+      <c r="CF18" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="CG18" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="CH18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CI18" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="CJ18" s="0" t="s">
+        <v>999</v>
+      </c>
+      <c r="CK18" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="CL18" s="0" t="s">
+        <v>1001</v>
+      </c>
+      <c r="CM18" s="0" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>916</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>917</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>773</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>846</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>847</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="19" t="s">
+      <c r="A19" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>848</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>929</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>930</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="23" t="s">
-        <v>848</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>849</v>
-      </c>
-      <c r="J19" s="23" t="s">
-        <v>849</v>
-      </c>
-      <c r="K19" s="21" t="s">
-        <v>850</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>851</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>918</v>
-      </c>
-      <c r="N19" s="19" t="s">
+      <c r="H19" s="24" t="s">
+        <v>931</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>932</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>932</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>933</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>934</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>1005</v>
+      </c>
+      <c r="N19" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="O19" s="19" t="s">
+      <c r="O19" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q19" s="19" t="s">
+      <c r="P19" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q19" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R19" s="19" t="s">
+      <c r="R19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="S19" s="19" t="s">
+      <c r="S19" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="T19" s="19" t="s">
+      <c r="T19" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="19" t="s">
+      <c r="U19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="19" t="s">
+      <c r="V19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="19" t="s">
+      <c r="W19" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="X19" s="19" t="s">
-        <v>919</v>
-      </c>
-      <c r="Y19" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="Z19" s="19" t="s">
-        <v>520</v>
-      </c>
-      <c r="AA19" s="19" t="s">
-        <v>920</v>
-      </c>
-      <c r="AB19" s="19" t="s">
+      <c r="X19" s="20" t="s">
+        <v>1006</v>
+      </c>
+      <c r="Y19" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z19" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="AA19" s="20" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AB19" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="AC19" s="19" t="s">
-        <v>921</v>
-      </c>
-      <c r="AD19" s="19" t="s">
-        <v>922</v>
+      <c r="AC19" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD19" s="20" t="s">
+        <v>1008</v>
       </c>
       <c r="AE19" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF19" s="20" t="s">
+        <v>1009</v>
+      </c>
+      <c r="AF19" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="AG19" s="20" t="s">
+      <c r="AG19" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="AH19" s="20" t="s">
-        <v>923</v>
-      </c>
-      <c r="AI19" s="20" t="s">
+      <c r="AH19" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI19" s="21" t="s">
+        <v>1010</v>
+      </c>
+      <c r="AJ19" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AK19" s="1" t="s">
-        <v>924</v>
-      </c>
       <c r="AL19" s="1" t="s">
-        <v>37</v>
+        <v>1011</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>925</v>
+        <v>38</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>39</v>
+        <v>1012</v>
       </c>
       <c r="AO19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP19" s="20" t="s">
+      <c r="AP19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ19" s="1" t="s">
+      <c r="AQ19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR19" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AR19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS19" s="1" t="s">
-        <v>43</v>
+      <c r="AS19" s="21" t="s">
+        <v>44</v>
       </c>
       <c r="AT19" s="1" t="s">
-        <v>274</v>
+        <v>46</v>
       </c>
       <c r="AU19" s="1" t="s">
         <v>46</v>
       </c>
       <c r="AV19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>48</v>
+        <v>297</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>49</v>
@@ -10213,25 +11188,25 @@
         <v>53</v>
       </c>
       <c r="BC19" s="1" t="s">
-        <v>926</v>
+        <v>54</v>
       </c>
       <c r="BD19" s="1" t="s">
-        <v>926</v>
+        <v>55</v>
       </c>
       <c r="BE19" s="1" t="s">
-        <v>229</v>
+        <v>56</v>
       </c>
       <c r="BF19" s="1" t="s">
         <v>57</v>
       </c>
       <c r="BG19" s="1" t="s">
-        <v>58</v>
+        <v>1013</v>
       </c>
       <c r="BH19" s="1" t="s">
-        <v>275</v>
+        <v>1013</v>
       </c>
       <c r="BI19" s="1" t="s">
-        <v>927</v>
+        <v>248</v>
       </c>
       <c r="BJ19" s="1" t="s">
         <v>61</v>
@@ -10240,313 +11215,361 @@
         <v>62</v>
       </c>
       <c r="BL19" s="1" t="s">
-        <v>102</v>
+        <v>298</v>
       </c>
       <c r="BM19" s="1" t="s">
-        <v>64</v>
+        <v>1014</v>
       </c>
       <c r="BN19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BO19" s="20" t="s">
+      <c r="BO19" s="1" t="s">
         <v>66</v>
       </c>
       <c r="BP19" s="1" t="s">
-        <v>928</v>
+        <v>111</v>
       </c>
       <c r="BQ19" s="1" t="s">
-        <v>929</v>
+        <v>68</v>
       </c>
       <c r="BR19" s="1" t="s">
-        <v>930</v>
-      </c>
-      <c r="BS19" s="1" t="s">
-        <v>931</v>
+        <v>69</v>
+      </c>
+      <c r="BS19" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="BT19" s="1" t="s">
-        <v>932</v>
-      </c>
-      <c r="BU19" s="20" t="s">
-        <v>933</v>
+        <v>1015</v>
+      </c>
+      <c r="BU19" s="1" t="s">
+        <v>1016</v>
       </c>
       <c r="BV19" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="BW19" s="19" t="s">
-        <v>934</v>
-      </c>
-      <c r="BX19" s="20" t="s">
-        <v>935</v>
-      </c>
-      <c r="BY19" s="20" t="s">
-        <v>936</v>
-      </c>
-      <c r="BZ19" s="19" t="s">
-        <v>937</v>
-      </c>
-      <c r="CA19" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="CB19" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="BW19" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="BX19" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="BY19" s="21" t="s">
+        <v>1020</v>
+      </c>
+      <c r="BZ19" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="CC19" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="CD19" s="1" t="s">
-        <v>940</v>
+      <c r="CA19" s="20" t="s">
+        <v>1021</v>
+      </c>
+      <c r="CB19" s="21" t="s">
+        <v>1022</v>
+      </c>
+      <c r="CC19" s="21" t="s">
+        <v>1023</v>
+      </c>
+      <c r="CD19" s="20" t="s">
+        <v>1024</v>
       </c>
       <c r="CE19" s="1" t="s">
-        <v>82</v>
+        <v>1025</v>
+      </c>
+      <c r="CF19" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="CG19" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="CH19" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="CI19" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ19" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="CK19" s="0" t="s">
+        <v>1028</v>
+      </c>
+      <c r="CL19" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM19" s="0" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>941</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>942</v>
-      </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19" t="s">
-        <v>510</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>943</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>944</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>945</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>946</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>947</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>948</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>949</v>
-      </c>
-      <c r="L20" s="20" t="s">
-        <v>950</v>
-      </c>
-      <c r="M20" s="20" t="s">
-        <v>951</v>
-      </c>
-      <c r="N20" s="20" t="s">
-        <v>952</v>
-      </c>
-      <c r="O20" s="18" t="s">
-        <v>953</v>
-      </c>
-      <c r="P20" s="18" t="s">
-        <v>954</v>
-      </c>
-      <c r="Q20" s="20" t="s">
-        <v>955</v>
-      </c>
-      <c r="R20" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="S20" s="20" t="s">
+      <c r="A20" s="20" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20" t="s">
+        <v>555</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>1039</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="O20" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="Q20" s="21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="R20" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="S20" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="T20" s="20" t="s">
+      <c r="T20" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="U20" s="20" t="s">
-        <v>956</v>
-      </c>
-      <c r="V20" s="20" t="s">
-        <v>957</v>
-      </c>
-      <c r="W20" s="20" t="s">
-        <v>958</v>
-      </c>
-      <c r="X20" s="20" t="s">
-        <v>959</v>
-      </c>
-      <c r="Y20" s="18" t="s">
-        <v>960</v>
-      </c>
-      <c r="Z20" s="18" t="s">
-        <v>961</v>
-      </c>
-      <c r="AA20" s="20" t="s">
-        <v>962</v>
-      </c>
-      <c r="AB20" s="20" t="s">
-        <v>963</v>
-      </c>
-      <c r="AC20" s="20" t="s">
-        <v>964</v>
-      </c>
-      <c r="AD20" s="20" t="s">
-        <v>965</v>
-      </c>
-      <c r="AE20" s="20" t="s">
-        <v>966</v>
-      </c>
-      <c r="AF20" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG20" s="20" t="s">
-        <v>967</v>
-      </c>
-      <c r="AH20" s="20" t="s">
-        <v>968</v>
-      </c>
-      <c r="AI20" s="20" t="s">
-        <v>969</v>
-      </c>
-      <c r="AJ20" s="1" t="s">
-        <v>970</v>
+      <c r="U20" s="21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="V20" s="21" t="s">
+        <v>1045</v>
+      </c>
+      <c r="W20" s="21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="X20" s="21" t="s">
+        <v>1047</v>
+      </c>
+      <c r="Y20" s="19" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Z20" s="19" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AA20" s="21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AB20" s="21" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AC20" s="21" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AD20" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AE20" s="21" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AF20" s="21" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AG20" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH20" s="21" t="s">
+        <v>1056</v>
+      </c>
+      <c r="AI20" s="21" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AJ20" s="21" t="s">
+        <v>1058</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>971</v>
+        <v>1059</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>972</v>
+        <v>1060</v>
       </c>
       <c r="AM20" s="1" t="s">
-        <v>973</v>
+        <v>1061</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>974</v>
+        <v>1062</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="AP20" s="20" t="s">
-        <v>976</v>
-      </c>
-      <c r="AQ20" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="AR20" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="AS20" s="1" t="s">
-        <v>979</v>
+        <v>1063</v>
+      </c>
+      <c r="AP20" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="AQ20" s="21" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AR20" s="21" t="s">
+        <v>1066</v>
+      </c>
+      <c r="AS20" s="21" t="s">
+        <v>1067</v>
       </c>
       <c r="AT20" s="1" t="s">
-        <v>980</v>
+        <v>1068</v>
       </c>
       <c r="AU20" s="1" t="s">
-        <v>981</v>
+        <v>1069</v>
       </c>
       <c r="AV20" s="1" t="s">
-        <v>982</v>
+        <v>1070</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>983</v>
+        <v>1071</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>984</v>
+        <v>1072</v>
       </c>
       <c r="AY20" s="1" t="s">
-        <v>50</v>
+        <v>1073</v>
       </c>
       <c r="AZ20" s="1" t="s">
-        <v>985</v>
+        <v>1074</v>
       </c>
       <c r="BA20" s="1" t="s">
-        <v>978</v>
+        <v>1075</v>
       </c>
       <c r="BB20" s="1" t="s">
-        <v>53</v>
+        <v>1076</v>
       </c>
       <c r="BC20" s="1" t="s">
-        <v>986</v>
+        <v>54</v>
       </c>
       <c r="BD20" s="1" t="s">
-        <v>987</v>
+        <v>1077</v>
       </c>
       <c r="BE20" s="1" t="s">
-        <v>988</v>
+        <v>1069</v>
       </c>
       <c r="BF20" s="1" t="s">
-        <v>989</v>
+        <v>57</v>
       </c>
       <c r="BG20" s="1" t="s">
-        <v>990</v>
+        <v>1078</v>
       </c>
       <c r="BH20" s="1" t="s">
-        <v>991</v>
+        <v>1079</v>
       </c>
       <c r="BI20" s="1" t="s">
-        <v>992</v>
+        <v>1080</v>
       </c>
       <c r="BJ20" s="1" t="s">
-        <v>993</v>
+        <v>1081</v>
       </c>
       <c r="BK20" s="1" t="s">
-        <v>994</v>
+        <v>1082</v>
       </c>
       <c r="BL20" s="1" t="s">
-        <v>995</v>
+        <v>1083</v>
       </c>
       <c r="BM20" s="1" t="s">
-        <v>64</v>
+        <v>1084</v>
       </c>
       <c r="BN20" s="1" t="s">
-        <v>996</v>
-      </c>
-      <c r="BO20" s="20" t="s">
-        <v>997</v>
+        <v>1085</v>
+      </c>
+      <c r="BO20" s="1" t="s">
+        <v>1086</v>
       </c>
       <c r="BP20" s="1" t="s">
-        <v>998</v>
+        <v>1087</v>
       </c>
       <c r="BQ20" s="1" t="s">
-        <v>999</v>
+        <v>68</v>
       </c>
       <c r="BR20" s="1" t="s">
-        <v>1000</v>
-      </c>
-      <c r="BS20" s="1" t="s">
-        <v>1001</v>
+        <v>1088</v>
+      </c>
+      <c r="BS20" s="21" t="s">
+        <v>1089</v>
       </c>
       <c r="BT20" s="1" t="s">
-        <v>1002</v>
-      </c>
-      <c r="BU20" s="20" t="s">
-        <v>1003</v>
+        <v>1090</v>
+      </c>
+      <c r="BU20" s="1" t="s">
+        <v>1091</v>
       </c>
       <c r="BV20" s="1" t="s">
-        <v>1004</v>
-      </c>
-      <c r="BW20" s="21" t="s">
-        <v>1005</v>
-      </c>
-      <c r="BX20" s="20" t="s">
-        <v>1006</v>
-      </c>
-      <c r="BY20" s="20" t="s">
-        <v>1007</v>
-      </c>
-      <c r="BZ20" s="20" t="s">
-        <v>1008</v>
-      </c>
-      <c r="CA20" s="1" t="s">
-        <v>1009</v>
-      </c>
-      <c r="CB20" s="1" t="s">
-        <v>1010</v>
-      </c>
-      <c r="CC20" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="CD20" s="1" t="s">
-        <v>1012</v>
+        <v>1092</v>
+      </c>
+      <c r="BW20" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="BX20" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="BY20" s="21" t="s">
+        <v>1095</v>
+      </c>
+      <c r="BZ20" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="CA20" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="CB20" s="21" t="s">
+        <v>1098</v>
+      </c>
+      <c r="CC20" s="21" t="s">
+        <v>1099</v>
+      </c>
+      <c r="CD20" s="21" t="s">
+        <v>1100</v>
       </c>
       <c r="CE20" s="1" t="s">
-        <v>1013</v>
+        <v>1101</v>
+      </c>
+      <c r="CF20" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="CG20" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="CH20" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="CI20" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="CJ20" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="CK20" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="CL20" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="CM20" s="0" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10628,6 +11651,10 @@
       <c r="BX21" s="6"/>
       <c r="BY21" s="6"/>
       <c r="BZ21" s="6"/>
+      <c r="CA21" s="6"/>
+      <c r="CB21" s="6"/>
+      <c r="CC21" s="6"/>
+      <c r="CD21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
@@ -10708,6 +11735,10 @@
       <c r="BX22" s="6"/>
       <c r="BY22" s="6"/>
       <c r="BZ22" s="6"/>
+      <c r="CA22" s="6"/>
+      <c r="CB22" s="6"/>
+      <c r="CC22" s="6"/>
+      <c r="CD22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
@@ -10788,6 +11819,10 @@
       <c r="BX23" s="6"/>
       <c r="BY23" s="6"/>
       <c r="BZ23" s="6"/>
+      <c r="CA23" s="6"/>
+      <c r="CB23" s="6"/>
+      <c r="CC23" s="6"/>
+      <c r="CD23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -10868,6 +11903,10 @@
       <c r="BX24" s="6"/>
       <c r="BY24" s="6"/>
       <c r="BZ24" s="6"/>
+      <c r="CA24" s="6"/>
+      <c r="CB24" s="6"/>
+      <c r="CC24" s="6"/>
+      <c r="CD24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
@@ -10948,6 +11987,10 @@
       <c r="BX25" s="6"/>
       <c r="BY25" s="6"/>
       <c r="BZ25" s="6"/>
+      <c r="CA25" s="6"/>
+      <c r="CB25" s="6"/>
+      <c r="CC25" s="6"/>
+      <c r="CD25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -11028,6 +12071,10 @@
       <c r="BX26" s="6"/>
       <c r="BY26" s="6"/>
       <c r="BZ26" s="6"/>
+      <c r="CA26" s="6"/>
+      <c r="CB26" s="6"/>
+      <c r="CC26" s="6"/>
+      <c r="CD26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
@@ -11108,6 +12155,10 @@
       <c r="BX27" s="6"/>
       <c r="BY27" s="6"/>
       <c r="BZ27" s="6"/>
+      <c r="CA27" s="6"/>
+      <c r="CB27" s="6"/>
+      <c r="CC27" s="6"/>
+      <c r="CD27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -11188,6 +12239,10 @@
       <c r="BX28" s="6"/>
       <c r="BY28" s="6"/>
       <c r="BZ28" s="6"/>
+      <c r="CA28" s="6"/>
+      <c r="CB28" s="6"/>
+      <c r="CC28" s="6"/>
+      <c r="CD28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
@@ -11268,6 +12323,10 @@
       <c r="BX29" s="6"/>
       <c r="BY29" s="6"/>
       <c r="BZ29" s="6"/>
+      <c r="CA29" s="6"/>
+      <c r="CB29" s="6"/>
+      <c r="CC29" s="6"/>
+      <c r="CD29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -11348,6 +12407,10 @@
       <c r="BX30" s="6"/>
       <c r="BY30" s="6"/>
       <c r="BZ30" s="6"/>
+      <c r="CA30" s="6"/>
+      <c r="CB30" s="6"/>
+      <c r="CC30" s="6"/>
+      <c r="CD30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
@@ -11428,6 +12491,10 @@
       <c r="BX31" s="6"/>
       <c r="BY31" s="6"/>
       <c r="BZ31" s="6"/>
+      <c r="CA31" s="6"/>
+      <c r="CB31" s="6"/>
+      <c r="CC31" s="6"/>
+      <c r="CD31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -11508,6 +12575,10 @@
       <c r="BX32" s="6"/>
       <c r="BY32" s="6"/>
       <c r="BZ32" s="6"/>
+      <c r="CA32" s="6"/>
+      <c r="CB32" s="6"/>
+      <c r="CC32" s="6"/>
+      <c r="CD32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
@@ -11588,6 +12659,10 @@
       <c r="BX33" s="6"/>
       <c r="BY33" s="6"/>
       <c r="BZ33" s="6"/>
+      <c r="CA33" s="6"/>
+      <c r="CB33" s="6"/>
+      <c r="CC33" s="6"/>
+      <c r="CD33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -11668,6 +12743,10 @@
       <c r="BX34" s="6"/>
       <c r="BY34" s="6"/>
       <c r="BZ34" s="6"/>
+      <c r="CA34" s="6"/>
+      <c r="CB34" s="6"/>
+      <c r="CC34" s="6"/>
+      <c r="CD34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
@@ -11748,6 +12827,10 @@
       <c r="BX35" s="6"/>
       <c r="BY35" s="6"/>
       <c r="BZ35" s="6"/>
+      <c r="CA35" s="6"/>
+      <c r="CB35" s="6"/>
+      <c r="CC35" s="6"/>
+      <c r="CD35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -11828,6 +12911,10 @@
       <c r="BX36" s="6"/>
       <c r="BY36" s="6"/>
       <c r="BZ36" s="6"/>
+      <c r="CA36" s="6"/>
+      <c r="CB36" s="6"/>
+      <c r="CC36" s="6"/>
+      <c r="CD36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6"/>
@@ -11908,6 +12995,10 @@
       <c r="BX37" s="6"/>
       <c r="BY37" s="6"/>
       <c r="BZ37" s="6"/>
+      <c r="CA37" s="6"/>
+      <c r="CB37" s="6"/>
+      <c r="CC37" s="6"/>
+      <c r="CD37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -11988,6 +13079,10 @@
       <c r="BX38" s="6"/>
       <c r="BY38" s="6"/>
       <c r="BZ38" s="6"/>
+      <c r="CA38" s="6"/>
+      <c r="CB38" s="6"/>
+      <c r="CC38" s="6"/>
+      <c r="CD38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6"/>
@@ -12068,6 +13163,10 @@
       <c r="BX39" s="6"/>
       <c r="BY39" s="6"/>
       <c r="BZ39" s="6"/>
+      <c r="CA39" s="6"/>
+      <c r="CB39" s="6"/>
+      <c r="CC39" s="6"/>
+      <c r="CD39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6"/>
@@ -12148,6 +13247,10 @@
       <c r="BX40" s="6"/>
       <c r="BY40" s="6"/>
       <c r="BZ40" s="6"/>
+      <c r="CA40" s="6"/>
+      <c r="CB40" s="6"/>
+      <c r="CC40" s="6"/>
+      <c r="CD40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6"/>
@@ -12228,6 +13331,10 @@
       <c r="BX41" s="6"/>
       <c r="BY41" s="6"/>
       <c r="BZ41" s="6"/>
+      <c r="CA41" s="6"/>
+      <c r="CB41" s="6"/>
+      <c r="CC41" s="6"/>
+      <c r="CD41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6"/>
@@ -12308,6 +13415,10 @@
       <c r="BX42" s="6"/>
       <c r="BY42" s="6"/>
       <c r="BZ42" s="6"/>
+      <c r="CA42" s="6"/>
+      <c r="CB42" s="6"/>
+      <c r="CC42" s="6"/>
+      <c r="CD42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6"/>
@@ -12388,6 +13499,10 @@
       <c r="BX43" s="6"/>
       <c r="BY43" s="6"/>
       <c r="BZ43" s="6"/>
+      <c r="CA43" s="6"/>
+      <c r="CB43" s="6"/>
+      <c r="CC43" s="6"/>
+      <c r="CD43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6"/>
@@ -12468,6 +13583,10 @@
       <c r="BX44" s="6"/>
       <c r="BY44" s="6"/>
       <c r="BZ44" s="6"/>
+      <c r="CA44" s="6"/>
+      <c r="CB44" s="6"/>
+      <c r="CC44" s="6"/>
+      <c r="CD44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -12548,6 +13667,10 @@
       <c r="BX45" s="6"/>
       <c r="BY45" s="6"/>
       <c r="BZ45" s="6"/>
+      <c r="CA45" s="6"/>
+      <c r="CB45" s="6"/>
+      <c r="CC45" s="6"/>
+      <c r="CD45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6"/>
@@ -12628,6 +13751,10 @@
       <c r="BX46" s="6"/>
       <c r="BY46" s="6"/>
       <c r="BZ46" s="6"/>
+      <c r="CA46" s="6"/>
+      <c r="CB46" s="6"/>
+      <c r="CC46" s="6"/>
+      <c r="CD46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -12708,6 +13835,10 @@
       <c r="BX47" s="6"/>
       <c r="BY47" s="6"/>
       <c r="BZ47" s="6"/>
+      <c r="CA47" s="6"/>
+      <c r="CB47" s="6"/>
+      <c r="CC47" s="6"/>
+      <c r="CD47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6"/>
@@ -12788,6 +13919,10 @@
       <c r="BX48" s="6"/>
       <c r="BY48" s="6"/>
       <c r="BZ48" s="6"/>
+      <c r="CA48" s="6"/>
+      <c r="CB48" s="6"/>
+      <c r="CC48" s="6"/>
+      <c r="CD48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -12868,6 +14003,10 @@
       <c r="BX49" s="6"/>
       <c r="BY49" s="6"/>
       <c r="BZ49" s="6"/>
+      <c r="CA49" s="6"/>
+      <c r="CB49" s="6"/>
+      <c r="CC49" s="6"/>
+      <c r="CD49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6"/>
@@ -12948,6 +14087,10 @@
       <c r="BX50" s="6"/>
       <c r="BY50" s="6"/>
       <c r="BZ50" s="6"/>
+      <c r="CA50" s="6"/>
+      <c r="CB50" s="6"/>
+      <c r="CC50" s="6"/>
+      <c r="CD50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -13028,6 +14171,10 @@
       <c r="BX51" s="6"/>
       <c r="BY51" s="6"/>
       <c r="BZ51" s="6"/>
+      <c r="CA51" s="6"/>
+      <c r="CB51" s="6"/>
+      <c r="CC51" s="6"/>
+      <c r="CD51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6"/>
@@ -13108,6 +14255,10 @@
       <c r="BX52" s="6"/>
       <c r="BY52" s="6"/>
       <c r="BZ52" s="6"/>
+      <c r="CA52" s="6"/>
+      <c r="CB52" s="6"/>
+      <c r="CC52" s="6"/>
+      <c r="CD52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -13188,6 +14339,10 @@
       <c r="BX53" s="6"/>
       <c r="BY53" s="6"/>
       <c r="BZ53" s="6"/>
+      <c r="CA53" s="6"/>
+      <c r="CB53" s="6"/>
+      <c r="CC53" s="6"/>
+      <c r="CD53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6"/>
@@ -13268,6 +14423,10 @@
       <c r="BX54" s="6"/>
       <c r="BY54" s="6"/>
       <c r="BZ54" s="6"/>
+      <c r="CA54" s="6"/>
+      <c r="CB54" s="6"/>
+      <c r="CC54" s="6"/>
+      <c r="CD54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -13348,6 +14507,10 @@
       <c r="BX55" s="6"/>
       <c r="BY55" s="6"/>
       <c r="BZ55" s="6"/>
+      <c r="CA55" s="6"/>
+      <c r="CB55" s="6"/>
+      <c r="CC55" s="6"/>
+      <c r="CD55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6"/>
@@ -13428,6 +14591,10 @@
       <c r="BX56" s="6"/>
       <c r="BY56" s="6"/>
       <c r="BZ56" s="6"/>
+      <c r="CA56" s="6"/>
+      <c r="CB56" s="6"/>
+      <c r="CC56" s="6"/>
+      <c r="CD56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -13508,6 +14675,10 @@
       <c r="BX57" s="6"/>
       <c r="BY57" s="6"/>
       <c r="BZ57" s="6"/>
+      <c r="CA57" s="6"/>
+      <c r="CB57" s="6"/>
+      <c r="CC57" s="6"/>
+      <c r="CD57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6"/>
@@ -13588,6 +14759,10 @@
       <c r="BX58" s="6"/>
       <c r="BY58" s="6"/>
       <c r="BZ58" s="6"/>
+      <c r="CA58" s="6"/>
+      <c r="CB58" s="6"/>
+      <c r="CC58" s="6"/>
+      <c r="CD58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6"/>
@@ -13668,6 +14843,10 @@
       <c r="BX59" s="6"/>
       <c r="BY59" s="6"/>
       <c r="BZ59" s="6"/>
+      <c r="CA59" s="6"/>
+      <c r="CB59" s="6"/>
+      <c r="CC59" s="6"/>
+      <c r="CD59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6"/>
@@ -13748,6 +14927,10 @@
       <c r="BX60" s="6"/>
       <c r="BY60" s="6"/>
       <c r="BZ60" s="6"/>
+      <c r="CA60" s="6"/>
+      <c r="CB60" s="6"/>
+      <c r="CC60" s="6"/>
+      <c r="CD60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6"/>
@@ -13828,6 +15011,10 @@
       <c r="BX61" s="6"/>
       <c r="BY61" s="6"/>
       <c r="BZ61" s="6"/>
+      <c r="CA61" s="6"/>
+      <c r="CB61" s="6"/>
+      <c r="CC61" s="6"/>
+      <c r="CD61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6"/>
@@ -13908,6 +15095,10 @@
       <c r="BX62" s="6"/>
       <c r="BY62" s="6"/>
       <c r="BZ62" s="6"/>
+      <c r="CA62" s="6"/>
+      <c r="CB62" s="6"/>
+      <c r="CC62" s="6"/>
+      <c r="CD62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6"/>
@@ -13988,6 +15179,10 @@
       <c r="BX63" s="6"/>
       <c r="BY63" s="6"/>
       <c r="BZ63" s="6"/>
+      <c r="CA63" s="6"/>
+      <c r="CB63" s="6"/>
+      <c r="CC63" s="6"/>
+      <c r="CD63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -14068,6 +15263,10 @@
       <c r="BX64" s="6"/>
       <c r="BY64" s="6"/>
       <c r="BZ64" s="6"/>
+      <c r="CA64" s="6"/>
+      <c r="CB64" s="6"/>
+      <c r="CC64" s="6"/>
+      <c r="CD64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6"/>
@@ -14148,6 +15347,10 @@
       <c r="BX65" s="6"/>
       <c r="BY65" s="6"/>
       <c r="BZ65" s="6"/>
+      <c r="CA65" s="6"/>
+      <c r="CB65" s="6"/>
+      <c r="CC65" s="6"/>
+      <c r="CD65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -14228,6 +15431,10 @@
       <c r="BX66" s="6"/>
       <c r="BY66" s="6"/>
       <c r="BZ66" s="6"/>
+      <c r="CA66" s="6"/>
+      <c r="CB66" s="6"/>
+      <c r="CC66" s="6"/>
+      <c r="CD66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6"/>
@@ -14308,6 +15515,10 @@
       <c r="BX67" s="6"/>
       <c r="BY67" s="6"/>
       <c r="BZ67" s="6"/>
+      <c r="CA67" s="6"/>
+      <c r="CB67" s="6"/>
+      <c r="CC67" s="6"/>
+      <c r="CD67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -14388,6 +15599,10 @@
       <c r="BX68" s="6"/>
       <c r="BY68" s="6"/>
       <c r="BZ68" s="6"/>
+      <c r="CA68" s="6"/>
+      <c r="CB68" s="6"/>
+      <c r="CC68" s="6"/>
+      <c r="CD68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6"/>
@@ -14468,6 +15683,10 @@
       <c r="BX69" s="6"/>
       <c r="BY69" s="6"/>
       <c r="BZ69" s="6"/>
+      <c r="CA69" s="6"/>
+      <c r="CB69" s="6"/>
+      <c r="CC69" s="6"/>
+      <c r="CD69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -14548,6 +15767,10 @@
       <c r="BX70" s="6"/>
       <c r="BY70" s="6"/>
       <c r="BZ70" s="6"/>
+      <c r="CA70" s="6"/>
+      <c r="CB70" s="6"/>
+      <c r="CC70" s="6"/>
+      <c r="CD70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6"/>
@@ -14628,6 +15851,10 @@
       <c r="BX71" s="6"/>
       <c r="BY71" s="6"/>
       <c r="BZ71" s="6"/>
+      <c r="CA71" s="6"/>
+      <c r="CB71" s="6"/>
+      <c r="CC71" s="6"/>
+      <c r="CD71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -14708,6 +15935,10 @@
       <c r="BX72" s="6"/>
       <c r="BY72" s="6"/>
       <c r="BZ72" s="6"/>
+      <c r="CA72" s="6"/>
+      <c r="CB72" s="6"/>
+      <c r="CC72" s="6"/>
+      <c r="CD72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6"/>
@@ -14788,6 +16019,10 @@
       <c r="BX73" s="6"/>
       <c r="BY73" s="6"/>
       <c r="BZ73" s="6"/>
+      <c r="CA73" s="6"/>
+      <c r="CB73" s="6"/>
+      <c r="CC73" s="6"/>
+      <c r="CD73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -14868,6 +16103,10 @@
       <c r="BX74" s="6"/>
       <c r="BY74" s="6"/>
       <c r="BZ74" s="6"/>
+      <c r="CA74" s="6"/>
+      <c r="CB74" s="6"/>
+      <c r="CC74" s="6"/>
+      <c r="CD74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6"/>
@@ -14948,6 +16187,10 @@
       <c r="BX75" s="6"/>
       <c r="BY75" s="6"/>
       <c r="BZ75" s="6"/>
+      <c r="CA75" s="6"/>
+      <c r="CB75" s="6"/>
+      <c r="CC75" s="6"/>
+      <c r="CD75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -15028,6 +16271,10 @@
       <c r="BX76" s="6"/>
       <c r="BY76" s="6"/>
       <c r="BZ76" s="6"/>
+      <c r="CA76" s="6"/>
+      <c r="CB76" s="6"/>
+      <c r="CC76" s="6"/>
+      <c r="CD76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6"/>
@@ -15108,6 +16355,10 @@
       <c r="BX77" s="6"/>
       <c r="BY77" s="6"/>
       <c r="BZ77" s="6"/>
+      <c r="CA77" s="6"/>
+      <c r="CB77" s="6"/>
+      <c r="CC77" s="6"/>
+      <c r="CD77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="6"/>
@@ -15188,6 +16439,10 @@
       <c r="BX78" s="6"/>
       <c r="BY78" s="6"/>
       <c r="BZ78" s="6"/>
+      <c r="CA78" s="6"/>
+      <c r="CB78" s="6"/>
+      <c r="CC78" s="6"/>
+      <c r="CD78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="6"/>
@@ -15268,6 +16523,10 @@
       <c r="BX79" s="6"/>
       <c r="BY79" s="6"/>
       <c r="BZ79" s="6"/>
+      <c r="CA79" s="6"/>
+      <c r="CB79" s="6"/>
+      <c r="CC79" s="6"/>
+      <c r="CD79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="6"/>
@@ -15348,6 +16607,10 @@
       <c r="BX80" s="6"/>
       <c r="BY80" s="6"/>
       <c r="BZ80" s="6"/>
+      <c r="CA80" s="6"/>
+      <c r="CB80" s="6"/>
+      <c r="CC80" s="6"/>
+      <c r="CD80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="6"/>
@@ -15428,6 +16691,10 @@
       <c r="BX81" s="6"/>
       <c r="BY81" s="6"/>
       <c r="BZ81" s="6"/>
+      <c r="CA81" s="6"/>
+      <c r="CB81" s="6"/>
+      <c r="CC81" s="6"/>
+      <c r="CD81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6"/>
@@ -15508,6 +16775,10 @@
       <c r="BX82" s="6"/>
       <c r="BY82" s="6"/>
       <c r="BZ82" s="6"/>
+      <c r="CA82" s="6"/>
+      <c r="CB82" s="6"/>
+      <c r="CC82" s="6"/>
+      <c r="CD82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="6"/>
@@ -15588,6 +16859,10 @@
       <c r="BX83" s="6"/>
       <c r="BY83" s="6"/>
       <c r="BZ83" s="6"/>
+      <c r="CA83" s="6"/>
+      <c r="CB83" s="6"/>
+      <c r="CC83" s="6"/>
+      <c r="CD83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6"/>
@@ -15668,6 +16943,10 @@
       <c r="BX84" s="6"/>
       <c r="BY84" s="6"/>
       <c r="BZ84" s="6"/>
+      <c r="CA84" s="6"/>
+      <c r="CB84" s="6"/>
+      <c r="CC84" s="6"/>
+      <c r="CD84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="6"/>
@@ -15748,6 +17027,10 @@
       <c r="BX85" s="6"/>
       <c r="BY85" s="6"/>
       <c r="BZ85" s="6"/>
+      <c r="CA85" s="6"/>
+      <c r="CB85" s="6"/>
+      <c r="CC85" s="6"/>
+      <c r="CD85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="6"/>
@@ -15828,6 +17111,10 @@
       <c r="BX86" s="6"/>
       <c r="BY86" s="6"/>
       <c r="BZ86" s="6"/>
+      <c r="CA86" s="6"/>
+      <c r="CB86" s="6"/>
+      <c r="CC86" s="6"/>
+      <c r="CD86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="6"/>
@@ -15908,6 +17195,10 @@
       <c r="BX87" s="6"/>
       <c r="BY87" s="6"/>
       <c r="BZ87" s="6"/>
+      <c r="CA87" s="6"/>
+      <c r="CB87" s="6"/>
+      <c r="CC87" s="6"/>
+      <c r="CD87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="6"/>
@@ -15988,6 +17279,10 @@
       <c r="BX88" s="6"/>
       <c r="BY88" s="6"/>
       <c r="BZ88" s="6"/>
+      <c r="CA88" s="6"/>
+      <c r="CB88" s="6"/>
+      <c r="CC88" s="6"/>
+      <c r="CD88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6"/>
@@ -16068,6 +17363,10 @@
       <c r="BX89" s="6"/>
       <c r="BY89" s="6"/>
       <c r="BZ89" s="6"/>
+      <c r="CA89" s="6"/>
+      <c r="CB89" s="6"/>
+      <c r="CC89" s="6"/>
+      <c r="CD89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="6"/>
@@ -16148,6 +17447,10 @@
       <c r="BX90" s="6"/>
       <c r="BY90" s="6"/>
       <c r="BZ90" s="6"/>
+      <c r="CA90" s="6"/>
+      <c r="CB90" s="6"/>
+      <c r="CC90" s="6"/>
+      <c r="CD90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6"/>
@@ -16228,6 +17531,10 @@
       <c r="BX91" s="6"/>
       <c r="BY91" s="6"/>
       <c r="BZ91" s="6"/>
+      <c r="CA91" s="6"/>
+      <c r="CB91" s="6"/>
+      <c r="CC91" s="6"/>
+      <c r="CD91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="6"/>
@@ -16308,6 +17615,10 @@
       <c r="BX92" s="6"/>
       <c r="BY92" s="6"/>
       <c r="BZ92" s="6"/>
+      <c r="CA92" s="6"/>
+      <c r="CB92" s="6"/>
+      <c r="CC92" s="6"/>
+      <c r="CD92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="6"/>
@@ -16388,6 +17699,10 @@
       <c r="BX93" s="6"/>
       <c r="BY93" s="6"/>
       <c r="BZ93" s="6"/>
+      <c r="CA93" s="6"/>
+      <c r="CB93" s="6"/>
+      <c r="CC93" s="6"/>
+      <c r="CD93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="6"/>
@@ -16468,6 +17783,10 @@
       <c r="BX94" s="6"/>
       <c r="BY94" s="6"/>
       <c r="BZ94" s="6"/>
+      <c r="CA94" s="6"/>
+      <c r="CB94" s="6"/>
+      <c r="CC94" s="6"/>
+      <c r="CD94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="6"/>
@@ -16548,6 +17867,10 @@
       <c r="BX95" s="6"/>
       <c r="BY95" s="6"/>
       <c r="BZ95" s="6"/>
+      <c r="CA95" s="6"/>
+      <c r="CB95" s="6"/>
+      <c r="CC95" s="6"/>
+      <c r="CD95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="6"/>
@@ -16628,6 +17951,10 @@
       <c r="BX96" s="6"/>
       <c r="BY96" s="6"/>
       <c r="BZ96" s="6"/>
+      <c r="CA96" s="6"/>
+      <c r="CB96" s="6"/>
+      <c r="CC96" s="6"/>
+      <c r="CD96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="6"/>
@@ -16708,6 +18035,10 @@
       <c r="BX97" s="6"/>
       <c r="BY97" s="6"/>
       <c r="BZ97" s="6"/>
+      <c r="CA97" s="6"/>
+      <c r="CB97" s="6"/>
+      <c r="CC97" s="6"/>
+      <c r="CD97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="6"/>
@@ -16788,6 +18119,10 @@
       <c r="BX98" s="6"/>
       <c r="BY98" s="6"/>
       <c r="BZ98" s="6"/>
+      <c r="CA98" s="6"/>
+      <c r="CB98" s="6"/>
+      <c r="CC98" s="6"/>
+      <c r="CD98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="6"/>
@@ -16868,6 +18203,10 @@
       <c r="BX99" s="6"/>
       <c r="BY99" s="6"/>
       <c r="BZ99" s="6"/>
+      <c r="CA99" s="6"/>
+      <c r="CB99" s="6"/>
+      <c r="CC99" s="6"/>
+      <c r="CD99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="6"/>
@@ -16948,6 +18287,10 @@
       <c r="BX100" s="6"/>
       <c r="BY100" s="6"/>
       <c r="BZ100" s="6"/>
+      <c r="CA100" s="6"/>
+      <c r="CB100" s="6"/>
+      <c r="CC100" s="6"/>
+      <c r="CD100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="6"/>
@@ -17028,6 +18371,10 @@
       <c r="BX101" s="6"/>
       <c r="BY101" s="6"/>
       <c r="BZ101" s="6"/>
+      <c r="CA101" s="6"/>
+      <c r="CB101" s="6"/>
+      <c r="CC101" s="6"/>
+      <c r="CD101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="6"/>
@@ -17108,6 +18455,10 @@
       <c r="BX102" s="6"/>
       <c r="BY102" s="6"/>
       <c r="BZ102" s="6"/>
+      <c r="CA102" s="6"/>
+      <c r="CB102" s="6"/>
+      <c r="CC102" s="6"/>
+      <c r="CD102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="6"/>
@@ -17188,6 +18539,10 @@
       <c r="BX103" s="6"/>
       <c r="BY103" s="6"/>
       <c r="BZ103" s="6"/>
+      <c r="CA103" s="6"/>
+      <c r="CB103" s="6"/>
+      <c r="CC103" s="6"/>
+      <c r="CD103" s="6"/>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6"/>
@@ -17268,6 +18623,10 @@
       <c r="BX104" s="6"/>
       <c r="BY104" s="6"/>
       <c r="BZ104" s="6"/>
+      <c r="CA104" s="6"/>
+      <c r="CB104" s="6"/>
+      <c r="CC104" s="6"/>
+      <c r="CD104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="6"/>
@@ -17348,6 +18707,10 @@
       <c r="BX105" s="6"/>
       <c r="BY105" s="6"/>
       <c r="BZ105" s="6"/>
+      <c r="CA105" s="6"/>
+      <c r="CB105" s="6"/>
+      <c r="CC105" s="6"/>
+      <c r="CD105" s="6"/>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="6"/>
@@ -17428,6 +18791,10 @@
       <c r="BX106" s="6"/>
       <c r="BY106" s="6"/>
       <c r="BZ106" s="6"/>
+      <c r="CA106" s="6"/>
+      <c r="CB106" s="6"/>
+      <c r="CC106" s="6"/>
+      <c r="CD106" s="6"/>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="6"/>
@@ -17508,6 +18875,10 @@
       <c r="BX107" s="6"/>
       <c r="BY107" s="6"/>
       <c r="BZ107" s="6"/>
+      <c r="CA107" s="6"/>
+      <c r="CB107" s="6"/>
+      <c r="CC107" s="6"/>
+      <c r="CD107" s="6"/>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="6"/>
@@ -17588,6 +18959,10 @@
       <c r="BX108" s="6"/>
       <c r="BY108" s="6"/>
       <c r="BZ108" s="6"/>
+      <c r="CA108" s="6"/>
+      <c r="CB108" s="6"/>
+      <c r="CC108" s="6"/>
+      <c r="CD108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="6"/>
@@ -17668,6 +19043,10 @@
       <c r="BX109" s="6"/>
       <c r="BY109" s="6"/>
       <c r="BZ109" s="6"/>
+      <c r="CA109" s="6"/>
+      <c r="CB109" s="6"/>
+      <c r="CC109" s="6"/>
+      <c r="CD109" s="6"/>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="6"/>
@@ -17748,6 +19127,10 @@
       <c r="BX110" s="6"/>
       <c r="BY110" s="6"/>
       <c r="BZ110" s="6"/>
+      <c r="CA110" s="6"/>
+      <c r="CB110" s="6"/>
+      <c r="CC110" s="6"/>
+      <c r="CD110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="6"/>
@@ -17828,6 +19211,10 @@
       <c r="BX111" s="6"/>
       <c r="BY111" s="6"/>
       <c r="BZ111" s="6"/>
+      <c r="CA111" s="6"/>
+      <c r="CB111" s="6"/>
+      <c r="CC111" s="6"/>
+      <c r="CD111" s="6"/>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6"/>
@@ -17908,6 +19295,10 @@
       <c r="BX112" s="6"/>
       <c r="BY112" s="6"/>
       <c r="BZ112" s="6"/>
+      <c r="CA112" s="6"/>
+      <c r="CB112" s="6"/>
+      <c r="CC112" s="6"/>
+      <c r="CD112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="6"/>
@@ -17988,6 +19379,10 @@
       <c r="BX113" s="6"/>
       <c r="BY113" s="6"/>
       <c r="BZ113" s="6"/>
+      <c r="CA113" s="6"/>
+      <c r="CB113" s="6"/>
+      <c r="CC113" s="6"/>
+      <c r="CD113" s="6"/>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6"/>
@@ -18068,6 +19463,10 @@
       <c r="BX114" s="6"/>
       <c r="BY114" s="6"/>
       <c r="BZ114" s="6"/>
+      <c r="CA114" s="6"/>
+      <c r="CB114" s="6"/>
+      <c r="CC114" s="6"/>
+      <c r="CD114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="6"/>
@@ -18148,6 +19547,10 @@
       <c r="BX115" s="6"/>
       <c r="BY115" s="6"/>
       <c r="BZ115" s="6"/>
+      <c r="CA115" s="6"/>
+      <c r="CB115" s="6"/>
+      <c r="CC115" s="6"/>
+      <c r="CD115" s="6"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6"/>
@@ -18228,6 +19631,10 @@
       <c r="BX116" s="6"/>
       <c r="BY116" s="6"/>
       <c r="BZ116" s="6"/>
+      <c r="CA116" s="6"/>
+      <c r="CB116" s="6"/>
+      <c r="CC116" s="6"/>
+      <c r="CD116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="6"/>
@@ -18308,6 +19715,10 @@
       <c r="BX117" s="6"/>
       <c r="BY117" s="6"/>
       <c r="BZ117" s="6"/>
+      <c r="CA117" s="6"/>
+      <c r="CB117" s="6"/>
+      <c r="CC117" s="6"/>
+      <c r="CD117" s="6"/>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="6"/>
@@ -18388,6 +19799,10 @@
       <c r="BX118" s="6"/>
       <c r="BY118" s="6"/>
       <c r="BZ118" s="6"/>
+      <c r="CA118" s="6"/>
+      <c r="CB118" s="6"/>
+      <c r="CC118" s="6"/>
+      <c r="CD118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="6"/>
@@ -18468,6 +19883,10 @@
       <c r="BX119" s="6"/>
       <c r="BY119" s="6"/>
       <c r="BZ119" s="6"/>
+      <c r="CA119" s="6"/>
+      <c r="CB119" s="6"/>
+      <c r="CC119" s="6"/>
+      <c r="CD119" s="6"/>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6"/>
@@ -18548,6 +19967,10 @@
       <c r="BX120" s="6"/>
       <c r="BY120" s="6"/>
       <c r="BZ120" s="6"/>
+      <c r="CA120" s="6"/>
+      <c r="CB120" s="6"/>
+      <c r="CC120" s="6"/>
+      <c r="CD120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="6"/>
@@ -18628,6 +20051,10 @@
       <c r="BX121" s="6"/>
       <c r="BY121" s="6"/>
       <c r="BZ121" s="6"/>
+      <c r="CA121" s="6"/>
+      <c r="CB121" s="6"/>
+      <c r="CC121" s="6"/>
+      <c r="CD121" s="6"/>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="6"/>
@@ -18708,6 +20135,10 @@
       <c r="BX122" s="6"/>
       <c r="BY122" s="6"/>
       <c r="BZ122" s="6"/>
+      <c r="CA122" s="6"/>
+      <c r="CB122" s="6"/>
+      <c r="CC122" s="6"/>
+      <c r="CD122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="6"/>
@@ -18788,6 +20219,10 @@
       <c r="BX123" s="6"/>
       <c r="BY123" s="6"/>
       <c r="BZ123" s="6"/>
+      <c r="CA123" s="6"/>
+      <c r="CB123" s="6"/>
+      <c r="CC123" s="6"/>
+      <c r="CD123" s="6"/>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6"/>
@@ -18868,6 +20303,10 @@
       <c r="BX124" s="6"/>
       <c r="BY124" s="6"/>
       <c r="BZ124" s="6"/>
+      <c r="CA124" s="6"/>
+      <c r="CB124" s="6"/>
+      <c r="CC124" s="6"/>
+      <c r="CD124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="6"/>
@@ -18948,6 +20387,10 @@
       <c r="BX125" s="6"/>
       <c r="BY125" s="6"/>
       <c r="BZ125" s="6"/>
+      <c r="CA125" s="6"/>
+      <c r="CB125" s="6"/>
+      <c r="CC125" s="6"/>
+      <c r="CD125" s="6"/>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6"/>
@@ -19028,6 +20471,10 @@
       <c r="BX126" s="6"/>
       <c r="BY126" s="6"/>
       <c r="BZ126" s="6"/>
+      <c r="CA126" s="6"/>
+      <c r="CB126" s="6"/>
+      <c r="CC126" s="6"/>
+      <c r="CD126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="6"/>
@@ -19108,6 +20555,10 @@
       <c r="BX127" s="6"/>
       <c r="BY127" s="6"/>
       <c r="BZ127" s="6"/>
+      <c r="CA127" s="6"/>
+      <c r="CB127" s="6"/>
+      <c r="CC127" s="6"/>
+      <c r="CD127" s="6"/>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6"/>
@@ -19188,6 +20639,10 @@
       <c r="BX128" s="6"/>
       <c r="BY128" s="6"/>
       <c r="BZ128" s="6"/>
+      <c r="CA128" s="6"/>
+      <c r="CB128" s="6"/>
+      <c r="CC128" s="6"/>
+      <c r="CD128" s="6"/>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="6"/>
@@ -19268,6 +20723,10 @@
       <c r="BX129" s="6"/>
       <c r="BY129" s="6"/>
       <c r="BZ129" s="6"/>
+      <c r="CA129" s="6"/>
+      <c r="CB129" s="6"/>
+      <c r="CC129" s="6"/>
+      <c r="CD129" s="6"/>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6"/>
@@ -19348,6 +20807,10 @@
       <c r="BX130" s="6"/>
       <c r="BY130" s="6"/>
       <c r="BZ130" s="6"/>
+      <c r="CA130" s="6"/>
+      <c r="CB130" s="6"/>
+      <c r="CC130" s="6"/>
+      <c r="CD130" s="6"/>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="6"/>
@@ -19428,6 +20891,10 @@
       <c r="BX131" s="6"/>
       <c r="BY131" s="6"/>
       <c r="BZ131" s="6"/>
+      <c r="CA131" s="6"/>
+      <c r="CB131" s="6"/>
+      <c r="CC131" s="6"/>
+      <c r="CD131" s="6"/>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6"/>
@@ -19508,6 +20975,10 @@
       <c r="BX132" s="6"/>
       <c r="BY132" s="6"/>
       <c r="BZ132" s="6"/>
+      <c r="CA132" s="6"/>
+      <c r="CB132" s="6"/>
+      <c r="CC132" s="6"/>
+      <c r="CD132" s="6"/>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="6"/>
@@ -19588,6 +21059,10 @@
       <c r="BX133" s="6"/>
       <c r="BY133" s="6"/>
       <c r="BZ133" s="6"/>
+      <c r="CA133" s="6"/>
+      <c r="CB133" s="6"/>
+      <c r="CC133" s="6"/>
+      <c r="CD133" s="6"/>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6"/>
@@ -19668,6 +21143,10 @@
       <c r="BX134" s="6"/>
       <c r="BY134" s="6"/>
       <c r="BZ134" s="6"/>
+      <c r="CA134" s="6"/>
+      <c r="CB134" s="6"/>
+      <c r="CC134" s="6"/>
+      <c r="CD134" s="6"/>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="6"/>
@@ -19748,6 +21227,10 @@
       <c r="BX135" s="6"/>
       <c r="BY135" s="6"/>
       <c r="BZ135" s="6"/>
+      <c r="CA135" s="6"/>
+      <c r="CB135" s="6"/>
+      <c r="CC135" s="6"/>
+      <c r="CD135" s="6"/>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6"/>
@@ -19828,6 +21311,10 @@
       <c r="BX136" s="6"/>
       <c r="BY136" s="6"/>
       <c r="BZ136" s="6"/>
+      <c r="CA136" s="6"/>
+      <c r="CB136" s="6"/>
+      <c r="CC136" s="6"/>
+      <c r="CD136" s="6"/>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="6"/>
@@ -19908,6 +21395,10 @@
       <c r="BX137" s="6"/>
       <c r="BY137" s="6"/>
       <c r="BZ137" s="6"/>
+      <c r="CA137" s="6"/>
+      <c r="CB137" s="6"/>
+      <c r="CC137" s="6"/>
+      <c r="CD137" s="6"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6"/>
@@ -19988,6 +21479,10 @@
       <c r="BX138" s="6"/>
       <c r="BY138" s="6"/>
       <c r="BZ138" s="6"/>
+      <c r="CA138" s="6"/>
+      <c r="CB138" s="6"/>
+      <c r="CC138" s="6"/>
+      <c r="CD138" s="6"/>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="6"/>
@@ -20068,6 +21563,10 @@
       <c r="BX139" s="6"/>
       <c r="BY139" s="6"/>
       <c r="BZ139" s="6"/>
+      <c r="CA139" s="6"/>
+      <c r="CB139" s="6"/>
+      <c r="CC139" s="6"/>
+      <c r="CD139" s="6"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6"/>
@@ -20148,6 +21647,10 @@
       <c r="BX140" s="6"/>
       <c r="BY140" s="6"/>
       <c r="BZ140" s="6"/>
+      <c r="CA140" s="6"/>
+      <c r="CB140" s="6"/>
+      <c r="CC140" s="6"/>
+      <c r="CD140" s="6"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="6"/>
@@ -20228,6 +21731,10 @@
       <c r="BX141" s="6"/>
       <c r="BY141" s="6"/>
       <c r="BZ141" s="6"/>
+      <c r="CA141" s="6"/>
+      <c r="CB141" s="6"/>
+      <c r="CC141" s="6"/>
+      <c r="CD141" s="6"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6"/>
@@ -20308,6 +21815,10 @@
       <c r="BX142" s="6"/>
       <c r="BY142" s="6"/>
       <c r="BZ142" s="6"/>
+      <c r="CA142" s="6"/>
+      <c r="CB142" s="6"/>
+      <c r="CC142" s="6"/>
+      <c r="CD142" s="6"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="6"/>
@@ -20388,6 +21899,10 @@
       <c r="BX143" s="6"/>
       <c r="BY143" s="6"/>
       <c r="BZ143" s="6"/>
+      <c r="CA143" s="6"/>
+      <c r="CB143" s="6"/>
+      <c r="CC143" s="6"/>
+      <c r="CD143" s="6"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6"/>
@@ -20468,6 +21983,10 @@
       <c r="BX144" s="6"/>
       <c r="BY144" s="6"/>
       <c r="BZ144" s="6"/>
+      <c r="CA144" s="6"/>
+      <c r="CB144" s="6"/>
+      <c r="CC144" s="6"/>
+      <c r="CD144" s="6"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="6"/>
@@ -20548,6 +22067,10 @@
       <c r="BX145" s="6"/>
       <c r="BY145" s="6"/>
       <c r="BZ145" s="6"/>
+      <c r="CA145" s="6"/>
+      <c r="CB145" s="6"/>
+      <c r="CC145" s="6"/>
+      <c r="CD145" s="6"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6"/>
@@ -20628,6 +22151,10 @@
       <c r="BX146" s="6"/>
       <c r="BY146" s="6"/>
       <c r="BZ146" s="6"/>
+      <c r="CA146" s="6"/>
+      <c r="CB146" s="6"/>
+      <c r="CC146" s="6"/>
+      <c r="CD146" s="6"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="6"/>
@@ -20708,6 +22235,10 @@
       <c r="BX147" s="6"/>
       <c r="BY147" s="6"/>
       <c r="BZ147" s="6"/>
+      <c r="CA147" s="6"/>
+      <c r="CB147" s="6"/>
+      <c r="CC147" s="6"/>
+      <c r="CD147" s="6"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6"/>
@@ -20788,6 +22319,10 @@
       <c r="BX148" s="6"/>
       <c r="BY148" s="6"/>
       <c r="BZ148" s="6"/>
+      <c r="CA148" s="6"/>
+      <c r="CB148" s="6"/>
+      <c r="CC148" s="6"/>
+      <c r="CD148" s="6"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="6"/>
@@ -20868,6 +22403,10 @@
       <c r="BX149" s="6"/>
       <c r="BY149" s="6"/>
       <c r="BZ149" s="6"/>
+      <c r="CA149" s="6"/>
+      <c r="CB149" s="6"/>
+      <c r="CC149" s="6"/>
+      <c r="CD149" s="6"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6"/>
@@ -20948,6 +22487,10 @@
       <c r="BX150" s="6"/>
       <c r="BY150" s="6"/>
       <c r="BZ150" s="6"/>
+      <c r="CA150" s="6"/>
+      <c r="CB150" s="6"/>
+      <c r="CC150" s="6"/>
+      <c r="CD150" s="6"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="6"/>
@@ -21028,6 +22571,10 @@
       <c r="BX151" s="6"/>
       <c r="BY151" s="6"/>
       <c r="BZ151" s="6"/>
+      <c r="CA151" s="6"/>
+      <c r="CB151" s="6"/>
+      <c r="CC151" s="6"/>
+      <c r="CD151" s="6"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6"/>
@@ -21108,6 +22655,10 @@
       <c r="BX152" s="6"/>
       <c r="BY152" s="6"/>
       <c r="BZ152" s="6"/>
+      <c r="CA152" s="6"/>
+      <c r="CB152" s="6"/>
+      <c r="CC152" s="6"/>
+      <c r="CD152" s="6"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="6"/>
@@ -21188,6 +22739,10 @@
       <c r="BX153" s="6"/>
       <c r="BY153" s="6"/>
       <c r="BZ153" s="6"/>
+      <c r="CA153" s="6"/>
+      <c r="CB153" s="6"/>
+      <c r="CC153" s="6"/>
+      <c r="CD153" s="6"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6"/>
@@ -21268,6 +22823,10 @@
       <c r="BX154" s="6"/>
       <c r="BY154" s="6"/>
       <c r="BZ154" s="6"/>
+      <c r="CA154" s="6"/>
+      <c r="CB154" s="6"/>
+      <c r="CC154" s="6"/>
+      <c r="CD154" s="6"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="6"/>
@@ -21348,6 +22907,10 @@
       <c r="BX155" s="6"/>
       <c r="BY155" s="6"/>
       <c r="BZ155" s="6"/>
+      <c r="CA155" s="6"/>
+      <c r="CB155" s="6"/>
+      <c r="CC155" s="6"/>
+      <c r="CD155" s="6"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6"/>
@@ -21428,6 +22991,10 @@
       <c r="BX156" s="6"/>
       <c r="BY156" s="6"/>
       <c r="BZ156" s="6"/>
+      <c r="CA156" s="6"/>
+      <c r="CB156" s="6"/>
+      <c r="CC156" s="6"/>
+      <c r="CD156" s="6"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="6"/>
@@ -21508,6 +23075,10 @@
       <c r="BX157" s="6"/>
       <c r="BY157" s="6"/>
       <c r="BZ157" s="6"/>
+      <c r="CA157" s="6"/>
+      <c r="CB157" s="6"/>
+      <c r="CC157" s="6"/>
+      <c r="CD157" s="6"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6"/>
@@ -21588,6 +23159,10 @@
       <c r="BX158" s="6"/>
       <c r="BY158" s="6"/>
       <c r="BZ158" s="6"/>
+      <c r="CA158" s="6"/>
+      <c r="CB158" s="6"/>
+      <c r="CC158" s="6"/>
+      <c r="CD158" s="6"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="6"/>
@@ -21668,6 +23243,10 @@
       <c r="BX159" s="6"/>
       <c r="BY159" s="6"/>
       <c r="BZ159" s="6"/>
+      <c r="CA159" s="6"/>
+      <c r="CB159" s="6"/>
+      <c r="CC159" s="6"/>
+      <c r="CD159" s="6"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6"/>
@@ -21748,6 +23327,10 @@
       <c r="BX160" s="6"/>
       <c r="BY160" s="6"/>
       <c r="BZ160" s="6"/>
+      <c r="CA160" s="6"/>
+      <c r="CB160" s="6"/>
+      <c r="CC160" s="6"/>
+      <c r="CD160" s="6"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="6"/>
@@ -21828,6 +23411,10 @@
       <c r="BX161" s="6"/>
       <c r="BY161" s="6"/>
       <c r="BZ161" s="6"/>
+      <c r="CA161" s="6"/>
+      <c r="CB161" s="6"/>
+      <c r="CC161" s="6"/>
+      <c r="CD161" s="6"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6"/>
@@ -21908,6 +23495,10 @@
       <c r="BX162" s="6"/>
       <c r="BY162" s="6"/>
       <c r="BZ162" s="6"/>
+      <c r="CA162" s="6"/>
+      <c r="CB162" s="6"/>
+      <c r="CC162" s="6"/>
+      <c r="CD162" s="6"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="6"/>
@@ -21988,6 +23579,10 @@
       <c r="BX163" s="6"/>
       <c r="BY163" s="6"/>
       <c r="BZ163" s="6"/>
+      <c r="CA163" s="6"/>
+      <c r="CB163" s="6"/>
+      <c r="CC163" s="6"/>
+      <c r="CD163" s="6"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6"/>
@@ -22068,6 +23663,10 @@
       <c r="BX164" s="6"/>
       <c r="BY164" s="6"/>
       <c r="BZ164" s="6"/>
+      <c r="CA164" s="6"/>
+      <c r="CB164" s="6"/>
+      <c r="CC164" s="6"/>
+      <c r="CD164" s="6"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="6"/>
@@ -22148,6 +23747,10 @@
       <c r="BX165" s="6"/>
       <c r="BY165" s="6"/>
       <c r="BZ165" s="6"/>
+      <c r="CA165" s="6"/>
+      <c r="CB165" s="6"/>
+      <c r="CC165" s="6"/>
+      <c r="CD165" s="6"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6"/>
@@ -22228,6 +23831,10 @@
       <c r="BX166" s="6"/>
       <c r="BY166" s="6"/>
       <c r="BZ166" s="6"/>
+      <c r="CA166" s="6"/>
+      <c r="CB166" s="6"/>
+      <c r="CC166" s="6"/>
+      <c r="CD166" s="6"/>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="6"/>
@@ -22308,6 +23915,10 @@
       <c r="BX167" s="6"/>
       <c r="BY167" s="6"/>
       <c r="BZ167" s="6"/>
+      <c r="CA167" s="6"/>
+      <c r="CB167" s="6"/>
+      <c r="CC167" s="6"/>
+      <c r="CD167" s="6"/>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6"/>
@@ -22388,6 +23999,10 @@
       <c r="BX168" s="6"/>
       <c r="BY168" s="6"/>
       <c r="BZ168" s="6"/>
+      <c r="CA168" s="6"/>
+      <c r="CB168" s="6"/>
+      <c r="CC168" s="6"/>
+      <c r="CD168" s="6"/>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="6"/>
@@ -22468,6 +24083,10 @@
       <c r="BX169" s="6"/>
       <c r="BY169" s="6"/>
       <c r="BZ169" s="6"/>
+      <c r="CA169" s="6"/>
+      <c r="CB169" s="6"/>
+      <c r="CC169" s="6"/>
+      <c r="CD169" s="6"/>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6"/>
@@ -22548,6 +24167,10 @@
       <c r="BX170" s="6"/>
       <c r="BY170" s="6"/>
       <c r="BZ170" s="6"/>
+      <c r="CA170" s="6"/>
+      <c r="CB170" s="6"/>
+      <c r="CC170" s="6"/>
+      <c r="CD170" s="6"/>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="6"/>
@@ -22628,6 +24251,10 @@
       <c r="BX171" s="6"/>
       <c r="BY171" s="6"/>
       <c r="BZ171" s="6"/>
+      <c r="CA171" s="6"/>
+      <c r="CB171" s="6"/>
+      <c r="CC171" s="6"/>
+      <c r="CD171" s="6"/>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6"/>
@@ -22708,6 +24335,10 @@
       <c r="BX172" s="6"/>
       <c r="BY172" s="6"/>
       <c r="BZ172" s="6"/>
+      <c r="CA172" s="6"/>
+      <c r="CB172" s="6"/>
+      <c r="CC172" s="6"/>
+      <c r="CD172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="6"/>
@@ -22788,6 +24419,10 @@
       <c r="BX173" s="6"/>
       <c r="BY173" s="6"/>
       <c r="BZ173" s="6"/>
+      <c r="CA173" s="6"/>
+      <c r="CB173" s="6"/>
+      <c r="CC173" s="6"/>
+      <c r="CD173" s="6"/>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6"/>
@@ -22868,6 +24503,10 @@
       <c r="BX174" s="6"/>
       <c r="BY174" s="6"/>
       <c r="BZ174" s="6"/>
+      <c r="CA174" s="6"/>
+      <c r="CB174" s="6"/>
+      <c r="CC174" s="6"/>
+      <c r="CD174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="6"/>
@@ -22948,6 +24587,10 @@
       <c r="BX175" s="6"/>
       <c r="BY175" s="6"/>
       <c r="BZ175" s="6"/>
+      <c r="CA175" s="6"/>
+      <c r="CB175" s="6"/>
+      <c r="CC175" s="6"/>
+      <c r="CD175" s="6"/>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6"/>
@@ -23028,6 +24671,10 @@
       <c r="BX176" s="6"/>
       <c r="BY176" s="6"/>
       <c r="BZ176" s="6"/>
+      <c r="CA176" s="6"/>
+      <c r="CB176" s="6"/>
+      <c r="CC176" s="6"/>
+      <c r="CD176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="6"/>
@@ -23108,6 +24755,10 @@
       <c r="BX177" s="6"/>
       <c r="BY177" s="6"/>
       <c r="BZ177" s="6"/>
+      <c r="CA177" s="6"/>
+      <c r="CB177" s="6"/>
+      <c r="CC177" s="6"/>
+      <c r="CD177" s="6"/>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6"/>
@@ -23188,6 +24839,10 @@
       <c r="BX178" s="6"/>
       <c r="BY178" s="6"/>
       <c r="BZ178" s="6"/>
+      <c r="CA178" s="6"/>
+      <c r="CB178" s="6"/>
+      <c r="CC178" s="6"/>
+      <c r="CD178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="6"/>
@@ -23268,6 +24923,10 @@
       <c r="BX179" s="6"/>
       <c r="BY179" s="6"/>
       <c r="BZ179" s="6"/>
+      <c r="CA179" s="6"/>
+      <c r="CB179" s="6"/>
+      <c r="CC179" s="6"/>
+      <c r="CD179" s="6"/>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6"/>
@@ -23348,6 +25007,10 @@
       <c r="BX180" s="6"/>
       <c r="BY180" s="6"/>
       <c r="BZ180" s="6"/>
+      <c r="CA180" s="6"/>
+      <c r="CB180" s="6"/>
+      <c r="CC180" s="6"/>
+      <c r="CD180" s="6"/>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="6"/>
@@ -23428,6 +25091,10 @@
       <c r="BX181" s="6"/>
       <c r="BY181" s="6"/>
       <c r="BZ181" s="6"/>
+      <c r="CA181" s="6"/>
+      <c r="CB181" s="6"/>
+      <c r="CC181" s="6"/>
+      <c r="CD181" s="6"/>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6"/>
@@ -23508,6 +25175,10 @@
       <c r="BX182" s="6"/>
       <c r="BY182" s="6"/>
       <c r="BZ182" s="6"/>
+      <c r="CA182" s="6"/>
+      <c r="CB182" s="6"/>
+      <c r="CC182" s="6"/>
+      <c r="CD182" s="6"/>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="6"/>
@@ -23588,6 +25259,10 @@
       <c r="BX183" s="6"/>
       <c r="BY183" s="6"/>
       <c r="BZ183" s="6"/>
+      <c r="CA183" s="6"/>
+      <c r="CB183" s="6"/>
+      <c r="CC183" s="6"/>
+      <c r="CD183" s="6"/>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6"/>
@@ -23668,6 +25343,10 @@
       <c r="BX184" s="6"/>
       <c r="BY184" s="6"/>
       <c r="BZ184" s="6"/>
+      <c r="CA184" s="6"/>
+      <c r="CB184" s="6"/>
+      <c r="CC184" s="6"/>
+      <c r="CD184" s="6"/>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="6"/>
@@ -23748,6 +25427,10 @@
       <c r="BX185" s="6"/>
       <c r="BY185" s="6"/>
       <c r="BZ185" s="6"/>
+      <c r="CA185" s="6"/>
+      <c r="CB185" s="6"/>
+      <c r="CC185" s="6"/>
+      <c r="CD185" s="6"/>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6"/>
@@ -23828,6 +25511,10 @@
       <c r="BX186" s="6"/>
       <c r="BY186" s="6"/>
       <c r="BZ186" s="6"/>
+      <c r="CA186" s="6"/>
+      <c r="CB186" s="6"/>
+      <c r="CC186" s="6"/>
+      <c r="CD186" s="6"/>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="6"/>
@@ -23908,6 +25595,10 @@
       <c r="BX187" s="6"/>
       <c r="BY187" s="6"/>
       <c r="BZ187" s="6"/>
+      <c r="CA187" s="6"/>
+      <c r="CB187" s="6"/>
+      <c r="CC187" s="6"/>
+      <c r="CD187" s="6"/>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6"/>
@@ -23988,6 +25679,10 @@
       <c r="BX188" s="6"/>
       <c r="BY188" s="6"/>
       <c r="BZ188" s="6"/>
+      <c r="CA188" s="6"/>
+      <c r="CB188" s="6"/>
+      <c r="CC188" s="6"/>
+      <c r="CD188" s="6"/>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="6"/>
@@ -24068,6 +25763,10 @@
       <c r="BX189" s="6"/>
       <c r="BY189" s="6"/>
       <c r="BZ189" s="6"/>
+      <c r="CA189" s="6"/>
+      <c r="CB189" s="6"/>
+      <c r="CC189" s="6"/>
+      <c r="CD189" s="6"/>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6"/>
@@ -24148,6 +25847,10 @@
       <c r="BX190" s="6"/>
       <c r="BY190" s="6"/>
       <c r="BZ190" s="6"/>
+      <c r="CA190" s="6"/>
+      <c r="CB190" s="6"/>
+      <c r="CC190" s="6"/>
+      <c r="CD190" s="6"/>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="6"/>
@@ -24228,6 +25931,10 @@
       <c r="BX191" s="6"/>
       <c r="BY191" s="6"/>
       <c r="BZ191" s="6"/>
+      <c r="CA191" s="6"/>
+      <c r="CB191" s="6"/>
+      <c r="CC191" s="6"/>
+      <c r="CD191" s="6"/>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6"/>
@@ -24308,6 +26015,10 @@
       <c r="BX192" s="6"/>
       <c r="BY192" s="6"/>
       <c r="BZ192" s="6"/>
+      <c r="CA192" s="6"/>
+      <c r="CB192" s="6"/>
+      <c r="CC192" s="6"/>
+      <c r="CD192" s="6"/>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="6"/>
@@ -24388,6 +26099,10 @@
       <c r="BX193" s="6"/>
       <c r="BY193" s="6"/>
       <c r="BZ193" s="6"/>
+      <c r="CA193" s="6"/>
+      <c r="CB193" s="6"/>
+      <c r="CC193" s="6"/>
+      <c r="CD193" s="6"/>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6"/>
@@ -24468,6 +26183,10 @@
       <c r="BX194" s="6"/>
       <c r="BY194" s="6"/>
       <c r="BZ194" s="6"/>
+      <c r="CA194" s="6"/>
+      <c r="CB194" s="6"/>
+      <c r="CC194" s="6"/>
+      <c r="CD194" s="6"/>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="6"/>
@@ -24548,6 +26267,10 @@
       <c r="BX195" s="6"/>
       <c r="BY195" s="6"/>
       <c r="BZ195" s="6"/>
+      <c r="CA195" s="6"/>
+      <c r="CB195" s="6"/>
+      <c r="CC195" s="6"/>
+      <c r="CD195" s="6"/>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="6"/>
@@ -24628,6 +26351,10 @@
       <c r="BX196" s="6"/>
       <c r="BY196" s="6"/>
       <c r="BZ196" s="6"/>
+      <c r="CA196" s="6"/>
+      <c r="CB196" s="6"/>
+      <c r="CC196" s="6"/>
+      <c r="CD196" s="6"/>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="6"/>
@@ -24708,6 +26435,10 @@
       <c r="BX197" s="6"/>
       <c r="BY197" s="6"/>
       <c r="BZ197" s="6"/>
+      <c r="CA197" s="6"/>
+      <c r="CB197" s="6"/>
+      <c r="CC197" s="6"/>
+      <c r="CD197" s="6"/>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="6"/>
@@ -24788,6 +26519,10 @@
       <c r="BX198" s="6"/>
       <c r="BY198" s="6"/>
       <c r="BZ198" s="6"/>
+      <c r="CA198" s="6"/>
+      <c r="CB198" s="6"/>
+      <c r="CC198" s="6"/>
+      <c r="CD198" s="6"/>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="6"/>
@@ -24868,6 +26603,10 @@
       <c r="BX199" s="6"/>
       <c r="BY199" s="6"/>
       <c r="BZ199" s="6"/>
+      <c r="CA199" s="6"/>
+      <c r="CB199" s="6"/>
+      <c r="CC199" s="6"/>
+      <c r="CD199" s="6"/>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="6"/>
@@ -24948,6 +26687,10 @@
       <c r="BX200" s="6"/>
       <c r="BY200" s="6"/>
       <c r="BZ200" s="6"/>
+      <c r="CA200" s="6"/>
+      <c r="CB200" s="6"/>
+      <c r="CC200" s="6"/>
+      <c r="CD200" s="6"/>
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="6"/>
@@ -25028,6 +26771,10 @@
       <c r="BX201" s="6"/>
       <c r="BY201" s="6"/>
       <c r="BZ201" s="6"/>
+      <c r="CA201" s="6"/>
+      <c r="CB201" s="6"/>
+      <c r="CC201" s="6"/>
+      <c r="CD201" s="6"/>
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="6"/>
@@ -25108,6 +26855,10 @@
       <c r="BX202" s="6"/>
       <c r="BY202" s="6"/>
       <c r="BZ202" s="6"/>
+      <c r="CA202" s="6"/>
+      <c r="CB202" s="6"/>
+      <c r="CC202" s="6"/>
+      <c r="CD202" s="6"/>
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="6"/>
@@ -25188,6 +26939,10 @@
       <c r="BX203" s="6"/>
       <c r="BY203" s="6"/>
       <c r="BZ203" s="6"/>
+      <c r="CA203" s="6"/>
+      <c r="CB203" s="6"/>
+      <c r="CC203" s="6"/>
+      <c r="CD203" s="6"/>
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="6"/>
@@ -25268,6 +27023,10 @@
       <c r="BX204" s="6"/>
       <c r="BY204" s="6"/>
       <c r="BZ204" s="6"/>
+      <c r="CA204" s="6"/>
+      <c r="CB204" s="6"/>
+      <c r="CC204" s="6"/>
+      <c r="CD204" s="6"/>
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="6"/>
@@ -25348,6 +27107,10 @@
       <c r="BX205" s="6"/>
       <c r="BY205" s="6"/>
       <c r="BZ205" s="6"/>
+      <c r="CA205" s="6"/>
+      <c r="CB205" s="6"/>
+      <c r="CC205" s="6"/>
+      <c r="CD205" s="6"/>
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="6"/>
@@ -25428,6 +27191,10 @@
       <c r="BX206" s="6"/>
       <c r="BY206" s="6"/>
       <c r="BZ206" s="6"/>
+      <c r="CA206" s="6"/>
+      <c r="CB206" s="6"/>
+      <c r="CC206" s="6"/>
+      <c r="CD206" s="6"/>
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="6"/>
@@ -25508,6 +27275,10 @@
       <c r="BX207" s="6"/>
       <c r="BY207" s="6"/>
       <c r="BZ207" s="6"/>
+      <c r="CA207" s="6"/>
+      <c r="CB207" s="6"/>
+      <c r="CC207" s="6"/>
+      <c r="CD207" s="6"/>
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="6"/>
@@ -25588,6 +27359,10 @@
       <c r="BX208" s="6"/>
       <c r="BY208" s="6"/>
       <c r="BZ208" s="6"/>
+      <c r="CA208" s="6"/>
+      <c r="CB208" s="6"/>
+      <c r="CC208" s="6"/>
+      <c r="CD208" s="6"/>
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="6"/>
@@ -25668,6 +27443,10 @@
       <c r="BX209" s="6"/>
       <c r="BY209" s="6"/>
       <c r="BZ209" s="6"/>
+      <c r="CA209" s="6"/>
+      <c r="CB209" s="6"/>
+      <c r="CC209" s="6"/>
+      <c r="CD209" s="6"/>
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="6"/>
@@ -25748,6 +27527,10 @@
       <c r="BX210" s="6"/>
       <c r="BY210" s="6"/>
       <c r="BZ210" s="6"/>
+      <c r="CA210" s="6"/>
+      <c r="CB210" s="6"/>
+      <c r="CC210" s="6"/>
+      <c r="CD210" s="6"/>
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="6"/>
@@ -25828,6 +27611,10 @@
       <c r="BX211" s="6"/>
       <c r="BY211" s="6"/>
       <c r="BZ211" s="6"/>
+      <c r="CA211" s="6"/>
+      <c r="CB211" s="6"/>
+      <c r="CC211" s="6"/>
+      <c r="CD211" s="6"/>
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6"/>
@@ -25908,6 +27695,10 @@
       <c r="BX212" s="6"/>
       <c r="BY212" s="6"/>
       <c r="BZ212" s="6"/>
+      <c r="CA212" s="6"/>
+      <c r="CB212" s="6"/>
+      <c r="CC212" s="6"/>
+      <c r="CD212" s="6"/>
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="6"/>
@@ -25988,6 +27779,10 @@
       <c r="BX213" s="6"/>
       <c r="BY213" s="6"/>
       <c r="BZ213" s="6"/>
+      <c r="CA213" s="6"/>
+      <c r="CB213" s="6"/>
+      <c r="CC213" s="6"/>
+      <c r="CD213" s="6"/>
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6"/>
@@ -26068,6 +27863,10 @@
       <c r="BX214" s="6"/>
       <c r="BY214" s="6"/>
       <c r="BZ214" s="6"/>
+      <c r="CA214" s="6"/>
+      <c r="CB214" s="6"/>
+      <c r="CC214" s="6"/>
+      <c r="CD214" s="6"/>
     </row>
     <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="6"/>
@@ -26148,6 +27947,10 @@
       <c r="BX215" s="6"/>
       <c r="BY215" s="6"/>
       <c r="BZ215" s="6"/>
+      <c r="CA215" s="6"/>
+      <c r="CB215" s="6"/>
+      <c r="CC215" s="6"/>
+      <c r="CD215" s="6"/>
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="6"/>
@@ -26228,6 +28031,10 @@
       <c r="BX216" s="6"/>
       <c r="BY216" s="6"/>
       <c r="BZ216" s="6"/>
+      <c r="CA216" s="6"/>
+      <c r="CB216" s="6"/>
+      <c r="CC216" s="6"/>
+      <c r="CD216" s="6"/>
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="6"/>
@@ -26308,6 +28115,10 @@
       <c r="BX217" s="6"/>
       <c r="BY217" s="6"/>
       <c r="BZ217" s="6"/>
+      <c r="CA217" s="6"/>
+      <c r="CB217" s="6"/>
+      <c r="CC217" s="6"/>
+      <c r="CD217" s="6"/>
     </row>
     <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="6"/>
@@ -26388,6 +28199,10 @@
       <c r="BX218" s="6"/>
       <c r="BY218" s="6"/>
       <c r="BZ218" s="6"/>
+      <c r="CA218" s="6"/>
+      <c r="CB218" s="6"/>
+      <c r="CC218" s="6"/>
+      <c r="CD218" s="6"/>
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="6"/>
@@ -26468,6 +28283,10 @@
       <c r="BX219" s="6"/>
       <c r="BY219" s="6"/>
       <c r="BZ219" s="6"/>
+      <c r="CA219" s="6"/>
+      <c r="CB219" s="6"/>
+      <c r="CC219" s="6"/>
+      <c r="CD219" s="6"/>
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="6"/>
@@ -26548,6 +28367,10 @@
       <c r="BX220" s="6"/>
       <c r="BY220" s="6"/>
       <c r="BZ220" s="6"/>
+      <c r="CA220" s="6"/>
+      <c r="CB220" s="6"/>
+      <c r="CC220" s="6"/>
+      <c r="CD220" s="6"/>
     </row>
     <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_tone.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_tone.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1151">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -205,6 +205,9 @@
     <t xml:space="preserve">봐</t>
   </si>
   <si>
+    <t xml:space="preserve">야</t>
+  </si>
+  <si>
     <t xml:space="preserve">이야</t>
   </si>
   <si>
@@ -293,6 +296,12 @@
   </si>
   <si>
     <t xml:space="preserve">어울려</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">들</t>
   </si>
   <si>
     <t xml:space="preserve">default</t>
@@ -599,6 +608,10 @@
   <si>
     <t xml:space="preserve">보세요,보십시오
 보세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">입니까,예요
+예요</t>
   </si>
   <si>
     <t xml:space="preserve">입니까,이에요</t>
@@ -818,6 +831,13 @@
 어울려요</t>
   </si>
   <si>
+    <t xml:space="preserve">입니다
+예요,랍니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">님들, 여러분</t>
+  </si>
+  <si>
     <t xml:space="preserve">rude</t>
   </si>
   <si>
@@ -945,6 +965,9 @@
   </si>
   <si>
     <t xml:space="preserve">봐,봐봐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야,냐</t>
   </si>
   <si>
     <t xml:space="preserve">이야,이냐</t>
@@ -1188,6 +1211,15 @@
 어울려</t>
   </si>
   <si>
+    <t xml:space="preserve">야,다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그래,응</t>
+  </si>
+  <si>
+    <t xml:space="preserve">들,들아</t>
+  </si>
+  <si>
     <t xml:space="preserve">friendly</t>
   </si>
   <si>
@@ -1474,6 +1506,13 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">야,예요
+야,예요,랍니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">응,그래</t>
+  </si>
+  <si>
     <t xml:space="preserve">shy</t>
   </si>
   <si>
@@ -1908,6 +1947,28 @@
   </si>
   <si>
     <t xml:space="preserve">봐…</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">이야…</t>
@@ -2412,6 +2473,53 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">야,예요</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">응</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">…</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">VIP</t>
   </si>
   <si>
@@ -2548,6 +2656,9 @@
   </si>
   <si>
     <t xml:space="preserve">것이냐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냐</t>
   </si>
   <si>
     <t xml:space="preserve">이냐</t>
@@ -2763,7 +2874,7 @@
     <t xml:space="preserve">낳거라</t>
   </si>
   <si>
-    <t xml:space="preserve">두렵도다</t>
+    <t xml:space="preserve">두렵도다,두렵구나</t>
   </si>
   <si>
     <t xml:space="preserve">기쁘구나,매우 기쁘구나,참으로 기쁘구나</t>
@@ -2776,6 +2887,12 @@
   </si>
   <si>
     <t xml:space="preserve">어울리는구나,어울리도다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이니라,다,로다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">들이여</t>
   </si>
   <si>
     <t xml:space="preserve">bushi</t>
@@ -3004,6 +3121,10 @@
   <si>
     <t xml:space="preserve">보시오
 보십시오</t>
+  </si>
+  <si>
+    <t xml:space="preserve">오
+입니까</t>
   </si>
   <si>
     <t xml:space="preserve">이오
@@ -3167,6 +3288,18 @@
 어울리옵니다</t>
   </si>
   <si>
+    <t xml:space="preserve">라오,요
+이옵니다,랍니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그렇소,그러하오
+그렇사옵니다,그러하옵니다</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 나리들
+여러분</t>
+  </si>
+  <si>
     <t xml:space="preserve">su</t>
   </si>
   <si>
@@ -3404,6 +3537,12 @@
   </si>
   <si>
     <t xml:space="preserve">어울림다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">임다,람다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">맞슴다,그렇슴다</t>
   </si>
   <si>
     <t xml:space="preserve">cat</t>
@@ -4074,6 +4213,9 @@
       </rPr>
       <t xml:space="preserve">앙</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">냥,냐-앙,먀</t>
   </si>
   <si>
     <r>
@@ -4706,6 +4848,12 @@
     <t xml:space="preserve">어울려냐,어울린다냐-</t>
   </si>
   <si>
+    <t xml:space="preserve">다냐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그래냐</t>
+  </si>
+  <si>
     <t xml:space="preserve">nano</t>
   </si>
   <si>
@@ -4893,6 +5041,12 @@
   </si>
   <si>
     <t xml:space="preserve">어울리는 것이에요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예요,인 것이에요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네,네에</t>
   </si>
   <si>
     <t xml:space="preserve">noble</t>
@@ -5075,6 +5229,10 @@
   <si>
     <t xml:space="preserve">보십시오
 보시와요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">입니까
+예요</t>
   </si>
   <si>
     <t xml:space="preserve">입니까
@@ -5233,6 +5391,14 @@
 어울리어요</t>
   </si>
   <si>
+    <t xml:space="preserve">예
+네,네에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">여러분
+님들,들, 여러분</t>
+  </si>
+  <si>
     <t xml:space="preserve">peko</t>
   </si>
   <si>
@@ -5396,6 +5562,9 @@
   </si>
   <si>
     <t xml:space="preserve">페코봐라,봐페코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">페코,야페코</t>
   </si>
   <si>
     <t xml:space="preserve">이페코,이야페코</t>
@@ -5517,6 +5686,12 @@
     <t xml:space="preserve">어울려페코</t>
   </si>
   <si>
+    <t xml:space="preserve">다페코</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그래페코</t>
+  </si>
+  <si>
     <t xml:space="preserve">VIP2</t>
   </si>
   <si>
@@ -5780,6 +5955,12 @@
     <t xml:space="preserve">어울려요</t>
   </si>
   <si>
+    <t xml:space="preserve">녜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">님들</t>
+  </si>
+  <si>
     <t xml:space="preserve">princess</t>
   </si>
   <si>
@@ -5896,6 +6077,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">응</t>
+  </si>
+  <si>
     <t xml:space="preserve">nyu</t>
   </si>
   <si>
@@ -6050,6 +6234,9 @@
   </si>
   <si>
     <t xml:space="preserve">봐라뉴-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야뉴</t>
   </si>
   <si>
     <t xml:space="preserve">이뉴</t>
@@ -6156,6 +6343,9 @@
   </si>
   <si>
     <t xml:space="preserve">어울려뉴-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">뉴,다뉴</t>
   </si>
 </sst>
 </file>
@@ -6360,7 +6550,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6402,10 +6592,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6650,7 +6836,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CM1000"/>
+  <dimension ref="A1:CQ1000"/>
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.57"/>
@@ -6660,13 +6846,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="6" style="1" width="30.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="16" style="1" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="71" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="78" min="77" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="79" style="1" width="35.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="80" min="80" style="1" width="39.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="81" min="81" style="1" width="44.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="1" width="38.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="71" min="16" style="1" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="77" min="72" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="78" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="80" min="80" style="1" width="35.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="81" min="81" style="1" width="39.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="1" width="44.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="83" style="1" width="38.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6916,7 +7102,7 @@
       <c r="CD1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" s="5" t="s">
         <v>82</v>
       </c>
       <c r="CF1" s="1" t="s">
@@ -6931,17 +7117,29 @@
       <c r="CI1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="0" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="0" t="s">
+      <c r="CK1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="0" t="s">
+      <c r="CL1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="0" t="s">
+      <c r="CM1" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7027,6 +7225,7 @@
       <c r="CB2" s="6"/>
       <c r="CC2" s="6"/>
       <c r="CD2" s="6"/>
+      <c r="CE2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
@@ -7111,6 +7310,7 @@
       <c r="CB3" s="6"/>
       <c r="CC3" s="6"/>
       <c r="CD3" s="6"/>
+      <c r="CE3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
@@ -7195,23 +7395,24 @@
       <c r="CB4" s="6"/>
       <c r="CC4" s="6"/>
       <c r="CD4" s="6"/>
+      <c r="CE4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>6</v>
@@ -7226,7 +7427,7 @@
         <v>9</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>11</v>
@@ -7241,7 +7442,7 @@
         <v>14</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>16</v>
@@ -7265,28 +7466,28 @@
         <v>22</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AB5" s="5" t="s">
         <v>27</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AD5" s="5" t="s">
         <v>29</v>
       </c>
       <c r="AE5" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AF5" s="5" t="s">
         <v>31</v>
@@ -7313,7 +7514,7 @@
         <v>38</v>
       </c>
       <c r="AN5" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO5" s="5" t="s">
         <v>40</v>
@@ -7331,16 +7532,16 @@
         <v>44</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AU5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="AV5" s="5" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AW5" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AX5" s="5" t="s">
         <v>49</v>
@@ -7373,7 +7574,7 @@
         <v>58</v>
       </c>
       <c r="BH5" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI5" s="5" t="s">
         <v>60</v>
@@ -7385,22 +7586,22 @@
         <v>62</v>
       </c>
       <c r="BL5" s="5" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="BM5" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BN5" s="5" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="BO5" s="5" t="s">
         <v>66</v>
       </c>
       <c r="BP5" s="5" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="BQ5" s="5" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="BR5" s="5" t="s">
         <v>69</v>
@@ -7421,382 +7622,406 @@
         <v>74</v>
       </c>
       <c r="BX5" s="5" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="BY5" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BZ5" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="CA5" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="CB5" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="CC5" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="CD5" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="CE5" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="CE5" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="CF5" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="CG5" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="CH5" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="CI5" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CJ5" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="CK5" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="CL5" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="CJ5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="CL5" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM5" s="0" t="s">
+      <c r="CM5" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="CN5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="CQ5" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="V6" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X6" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Y6" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="Z6" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AA6" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AB6" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AC6" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AE6" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF6" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AH6" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AJ6" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AK6" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL6" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM6" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AN6" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AO6" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AP6" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AQ6" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AR6" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AS6" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AT6" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AU6" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AV6" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AW6" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AX6" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AY6" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AZ6" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="BA6" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="BB6" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="BC6" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="BD6" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="BE6" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="BF6" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="BG6" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="BH6" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="BI6" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="BJ6" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BK6" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="BL6" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="BM6" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="BN6" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="BO6" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="BP6" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="BQ6" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="BR6" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="BS6" s="5" t="s">
-        <v>70</v>
+        <v>194</v>
+      </c>
+      <c r="BS6" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="BT6" s="5" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="BU6" s="5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="BV6" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="BW6" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="BX6" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="BY6" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="BZ6" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="CA6" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="CB6" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
+      </c>
+      <c r="CA6" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="CB6" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="CC6" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="CD6" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="CE6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="CF6" s="10" t="s">
         <v>204</v>
       </c>
+      <c r="CD6" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="CE6" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="CF6" s="1" t="s">
+        <v>207</v>
+      </c>
       <c r="CG6" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="CH6" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="CI6" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="CJ6" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="CK6" s="11" t="s">
+      <c r="CH6" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="CL6" s="11" t="s">
+      <c r="CI6" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="CM6" s="11" t="s">
+      <c r="CJ6" s="10" t="s">
         <v>211</v>
+      </c>
+      <c r="CK6" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="CL6" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="CM6" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="CN6" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="CO6" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="CP6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="CQ6" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="9" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="T7" s="4" t="s">
         <v>19</v>
@@ -7811,31 +8036,31 @@
         <v>22</v>
       </c>
       <c r="X7" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Y7" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Z7" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AA7" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AB7" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="AF7" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="AG7" s="4" t="s">
         <v>32</v>
@@ -7844,28 +8069,28 @@
         <v>33</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AJ7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AK7" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AL7" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AM7" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="AN7" s="4" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AO7" s="4" t="s">
         <v>40</v>
       </c>
       <c r="AP7" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AQ7" s="4" t="s">
         <v>42</v>
@@ -7877,37 +8102,37 @@
         <v>44</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AU7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AV7" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AW7" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="AX7" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="AX7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AY7" s="12" t="s">
+      <c r="AY7" s="11" t="s">
         <v>50</v>
       </c>
       <c r="AZ7" s="4" t="s">
         <v>51</v>
       </c>
       <c r="BA7" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="BB7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="BC7" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="BD7" s="4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="BE7" s="4" t="s">
         <v>56</v>
@@ -7916,121 +8141,133 @@
         <v>57</v>
       </c>
       <c r="BG7" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="BH7" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI7" s="4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="BJ7" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="BK7" s="4" t="s">
-        <v>62</v>
+        <v>256</v>
       </c>
       <c r="BL7" s="4" t="s">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="BM7" s="4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="BN7" s="4" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="BO7" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="BP7" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="BQ7" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="BR7" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="BS7" s="5" t="s">
-        <v>257</v>
+        <v>262</v>
+      </c>
+      <c r="BS7" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="BT7" s="5" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="BU7" s="5" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="BV7" s="5" t="s">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="BW7" s="5" t="s">
         <v>74</v>
       </c>
       <c r="BX7" s="5" t="s">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="BY7" s="5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="BZ7" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="CA7" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="CB7" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
+      </c>
+      <c r="CA7" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="CB7" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="CC7" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="CD7" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="CE7" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="CF7" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="CG7" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
+      </c>
+      <c r="CD7" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="CE7" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="CF7" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="CG7" s="10" t="s">
+        <v>275</v>
       </c>
       <c r="CH7" s="1" t="s">
-        <v>122</v>
+        <v>276</v>
       </c>
       <c r="CI7" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="CJ7" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="CK7" s="0" t="s">
-        <v>272</v>
-      </c>
-      <c r="CL7" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="CM7" s="11" t="s">
-        <v>274</v>
+        <v>125</v>
+      </c>
+      <c r="CJ7" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="CK7" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="CL7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="CM7" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="CN7" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="CO7" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="CP7" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="CQ7" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="9" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
@@ -8045,28 +8282,28 @@
         <v>9</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>18</v>
@@ -8084,31 +8321,31 @@
         <v>22</v>
       </c>
       <c r="X8" s="4" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AA8" s="4" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AB8" s="4" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AC8" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AD8" s="4" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AE8" s="4" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AF8" s="4" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="AG8" s="4" t="s">
         <v>32</v>
@@ -8117,22 +8354,22 @@
         <v>33</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="AJ8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="AK8" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AL8" s="4" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="AM8" s="4" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="AN8" s="4" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AO8" s="4" t="s">
         <v>40</v>
@@ -8150,21 +8387,21 @@
         <v>44</v>
       </c>
       <c r="AT8" s="4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="AU8" s="4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="AV8" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AW8" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="AX8" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="AX8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AY8" s="12" t="s">
+      <c r="AY8" s="11" t="s">
         <v>50</v>
       </c>
       <c r="AZ8" s="4" t="s">
@@ -8204,106 +8441,118 @@
         <v>62</v>
       </c>
       <c r="BL8" s="4" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="BM8" s="4" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="BN8" s="4" t="s">
-        <v>65</v>
+        <v>309</v>
       </c>
       <c r="BO8" s="4" t="s">
         <v>66</v>
       </c>
       <c r="BP8" s="4" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="BQ8" s="4" t="s">
-        <v>300</v>
+        <v>114</v>
       </c>
       <c r="BR8" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS8" s="5" t="s">
-        <v>301</v>
+        <v>310</v>
+      </c>
+      <c r="BS8" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="BT8" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="BU8" s="5" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="BV8" s="5" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="BW8" s="5" t="s">
-        <v>74</v>
+        <v>314</v>
       </c>
       <c r="BX8" s="5" t="s">
-        <v>305</v>
+        <v>75</v>
       </c>
       <c r="BY8" s="5" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="BZ8" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="CA8" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="CB8" s="5" t="s">
-        <v>309</v>
+        <v>316</v>
+      </c>
+      <c r="CA8" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="CB8" s="4" t="s">
+        <v>318</v>
       </c>
       <c r="CC8" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="CD8" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="CE8" s="1" t="s">
-        <v>312</v>
+        <v>319</v>
+      </c>
+      <c r="CD8" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="CE8" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="CF8" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="CG8" s="1" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="CH8" s="1" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="CI8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CJ8" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="CK8" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="CL8" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="CM8" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="CJ8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="CL8" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="CM8" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="CN8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO8" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="CP8" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="CQ8" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>6</v>
@@ -8314,11 +8563,11 @@
       <c r="I9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="12" t="s">
         <v>9</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>11</v>
@@ -8330,298 +8579,310 @@
         <v>13</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="U9" s="4" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="V9" s="4" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="X9" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="Y9" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="Z9" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="AA9" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="AB9" s="15" t="s">
-        <v>333</v>
-      </c>
-      <c r="AC9" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="AD9" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="AE9" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="AF9" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="AG9" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="X9" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y9" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="Z9" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="AA9" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="AB9" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD9" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="AE9" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="AF9" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="AG9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AH9" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="AI9" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="AJ9" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="AK9" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="AL9" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="AM9" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="AN9" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="AO9" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="AP9" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="AQ9" s="14" t="s">
-        <v>347</v>
+      <c r="AH9" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI9" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="AJ9" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="AK9" s="13" t="s">
+        <v>353</v>
+      </c>
+      <c r="AL9" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="AM9" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="AN9" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO9" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="AP9" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="AQ9" s="13" t="s">
+        <v>359</v>
       </c>
       <c r="AR9" s="4" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="AS9" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="AT9" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="AU9" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="AV9" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="AW9" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="AX9" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="AY9" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="AZ9" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="BA9" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="BB9" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="BC9" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="BD9" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="BE9" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="BF9" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="BG9" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="BH9" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="BI9" s="14" t="s">
+      <c r="AT9" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="BJ9" s="14" t="s">
+      <c r="AU9" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="AV9" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="AW9" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="BK9" s="14" t="s">
+      <c r="AX9" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="BL9" s="14" t="s">
+      <c r="AY9" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="BM9" s="14" t="s">
+      <c r="AZ9" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="BN9" s="14" t="s">
+      <c r="BA9" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="BO9" s="14" t="s">
+      <c r="BB9" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="BP9" s="14" t="s">
+      <c r="BC9" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="BQ9" s="14" t="s">
+      <c r="BD9" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="BR9" s="14" t="s">
+      <c r="BE9" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="BS9" s="5" t="s">
+      <c r="BF9" s="13" t="s">
         <v>372</v>
       </c>
+      <c r="BG9" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="BH9" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="BI9" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="BJ9" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="BK9" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="BL9" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="BM9" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="BN9" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="BO9" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="BP9" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="BQ9" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="BR9" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="BS9" s="13" t="s">
+        <v>384</v>
+      </c>
       <c r="BT9" s="5" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="BU9" s="5" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="BV9" s="5" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="BW9" s="5" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="BX9" s="5" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="BY9" s="5" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="BZ9" s="5" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="CA9" s="5" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="CB9" s="5" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="CC9" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="CD9" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="CE9" s="10" t="s">
-        <v>384</v>
+        <v>394</v>
+      </c>
+      <c r="CD9" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="CE9" s="4" t="s">
+        <v>396</v>
       </c>
       <c r="CF9" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="CG9" s="1" t="s">
-        <v>386</v>
+        <v>397</v>
+      </c>
+      <c r="CG9" s="10" t="s">
+        <v>398</v>
       </c>
       <c r="CH9" s="1" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="CI9" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="CJ9" s="0" t="s">
-        <v>389</v>
-      </c>
-      <c r="CK9" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="CL9" s="0" t="s">
-        <v>391</v>
-      </c>
-      <c r="CM9" s="0" t="s">
-        <v>392</v>
+        <v>400</v>
+      </c>
+      <c r="CJ9" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="CK9" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="CL9" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="CM9" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="CN9" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="CO9" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="CP9" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="CQ9" s="1" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="9" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="T10" s="5" t="s">
         <v>19</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="V10" s="5" t="s">
         <v>21</v>
@@ -8630,16 +8891,16 @@
         <v>22</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="AB10" s="5" t="s">
         <v>28</v>
@@ -8648,481 +8909,505 @@
         <v>28</v>
       </c>
       <c r="AD10" s="5" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="AE10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="AG10" s="5" t="s">
         <v>32</v>
       </c>
       <c r="AH10" s="5" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="AI10" s="5" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="AJ10" s="5" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="AK10" s="5" t="s">
         <v>36</v>
       </c>
       <c r="AL10" s="5" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="AM10" s="5" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="AN10" s="5" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="AO10" s="5" t="s">
         <v>40</v>
       </c>
       <c r="AP10" s="5" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="AQ10" s="5" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="AR10" s="5" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="AS10" s="5" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="AT10" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="AU10" s="16" t="s">
-        <v>426</v>
-      </c>
-      <c r="AV10" s="16" t="s">
-        <v>427</v>
-      </c>
-      <c r="AW10" s="16" t="s">
-        <v>428</v>
-      </c>
-      <c r="AX10" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="AU10" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="AV10" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="AW10" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="AX10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="AY10" s="12" t="s">
+      <c r="AY10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="AZ10" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="BA10" s="16" t="s">
-        <v>430</v>
-      </c>
-      <c r="BB10" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="BC10" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="BD10" s="16" t="s">
+      <c r="AZ10" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="BA10" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="BB10" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="BC10" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="BD10" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="BE10" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="BF10" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG10" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="BH10" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="BI10" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="BE10" s="16" t="s">
-        <v>434</v>
-      </c>
-      <c r="BF10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG10" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="BH10" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="BI10" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="BJ10" s="16" t="s">
-        <v>437</v>
-      </c>
-      <c r="BK10" s="16" t="s">
-        <v>438</v>
-      </c>
-      <c r="BL10" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="BM10" s="16" t="s">
-        <v>440</v>
-      </c>
-      <c r="BN10" s="16" t="s">
-        <v>441</v>
-      </c>
-      <c r="BO10" s="16" t="s">
-        <v>442</v>
-      </c>
-      <c r="BP10" s="16" t="s">
-        <v>443</v>
-      </c>
-      <c r="BQ10" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="BR10" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="BS10" s="5" t="s">
-        <v>446</v>
+      <c r="BJ10" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="BK10" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="BL10" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="BM10" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="BN10" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="BO10" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="BP10" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="BQ10" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="BR10" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="BS10" s="15" t="s">
+        <v>462</v>
       </c>
       <c r="BT10" s="5" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="BU10" s="5" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="BV10" s="5" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="BW10" s="5" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="BX10" s="5" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="BY10" s="5" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="BZ10" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="CA10" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="CB10" s="5" t="s">
-        <v>455</v>
+        <v>469</v>
+      </c>
+      <c r="CA10" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="CB10" s="4" t="s">
+        <v>471</v>
       </c>
       <c r="CC10" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="CD10" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="CE10" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="CF10" s="1" t="s">
-        <v>459</v>
+        <v>472</v>
+      </c>
+      <c r="CD10" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="CE10" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="CF10" s="16" t="s">
+        <v>475</v>
       </c>
       <c r="CG10" s="1" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="CH10" s="1" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="CI10" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="CJ10" s="0" t="s">
-        <v>463</v>
-      </c>
-      <c r="CK10" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="CL10" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="CM10" s="0" t="s">
-        <v>466</v>
+        <v>478</v>
+      </c>
+      <c r="CJ10" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="CK10" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="CL10" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="CM10" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="CN10" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="CO10" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="CP10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="CQ10" s="1" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="9" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="S11" s="4" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="U11" s="4" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="X11" s="4" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="Y11" s="4" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="Z11" s="4" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="AA11" s="4" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="AB11" s="4" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="AC11" s="4" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="AD11" s="4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="AE11" s="4" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="AF11" s="4" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="AG11" s="4" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="AH11" s="4" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="AJ11" s="4" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="AK11" s="4" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="AL11" s="4" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="AM11" s="4" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="AN11" s="4" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="AO11" s="4" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="AP11" s="4" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="AQ11" s="4" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="AR11" s="4" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="AS11" s="4" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="AT11" s="4" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="AU11" s="4" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="AV11" s="4" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="AW11" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="AX11" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="AY11" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="AZ11" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="BA11" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="BB11" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="BC11" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="BD11" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="BE11" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="BF11" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="BG11" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="BH11" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="BI11" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="BJ11" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="BK11" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="BL11" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="BM11" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="BN11" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="BO11" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="BP11" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="BQ11" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="AX11" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="AY11" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="AZ11" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="BA11" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="BB11" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="BC11" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="BD11" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="BE11" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="BF11" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="BG11" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="BH11" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="BI11" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="BJ11" s="4" t="s">
-        <v>525</v>
-      </c>
-      <c r="BK11" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="BL11" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="BM11" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="BN11" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="BO11" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="BP11" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="BQ11" s="4" t="s">
-        <v>531</v>
-      </c>
       <c r="BR11" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="BS11" s="5" t="s">
-        <v>533</v>
+        <v>551</v>
+      </c>
+      <c r="BS11" s="4" t="s">
+        <v>552</v>
       </c>
       <c r="BT11" s="5" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="BU11" s="5" t="s">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="BV11" s="5" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="BW11" s="5" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="BX11" s="5" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="BY11" s="5" t="s">
-        <v>76</v>
+        <v>558</v>
       </c>
       <c r="BZ11" s="5" t="s">
-        <v>539</v>
+        <v>77</v>
       </c>
       <c r="CA11" s="5" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="CB11" s="5" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="CC11" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="CD11" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="CE11" s="10" t="s">
-        <v>544</v>
+        <v>561</v>
+      </c>
+      <c r="CD11" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="CE11" s="4" t="s">
+        <v>563</v>
       </c>
       <c r="CF11" s="10" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="CG11" s="10" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="CH11" s="10" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="CI11" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="CJ11" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="CK11" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="CL11" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="CM11" s="11" t="s">
-        <v>552</v>
+        <v>567</v>
+      </c>
+      <c r="CJ11" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="CK11" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="CL11" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="CM11" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="CN11" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="CO11" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="CP11" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="CQ11" s="10" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>553</v>
+        <v>576</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>554</v>
+        <v>577</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="9" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>6</v>
@@ -9137,1104 +9422,1152 @@
         <v>9</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="Q12" s="5" t="s">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>560</v>
+        <v>583</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="V12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="W12" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="Y12" s="5" t="s">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>566</v>
+        <v>589</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="AC12" s="5" t="s">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="AD12" s="5" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="AE12" s="5" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="AF12" s="5" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="AG12" s="5" t="s">
         <v>32</v>
       </c>
       <c r="AH12" s="5" t="s">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="AI12" s="5" t="s">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="AJ12" s="5" t="s">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="AK12" s="5" t="s">
-        <v>575</v>
+        <v>598</v>
       </c>
       <c r="AL12" s="5" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="AM12" s="5" t="s">
-        <v>577</v>
+        <v>600</v>
       </c>
       <c r="AN12" s="5" t="s">
-        <v>578</v>
+        <v>601</v>
       </c>
       <c r="AO12" s="5" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="AP12" s="5" t="s">
-        <v>580</v>
+        <v>603</v>
       </c>
       <c r="AQ12" s="5" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="AR12" s="5" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="AS12" s="5" t="s">
-        <v>583</v>
+        <v>606</v>
       </c>
       <c r="AT12" s="5" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="AU12" s="5" t="s">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="AV12" s="5" t="s">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="AW12" s="5" t="s">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="AX12" s="5" t="s">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="AY12" s="5" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="AZ12" s="5" t="s">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="BA12" s="5" t="s">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="BB12" s="5" t="s">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="BC12" s="5" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="BD12" s="5" t="s">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="BE12" s="5" t="s">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="BF12" s="5" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="BG12" s="5" t="s">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="BH12" s="5" t="s">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="BI12" s="5" t="s">
-        <v>597</v>
+        <v>620</v>
       </c>
       <c r="BJ12" s="5" t="s">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="BK12" s="5" t="s">
-        <v>599</v>
+        <v>621</v>
       </c>
       <c r="BL12" s="5" t="s">
-        <v>600</v>
+        <v>622</v>
       </c>
       <c r="BM12" s="5" t="s">
-        <v>601</v>
+        <v>623</v>
       </c>
       <c r="BN12" s="5" t="s">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="BO12" s="5" t="s">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="BP12" s="5" t="s">
-        <v>67</v>
+        <v>626</v>
       </c>
       <c r="BQ12" s="5" t="s">
-        <v>604</v>
+        <v>68</v>
       </c>
       <c r="BR12" s="5" t="s">
-        <v>605</v>
+        <v>627</v>
       </c>
       <c r="BS12" s="5" t="s">
-        <v>606</v>
+        <v>628</v>
       </c>
       <c r="BT12" s="5" t="s">
-        <v>607</v>
+        <v>629</v>
       </c>
       <c r="BU12" s="5" t="s">
-        <v>608</v>
+        <v>630</v>
       </c>
       <c r="BV12" s="5" t="s">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="BW12" s="5" t="s">
-        <v>610</v>
+        <v>632</v>
       </c>
       <c r="BX12" s="5" t="s">
-        <v>611</v>
+        <v>633</v>
       </c>
       <c r="BY12" s="5" t="s">
-        <v>261</v>
+        <v>634</v>
       </c>
       <c r="BZ12" s="5" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="CA12" s="5" t="s">
-        <v>612</v>
+        <v>269</v>
       </c>
       <c r="CB12" s="5" t="s">
-        <v>264</v>
+        <v>635</v>
       </c>
       <c r="CC12" s="5" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="CD12" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="CE12" s="1" t="s">
-        <v>614</v>
+        <v>272</v>
+      </c>
+      <c r="CE12" s="5" t="s">
+        <v>636</v>
       </c>
       <c r="CF12" s="1" t="s">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="CG12" s="1" t="s">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="CH12" s="1" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="CI12" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="CJ12" s="0" t="s">
-        <v>619</v>
-      </c>
-      <c r="CK12" s="0" t="s">
-        <v>620</v>
-      </c>
-      <c r="CL12" s="0" t="s">
-        <v>621</v>
-      </c>
-      <c r="CM12" s="0" t="s">
-        <v>622</v>
+        <v>640</v>
+      </c>
+      <c r="CJ12" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="CK12" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="CL12" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="CM12" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="CN12" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="CO12" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="CP12" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="CQ12" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>623</v>
+        <v>648</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>624</v>
+        <v>649</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="9" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>627</v>
+        <v>652</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>628</v>
+        <v>653</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>632</v>
+        <v>657</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>633</v>
+        <v>658</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>634</v>
+        <v>659</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>635</v>
+        <v>660</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>639</v>
+        <v>664</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>643</v>
+        <v>668</v>
       </c>
       <c r="X13" s="4" t="s">
-        <v>644</v>
+        <v>669</v>
       </c>
       <c r="Y13" s="4" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="Z13" s="4" t="s">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="AA13" s="4" t="s">
-        <v>647</v>
+        <v>672</v>
       </c>
       <c r="AB13" s="4" t="s">
-        <v>648</v>
+        <v>673</v>
       </c>
       <c r="AC13" s="4" t="s">
-        <v>649</v>
+        <v>674</v>
       </c>
       <c r="AD13" s="4" t="s">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="AE13" s="4" t="s">
-        <v>651</v>
+        <v>676</v>
       </c>
       <c r="AF13" s="4" t="s">
-        <v>652</v>
+        <v>677</v>
       </c>
       <c r="AG13" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AH13" s="4" t="s">
-        <v>653</v>
+        <v>678</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>654</v>
+        <v>679</v>
       </c>
       <c r="AJ13" s="4" t="s">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="AK13" s="4" t="s">
-        <v>656</v>
+        <v>681</v>
       </c>
       <c r="AL13" s="4" t="s">
-        <v>657</v>
+        <v>682</v>
       </c>
       <c r="AM13" s="4" t="s">
-        <v>658</v>
+        <v>683</v>
       </c>
       <c r="AN13" s="4" t="s">
-        <v>659</v>
+        <v>684</v>
       </c>
       <c r="AO13" s="4" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="AP13" s="4" t="s">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="AQ13" s="4" t="s">
-        <v>662</v>
+        <v>687</v>
       </c>
       <c r="AR13" s="4" t="s">
-        <v>663</v>
+        <v>688</v>
       </c>
       <c r="AS13" s="4" t="s">
-        <v>664</v>
+        <v>689</v>
       </c>
       <c r="AT13" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="AU13" s="14" t="s">
-        <v>666</v>
-      </c>
-      <c r="AV13" s="14" t="s">
-        <v>667</v>
-      </c>
-      <c r="AW13" s="14" t="s">
-        <v>668</v>
-      </c>
-      <c r="AX13" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="AY13" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="AZ13" s="14" t="s">
-        <v>671</v>
-      </c>
-      <c r="BA13" s="14" t="s">
-        <v>672</v>
-      </c>
-      <c r="BB13" s="14" t="s">
-        <v>673</v>
-      </c>
-      <c r="BC13" s="14" t="s">
-        <v>674</v>
-      </c>
-      <c r="BD13" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="BE13" s="14" t="s">
-        <v>676</v>
-      </c>
-      <c r="BF13" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="AU13" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="AV13" s="13" t="s">
+        <v>692</v>
+      </c>
+      <c r="AW13" s="13" t="s">
+        <v>693</v>
+      </c>
+      <c r="AX13" s="13" t="s">
+        <v>694</v>
+      </c>
+      <c r="AY13" s="13" t="s">
+        <v>695</v>
+      </c>
+      <c r="AZ13" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="BA13" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="BB13" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="BC13" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="BD13" s="13" t="s">
+        <v>700</v>
+      </c>
+      <c r="BE13" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="BF13" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="BG13" s="14" t="s">
-        <v>677</v>
-      </c>
-      <c r="BH13" s="14" t="s">
-        <v>678</v>
-      </c>
-      <c r="BI13" s="14" t="s">
-        <v>679</v>
-      </c>
-      <c r="BJ13" s="14" t="s">
-        <v>680</v>
-      </c>
-      <c r="BK13" s="14" t="s">
-        <v>681</v>
-      </c>
-      <c r="BL13" s="14" t="s">
-        <v>682</v>
-      </c>
-      <c r="BM13" s="14" t="s">
-        <v>683</v>
-      </c>
-      <c r="BN13" s="14" t="s">
-        <v>684</v>
-      </c>
-      <c r="BO13" s="14" t="s">
-        <v>685</v>
-      </c>
-      <c r="BP13" s="14" t="s">
-        <v>686</v>
-      </c>
-      <c r="BQ13" s="14" t="s">
-        <v>687</v>
-      </c>
-      <c r="BR13" s="14" t="s">
-        <v>688</v>
-      </c>
-      <c r="BS13" s="5" t="s">
-        <v>689</v>
+      <c r="BG13" s="13" t="s">
+        <v>702</v>
+      </c>
+      <c r="BH13" s="13" t="s">
+        <v>703</v>
+      </c>
+      <c r="BI13" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="BJ13" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="BK13" s="13" t="s">
+        <v>706</v>
+      </c>
+      <c r="BL13" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="BM13" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="BN13" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="BO13" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="BP13" s="13" t="s">
+        <v>711</v>
+      </c>
+      <c r="BQ13" s="13" t="s">
+        <v>712</v>
+      </c>
+      <c r="BR13" s="13" t="s">
+        <v>713</v>
+      </c>
+      <c r="BS13" s="13" t="s">
+        <v>714</v>
       </c>
       <c r="BT13" s="5" t="s">
-        <v>690</v>
+        <v>715</v>
       </c>
       <c r="BU13" s="5" t="s">
-        <v>691</v>
+        <v>716</v>
       </c>
       <c r="BV13" s="5" t="s">
-        <v>692</v>
+        <v>717</v>
       </c>
       <c r="BW13" s="5" t="s">
-        <v>693</v>
+        <v>718</v>
       </c>
       <c r="BX13" s="5" t="s">
-        <v>694</v>
+        <v>719</v>
       </c>
       <c r="BY13" s="5" t="s">
-        <v>695</v>
+        <v>720</v>
       </c>
       <c r="BZ13" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="CA13" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="CB13" s="5" t="s">
-        <v>698</v>
+        <v>721</v>
+      </c>
+      <c r="CA13" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="CB13" s="4" t="s">
+        <v>723</v>
       </c>
       <c r="CC13" s="5" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="CD13" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="CE13" s="1" t="s">
-        <v>701</v>
+        <v>725</v>
+      </c>
+      <c r="CE13" s="5" t="s">
+        <v>726</v>
       </c>
       <c r="CF13" s="1" t="s">
-        <v>702</v>
+        <v>727</v>
       </c>
       <c r="CG13" s="1" t="s">
-        <v>703</v>
+        <v>728</v>
       </c>
       <c r="CH13" s="1" t="s">
-        <v>704</v>
+        <v>729</v>
       </c>
       <c r="CI13" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="CJ13" s="0" t="s">
-        <v>706</v>
-      </c>
-      <c r="CK13" s="0" t="s">
-        <v>707</v>
-      </c>
-      <c r="CL13" s="0" t="s">
-        <v>708</v>
-      </c>
-      <c r="CM13" s="0" t="s">
-        <v>709</v>
+        <v>730</v>
+      </c>
+      <c r="CJ13" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="CK13" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="CL13" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="CM13" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="CN13" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="CO13" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="CP13" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="CQ13" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>711</v>
+        <v>738</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>739</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="19" t="s">
-        <v>712</v>
+      <c r="D14" s="18" t="s">
+        <v>740</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>713</v>
+        <v>741</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>714</v>
+        <v>742</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>714</v>
+        <v>742</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>715</v>
+        <v>743</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>716</v>
+        <v>744</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>717</v>
+        <v>745</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X14" s="4" t="s">
-        <v>718</v>
+        <v>746</v>
       </c>
       <c r="Y14" s="4" t="s">
-        <v>719</v>
+        <v>747</v>
       </c>
       <c r="Z14" s="4" t="s">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>721</v>
+        <v>749</v>
       </c>
       <c r="AB14" s="4" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="AC14" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AD14" s="4" t="s">
-        <v>722</v>
+        <v>750</v>
       </c>
       <c r="AE14" s="4" t="s">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="AF14" s="4" t="s">
-        <v>724</v>
+        <v>752</v>
       </c>
       <c r="AG14" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>725</v>
+        <v>753</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>726</v>
+        <v>754</v>
       </c>
       <c r="AJ14" s="4" t="s">
-        <v>727</v>
+        <v>755</v>
       </c>
       <c r="AK14" s="4" t="s">
-        <v>728</v>
+        <v>756</v>
       </c>
       <c r="AL14" s="4" t="s">
-        <v>729</v>
+        <v>757</v>
       </c>
       <c r="AM14" s="4" t="s">
-        <v>730</v>
+        <v>758</v>
       </c>
       <c r="AN14" s="4" t="s">
-        <v>731</v>
+        <v>759</v>
       </c>
       <c r="AO14" s="4" t="s">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="AP14" s="4" t="s">
-        <v>732</v>
+        <v>760</v>
       </c>
       <c r="AQ14" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="AR14" s="12" t="s">
-        <v>734</v>
-      </c>
-      <c r="AS14" s="12" t="s">
-        <v>735</v>
+        <v>761</v>
+      </c>
+      <c r="AR14" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="AS14" s="11" t="s">
+        <v>763</v>
       </c>
       <c r="AT14" s="4" t="s">
-        <v>736</v>
+        <v>764</v>
       </c>
       <c r="AU14" s="4" t="s">
-        <v>736</v>
+        <v>764</v>
       </c>
       <c r="AV14" s="4" t="s">
-        <v>737</v>
+        <v>765</v>
       </c>
       <c r="AW14" s="4" t="s">
-        <v>738</v>
+        <v>766</v>
       </c>
       <c r="AX14" s="4" t="s">
-        <v>739</v>
+        <v>767</v>
       </c>
       <c r="AY14" s="4" t="s">
-        <v>740</v>
+        <v>768</v>
       </c>
       <c r="AZ14" s="4" t="s">
-        <v>741</v>
+        <v>769</v>
       </c>
       <c r="BA14" s="4" t="s">
-        <v>742</v>
+        <v>770</v>
       </c>
       <c r="BB14" s="4" t="s">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="BC14" s="4" t="s">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="BD14" s="4" t="s">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="BE14" s="4" t="s">
-        <v>745</v>
+        <v>773</v>
       </c>
       <c r="BF14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="BG14" s="4" t="s">
-        <v>746</v>
+        <v>774</v>
       </c>
       <c r="BH14" s="4" t="s">
-        <v>747</v>
+        <v>775</v>
       </c>
       <c r="BI14" s="4" t="s">
-        <v>748</v>
+        <v>776</v>
       </c>
       <c r="BJ14" s="4" t="s">
-        <v>749</v>
+        <v>92</v>
       </c>
       <c r="BK14" s="4" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="BL14" s="4" t="s">
-        <v>751</v>
+        <v>778</v>
       </c>
       <c r="BM14" s="4" t="s">
-        <v>752</v>
+        <v>779</v>
       </c>
       <c r="BN14" s="4" t="s">
-        <v>725</v>
+        <v>780</v>
       </c>
       <c r="BO14" s="4" t="s">
         <v>753</v>
       </c>
       <c r="BP14" s="4" t="s">
-        <v>746</v>
+        <v>781</v>
       </c>
       <c r="BQ14" s="4" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="BR14" s="4" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="BS14" s="4" t="s">
-        <v>70</v>
+        <v>783</v>
       </c>
       <c r="BT14" s="4" t="s">
-        <v>756</v>
+        <v>71</v>
       </c>
       <c r="BU14" s="4" t="s">
-        <v>757</v>
+        <v>784</v>
       </c>
       <c r="BV14" s="4" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
       <c r="BW14" s="4" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="BX14" s="4" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="BY14" s="4" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="BZ14" s="4" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="CA14" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="CB14" s="5" t="s">
-        <v>200</v>
+        <v>790</v>
+      </c>
+      <c r="CB14" s="4" t="s">
+        <v>791</v>
       </c>
       <c r="CC14" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="CD14" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="CE14" s="1" t="s">
-        <v>765</v>
+        <v>204</v>
+      </c>
+      <c r="CD14" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="CE14" s="4" t="s">
+        <v>792</v>
       </c>
       <c r="CF14" s="1" t="s">
-        <v>766</v>
+        <v>793</v>
       </c>
       <c r="CG14" s="1" t="s">
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="CH14" s="1" t="s">
-        <v>206</v>
+        <v>795</v>
       </c>
       <c r="CI14" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="CJ14" s="0" t="s">
-        <v>769</v>
-      </c>
-      <c r="CK14" s="0" t="s">
-        <v>770</v>
-      </c>
-      <c r="CL14" s="0" t="s">
-        <v>771</v>
-      </c>
-      <c r="CM14" s="0" t="s">
-        <v>772</v>
+        <v>210</v>
+      </c>
+      <c r="CJ14" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="CK14" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="CL14" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="CM14" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="CN14" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="CO14" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="CP14" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="CQ14" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>773</v>
+        <v>803</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>774</v>
+        <v>804</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="9" t="s">
-        <v>712</v>
+        <v>740</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>775</v>
+        <v>805</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>776</v>
+        <v>806</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>778</v>
+        <v>808</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>779</v>
+        <v>809</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>780</v>
+        <v>810</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>782</v>
+        <v>812</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>783</v>
+        <v>813</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>784</v>
+        <v>814</v>
       </c>
       <c r="S15" s="4" t="s">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="V15" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>788</v>
+        <v>818</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>789</v>
+        <v>819</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>790</v>
+        <v>820</v>
       </c>
       <c r="AB15" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AC15" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AD15" s="4" t="s">
-        <v>791</v>
+        <v>821</v>
       </c>
       <c r="AE15" s="4" t="s">
-        <v>792</v>
+        <v>822</v>
       </c>
       <c r="AF15" s="4" t="s">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="AG15" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AH15" s="4" t="s">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="AJ15" s="4" t="s">
-        <v>796</v>
+        <v>826</v>
       </c>
       <c r="AK15" s="4" t="s">
-        <v>797</v>
+        <v>827</v>
       </c>
       <c r="AL15" s="4" t="s">
-        <v>798</v>
+        <v>828</v>
       </c>
       <c r="AM15" s="4" t="s">
-        <v>799</v>
+        <v>829</v>
       </c>
       <c r="AN15" s="4" t="s">
-        <v>731</v>
+        <v>759</v>
       </c>
       <c r="AO15" s="4" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="AP15" s="4" t="s">
-        <v>801</v>
+        <v>831</v>
       </c>
       <c r="AQ15" s="4" t="s">
-        <v>802</v>
+        <v>832</v>
       </c>
       <c r="AR15" s="4" t="s">
-        <v>803</v>
+        <v>833</v>
       </c>
       <c r="AS15" s="4" t="s">
-        <v>804</v>
+        <v>834</v>
       </c>
       <c r="AT15" s="4" t="s">
-        <v>805</v>
+        <v>835</v>
       </c>
       <c r="AU15" s="4" t="s">
-        <v>805</v>
+        <v>835</v>
       </c>
       <c r="AV15" s="4" t="s">
-        <v>806</v>
+        <v>836</v>
       </c>
       <c r="AW15" s="4" t="s">
-        <v>807</v>
+        <v>837</v>
       </c>
       <c r="AX15" s="4" t="s">
-        <v>808</v>
+        <v>838</v>
       </c>
       <c r="AY15" s="4" t="s">
-        <v>809</v>
+        <v>839</v>
       </c>
       <c r="AZ15" s="4" t="s">
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="BA15" s="4" t="s">
-        <v>811</v>
+        <v>841</v>
       </c>
       <c r="BB15" s="4" t="s">
-        <v>812</v>
+        <v>842</v>
       </c>
       <c r="BC15" s="4" t="s">
-        <v>813</v>
+        <v>843</v>
       </c>
       <c r="BD15" s="4" t="s">
-        <v>814</v>
+        <v>844</v>
       </c>
       <c r="BE15" s="4" t="s">
-        <v>815</v>
+        <v>845</v>
       </c>
       <c r="BF15" s="4" t="s">
         <v>57</v>
       </c>
       <c r="BG15" s="4" t="s">
-        <v>816</v>
+        <v>846</v>
       </c>
       <c r="BH15" s="4" t="s">
-        <v>817</v>
+        <v>847</v>
       </c>
       <c r="BI15" s="4" t="s">
-        <v>818</v>
+        <v>848</v>
       </c>
       <c r="BJ15" s="4" t="s">
-        <v>819</v>
+        <v>849</v>
       </c>
       <c r="BK15" s="4" t="s">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="BL15" s="4" t="s">
-        <v>821</v>
+        <v>851</v>
       </c>
       <c r="BM15" s="4" t="s">
-        <v>822</v>
+        <v>852</v>
       </c>
       <c r="BN15" s="4" t="s">
-        <v>823</v>
+        <v>853</v>
       </c>
       <c r="BO15" s="4" t="s">
-        <v>824</v>
+        <v>854</v>
       </c>
       <c r="BP15" s="4" t="s">
-        <v>825</v>
+        <v>855</v>
       </c>
       <c r="BQ15" s="4" t="s">
-        <v>826</v>
+        <v>856</v>
       </c>
       <c r="BR15" s="4" t="s">
-        <v>827</v>
-      </c>
-      <c r="BS15" s="5" t="s">
-        <v>70</v>
+        <v>857</v>
+      </c>
+      <c r="BS15" s="4" t="s">
+        <v>858</v>
       </c>
       <c r="BT15" s="5" t="s">
-        <v>828</v>
+        <v>71</v>
       </c>
       <c r="BU15" s="5" t="s">
-        <v>829</v>
+        <v>859</v>
       </c>
       <c r="BV15" s="5" t="s">
-        <v>830</v>
+        <v>860</v>
       </c>
       <c r="BW15" s="5" t="s">
-        <v>831</v>
+        <v>861</v>
       </c>
       <c r="BX15" s="5" t="s">
-        <v>832</v>
+        <v>862</v>
       </c>
       <c r="BY15" s="5" t="s">
-        <v>833</v>
+        <v>863</v>
       </c>
       <c r="BZ15" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="CA15" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="CB15" s="5" t="s">
-        <v>200</v>
+        <v>864</v>
+      </c>
+      <c r="CA15" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="CB15" s="4" t="s">
+        <v>866</v>
       </c>
       <c r="CC15" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="CD15" s="4" t="s">
-        <v>836</v>
-      </c>
-      <c r="CE15" s="10" t="s">
-        <v>837</v>
+        <v>204</v>
+      </c>
+      <c r="CD15" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="CE15" s="4" t="s">
+        <v>867</v>
       </c>
       <c r="CF15" s="10" t="s">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="CG15" s="10" t="s">
-        <v>839</v>
+        <v>869</v>
       </c>
       <c r="CH15" s="10" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="CI15" s="10" t="s">
-        <v>841</v>
-      </c>
-      <c r="CJ15" s="11" t="s">
-        <v>842</v>
-      </c>
-      <c r="CK15" s="11" t="s">
-        <v>843</v>
-      </c>
-      <c r="CL15" s="11" t="s">
-        <v>844</v>
-      </c>
-      <c r="CM15" s="11" t="s">
-        <v>845</v>
+        <v>871</v>
+      </c>
+      <c r="CJ15" s="10" t="s">
+        <v>872</v>
+      </c>
+      <c r="CK15" s="10" t="s">
+        <v>873</v>
+      </c>
+      <c r="CL15" s="10" t="s">
+        <v>874</v>
+      </c>
+      <c r="CM15" s="10" t="s">
+        <v>875</v>
+      </c>
+      <c r="CN15" s="10" t="s">
+        <v>876</v>
+      </c>
+      <c r="CO15" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="CP15" s="10" t="s">
+        <v>877</v>
+      </c>
+      <c r="CQ15" s="10" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>846</v>
+        <v>879</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>847</v>
+        <v>880</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>848</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>849</v>
+        <v>881</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>882</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>851</v>
+        <v>884</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>854</v>
+        <v>887</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>855</v>
+        <v>888</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>12</v>
@@ -10243,344 +10576,356 @@
         <v>13</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>856</v>
+        <v>889</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>857</v>
+        <v>890</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>858</v>
+        <v>891</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>859</v>
+        <v>892</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>860</v>
+        <v>893</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>861</v>
+        <v>894</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>862</v>
+        <v>895</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>863</v>
+        <v>896</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>864</v>
+        <v>897</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>865</v>
+        <v>898</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>866</v>
+        <v>899</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>867</v>
+        <v>900</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>868</v>
+        <v>901</v>
       </c>
       <c r="AB16" s="6" t="s">
-        <v>869</v>
+        <v>902</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>870</v>
+        <v>903</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>871</v>
+        <v>904</v>
       </c>
       <c r="AE16" s="6" t="s">
-        <v>872</v>
+        <v>905</v>
       </c>
       <c r="AF16" s="6" t="s">
-        <v>873</v>
+        <v>906</v>
       </c>
       <c r="AG16" s="6" t="s">
         <v>32</v>
       </c>
       <c r="AH16" s="6" t="s">
-        <v>874</v>
+        <v>907</v>
       </c>
       <c r="AI16" s="6" t="s">
-        <v>875</v>
+        <v>908</v>
       </c>
       <c r="AJ16" s="6" t="s">
-        <v>876</v>
+        <v>909</v>
       </c>
       <c r="AK16" s="6" t="s">
-        <v>877</v>
+        <v>910</v>
       </c>
       <c r="AL16" s="6" t="s">
-        <v>878</v>
+        <v>911</v>
       </c>
       <c r="AM16" s="6" t="s">
-        <v>879</v>
+        <v>912</v>
       </c>
       <c r="AN16" s="6" t="s">
-        <v>880</v>
+        <v>913</v>
       </c>
       <c r="AO16" s="6" t="s">
-        <v>881</v>
+        <v>914</v>
       </c>
       <c r="AP16" s="6" t="s">
-        <v>882</v>
+        <v>915</v>
       </c>
       <c r="AQ16" s="6" t="s">
-        <v>883</v>
+        <v>916</v>
       </c>
       <c r="AR16" s="6" t="s">
-        <v>884</v>
+        <v>917</v>
       </c>
       <c r="AS16" s="6" t="s">
-        <v>885</v>
+        <v>918</v>
       </c>
       <c r="AT16" s="6" t="s">
-        <v>886</v>
+        <v>919</v>
       </c>
       <c r="AU16" s="6" t="s">
-        <v>887</v>
+        <v>920</v>
       </c>
       <c r="AV16" s="6" t="s">
-        <v>888</v>
+        <v>921</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>889</v>
+        <v>922</v>
       </c>
       <c r="AX16" s="6" t="s">
-        <v>890</v>
+        <v>923</v>
       </c>
       <c r="AY16" s="6" t="s">
-        <v>891</v>
+        <v>924</v>
       </c>
       <c r="AZ16" s="6" t="s">
-        <v>892</v>
+        <v>925</v>
       </c>
       <c r="BA16" s="6" t="s">
-        <v>893</v>
+        <v>926</v>
       </c>
       <c r="BB16" s="6" t="s">
-        <v>894</v>
+        <v>927</v>
       </c>
       <c r="BC16" s="6" t="s">
-        <v>895</v>
+        <v>928</v>
       </c>
       <c r="BD16" s="6" t="s">
-        <v>896</v>
+        <v>929</v>
       </c>
       <c r="BE16" s="6" t="s">
-        <v>897</v>
+        <v>930</v>
       </c>
       <c r="BF16" s="6" t="s">
         <v>57</v>
       </c>
       <c r="BG16" s="6" t="s">
-        <v>898</v>
+        <v>931</v>
       </c>
       <c r="BH16" s="6" t="s">
-        <v>899</v>
+        <v>932</v>
       </c>
       <c r="BI16" s="6" t="s">
-        <v>900</v>
+        <v>933</v>
       </c>
       <c r="BJ16" s="6" t="s">
-        <v>901</v>
+        <v>934</v>
       </c>
       <c r="BK16" s="6" t="s">
-        <v>902</v>
+        <v>935</v>
       </c>
       <c r="BL16" s="6" t="s">
-        <v>903</v>
+        <v>936</v>
       </c>
       <c r="BM16" s="6" t="s">
-        <v>904</v>
+        <v>937</v>
       </c>
       <c r="BN16" s="6" t="s">
-        <v>905</v>
+        <v>938</v>
       </c>
       <c r="BO16" s="6" t="s">
-        <v>906</v>
+        <v>939</v>
       </c>
       <c r="BP16" s="6" t="s">
-        <v>907</v>
+        <v>940</v>
       </c>
       <c r="BQ16" s="6" t="s">
-        <v>908</v>
+        <v>941</v>
       </c>
       <c r="BR16" s="6" t="s">
-        <v>909</v>
-      </c>
-      <c r="BS16" s="5" t="s">
-        <v>70</v>
+        <v>942</v>
+      </c>
+      <c r="BS16" s="6" t="s">
+        <v>943</v>
       </c>
       <c r="BT16" s="5" t="s">
-        <v>910</v>
+        <v>71</v>
       </c>
       <c r="BU16" s="5" t="s">
-        <v>911</v>
+        <v>944</v>
       </c>
       <c r="BV16" s="5" t="s">
-        <v>912</v>
+        <v>945</v>
       </c>
       <c r="BW16" s="5" t="s">
-        <v>913</v>
+        <v>946</v>
       </c>
       <c r="BX16" s="5" t="s">
-        <v>914</v>
-      </c>
-      <c r="BY16" s="4" t="s">
-        <v>761</v>
+        <v>947</v>
+      </c>
+      <c r="BY16" s="5" t="s">
+        <v>948</v>
       </c>
       <c r="BZ16" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="CA16" s="6" t="s">
-        <v>916</v>
-      </c>
-      <c r="CB16" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="CC16" s="6" t="s">
-        <v>917</v>
+        <v>789</v>
+      </c>
+      <c r="CA16" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="CB16" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="CC16" s="5" t="s">
+        <v>204</v>
       </c>
       <c r="CD16" s="6" t="s">
-        <v>918</v>
-      </c>
-      <c r="CE16" s="1" t="s">
-        <v>919</v>
+        <v>951</v>
+      </c>
+      <c r="CE16" s="6" t="s">
+        <v>952</v>
       </c>
       <c r="CF16" s="1" t="s">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="CG16" s="1" t="s">
-        <v>921</v>
+        <v>954</v>
       </c>
       <c r="CH16" s="1" t="s">
-        <v>922</v>
+        <v>955</v>
       </c>
       <c r="CI16" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="CJ16" s="0" t="s">
-        <v>924</v>
-      </c>
-      <c r="CK16" s="0" t="s">
-        <v>925</v>
-      </c>
-      <c r="CL16" s="0" t="s">
-        <v>926</v>
-      </c>
-      <c r="CM16" s="0" t="s">
-        <v>927</v>
+        <v>956</v>
+      </c>
+      <c r="CJ16" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="CK16" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="CL16" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="CM16" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="CN16" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="CO16" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="CP16" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="CQ16" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>928</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>928</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>848</v>
+        <v>964</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>964</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>881</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>929</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>930</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="G17" s="21" t="s">
+        <v>965</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>966</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="G17" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>931</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>932</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>932</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>933</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>934</v>
-      </c>
-      <c r="M17" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="N17" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="O17" s="19" t="s">
+      <c r="H17" s="21" t="s">
+        <v>967</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>968</v>
+      </c>
+      <c r="J17" s="21" t="s">
+        <v>968</v>
+      </c>
+      <c r="K17" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>970</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="N17" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="O17" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="P17" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q17" s="21" t="s">
+      <c r="P17" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R17" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="S17" s="21" t="s">
+      <c r="R17" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="S17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="T17" s="21" t="s">
+      <c r="T17" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="U17" s="21" t="s">
+      <c r="U17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="V17" s="21" t="s">
+      <c r="V17" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="W17" s="21" t="s">
+      <c r="W17" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="X17" s="21" t="s">
+      <c r="X17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="Y17" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z17" s="19" t="s">
+      <c r="Y17" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z17" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="AA17" s="21" t="s">
-        <v>935</v>
-      </c>
-      <c r="AB17" s="21" t="s">
+      <c r="AA17" s="20" t="s">
+        <v>971</v>
+      </c>
+      <c r="AB17" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="AC17" s="21" t="s">
+      <c r="AC17" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="AD17" s="21" t="s">
+      <c r="AD17" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="AE17" s="21" t="s">
+      <c r="AE17" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="AF17" s="21" t="s">
+      <c r="AF17" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="AG17" s="21" t="s">
+      <c r="AG17" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="AH17" s="21" t="s">
+      <c r="AH17" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="AI17" s="21" t="s">
+      <c r="AI17" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="AJ17" s="21" t="s">
+      <c r="AJ17" s="20" t="s">
         <v>35</v>
       </c>
       <c r="AK17" s="1" t="s">
@@ -10593,7 +10938,7 @@
         <v>38</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AO17" s="1" t="s">
         <v>40</v>
@@ -10601,13 +10946,13 @@
       <c r="AP17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ17" s="21" t="s">
+      <c r="AQ17" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="AR17" s="21" t="s">
+      <c r="AR17" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="AS17" s="21" t="s">
+      <c r="AS17" s="20" t="s">
         <v>44</v>
       </c>
       <c r="AT17" s="1" t="s">
@@ -10620,7 +10965,7 @@
         <v>47</v>
       </c>
       <c r="AW17" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="AX17" s="1" t="s">
         <v>49</v>
@@ -10665,10 +11010,10 @@
         <v>62</v>
       </c>
       <c r="BL17" s="1" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="BM17" s="1" t="s">
-        <v>64</v>
+        <v>308</v>
       </c>
       <c r="BN17" s="1" t="s">
         <v>65</v>
@@ -10685,465 +11030,489 @@
       <c r="BR17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS17" s="21" t="s">
-        <v>936</v>
-      </c>
-      <c r="BT17" s="1" t="s">
-        <v>71</v>
+      <c r="BS17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT17" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="BU17" s="1" t="s">
-        <v>259</v>
+        <v>72</v>
       </c>
       <c r="BV17" s="1" t="s">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="BW17" s="1" t="s">
         <v>74</v>
       </c>
       <c r="BX17" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="BY17" s="21" t="s">
-        <v>938</v>
-      </c>
-      <c r="BZ17" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="CA17" s="21" t="s">
-        <v>940</v>
-      </c>
-      <c r="CB17" s="21" t="s">
-        <v>941</v>
-      </c>
-      <c r="CC17" s="21" t="s">
-        <v>942</v>
-      </c>
-      <c r="CD17" s="21" t="s">
-        <v>943</v>
-      </c>
-      <c r="CE17" s="1" t="s">
-        <v>944</v>
+        <v>75</v>
+      </c>
+      <c r="BY17" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="BZ17" s="20" t="s">
+        <v>974</v>
+      </c>
+      <c r="CA17" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="CB17" s="20" t="s">
+        <v>976</v>
+      </c>
+      <c r="CC17" s="20" t="s">
+        <v>977</v>
+      </c>
+      <c r="CD17" s="20" t="s">
+        <v>978</v>
+      </c>
+      <c r="CE17" s="20" t="s">
+        <v>979</v>
       </c>
       <c r="CF17" s="1" t="s">
-        <v>945</v>
+        <v>980</v>
       </c>
       <c r="CG17" s="1" t="s">
-        <v>314</v>
+        <v>981</v>
       </c>
       <c r="CH17" s="1" t="s">
-        <v>85</v>
+        <v>324</v>
       </c>
       <c r="CI17" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ17" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="CK17" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="CL17" s="0" t="s">
+      <c r="CJ17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="CL17" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="CM17" s="0" t="s">
+      <c r="CM17" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="CN17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO17" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="CP17" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="CQ17" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
-        <v>946</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>947</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>848</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>929</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>948</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="23" t="s">
+      <c r="A18" s="19" t="s">
+        <v>982</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>983</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>881</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>965</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>984</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>985</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>986</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>987</v>
+      </c>
+      <c r="L18" s="22" t="s">
+        <v>988</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="O18" s="19" t="s">
+        <v>989</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>990</v>
+      </c>
+      <c r="Q18" s="19" t="s">
+        <v>991</v>
+      </c>
+      <c r="R18" s="19" t="s">
+        <v>992</v>
+      </c>
+      <c r="S18" s="19" t="s">
+        <v>745</v>
+      </c>
+      <c r="T18" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="U18" s="19" t="s">
+        <v>993</v>
+      </c>
+      <c r="V18" s="19" t="s">
+        <v>994</v>
+      </c>
+      <c r="W18" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="X18" s="19" t="s">
+        <v>995</v>
+      </c>
+      <c r="Y18" s="19" t="s">
+        <v>747</v>
+      </c>
+      <c r="Z18" s="19" t="s">
+        <v>996</v>
+      </c>
+      <c r="AA18" s="19" t="s">
+        <v>997</v>
+      </c>
+      <c r="AB18" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="AC18" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD18" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="AE18" s="20" t="s">
+        <v>751</v>
+      </c>
+      <c r="AF18" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="AG18" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH18" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="AI18" s="19" t="s">
+        <v>1001</v>
+      </c>
+      <c r="AJ18" s="19" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AK18" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="AL18" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="AP18" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="AQ18" s="19" t="s">
+        <v>1006</v>
+      </c>
+      <c r="AR18" s="19" t="s">
+        <v>762</v>
+      </c>
+      <c r="AS18" s="19" t="s">
+        <v>1007</v>
+      </c>
+      <c r="AT18" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="AU18" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="AV18" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AW18" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="AX18" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="AY18" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="AZ18" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="BA18" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="BB18" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="BC18" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="BD18" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="BE18" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="BF18" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="BG18" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="BH18" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="BI18" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="BJ18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="BK18" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="BL18" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="BM18" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="BN18" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="BO18" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="BP18" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="BQ18" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="BR18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS18" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="BT18" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU18" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="BV18" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="BW18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX18" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="BY18" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="BZ18" s="19" t="s">
+        <v>1026</v>
+      </c>
+      <c r="CA18" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="I18" s="20" t="s">
-        <v>950</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>950</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>951</v>
-      </c>
-      <c r="L18" s="23" t="s">
-        <v>952</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="N18" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="O18" s="20" t="s">
-        <v>953</v>
-      </c>
-      <c r="P18" s="20" t="s">
-        <v>954</v>
-      </c>
-      <c r="Q18" s="20" t="s">
-        <v>955</v>
-      </c>
-      <c r="R18" s="20" t="s">
-        <v>956</v>
-      </c>
-      <c r="S18" s="20" t="s">
-        <v>717</v>
-      </c>
-      <c r="T18" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="U18" s="20" t="s">
-        <v>957</v>
-      </c>
-      <c r="V18" s="20" t="s">
-        <v>958</v>
-      </c>
-      <c r="W18" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="X18" s="20" t="s">
-        <v>959</v>
-      </c>
-      <c r="Y18" s="20" t="s">
-        <v>719</v>
-      </c>
-      <c r="Z18" s="20" t="s">
-        <v>960</v>
-      </c>
-      <c r="AA18" s="20" t="s">
-        <v>961</v>
-      </c>
-      <c r="AB18" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="AC18" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="AD18" s="20" t="s">
-        <v>962</v>
-      </c>
-      <c r="AE18" s="21" t="s">
-        <v>723</v>
-      </c>
-      <c r="AF18" s="20" t="s">
-        <v>963</v>
-      </c>
-      <c r="AG18" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH18" s="20" t="s">
-        <v>964</v>
-      </c>
-      <c r="AI18" s="20" t="s">
-        <v>965</v>
-      </c>
-      <c r="AJ18" s="20" t="s">
-        <v>966</v>
-      </c>
-      <c r="AK18" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="AL18" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="AM18" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="AN18" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="AO18" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="AP18" s="1" t="s">
-        <v>969</v>
-      </c>
-      <c r="AQ18" s="20" t="s">
-        <v>970</v>
-      </c>
-      <c r="AR18" s="20" t="s">
-        <v>734</v>
-      </c>
-      <c r="AS18" s="20" t="s">
-        <v>971</v>
-      </c>
-      <c r="AT18" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="AU18" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="AV18" s="1" t="s">
-        <v>972</v>
-      </c>
-      <c r="AW18" s="1" t="s">
-        <v>973</v>
-      </c>
-      <c r="AX18" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="AY18" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="AZ18" s="1" t="s">
-        <v>974</v>
-      </c>
-      <c r="BA18" s="1" t="s">
-        <v>975</v>
-      </c>
-      <c r="BB18" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="BC18" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="BD18" s="1" t="s">
-        <v>976</v>
-      </c>
-      <c r="BE18" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="BF18" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="BG18" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="BH18" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="BI18" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="BJ18" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="BK18" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="BL18" s="1" t="s">
-        <v>980</v>
-      </c>
-      <c r="BM18" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="BN18" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="BO18" s="1" t="s">
-        <v>983</v>
-      </c>
-      <c r="BP18" s="1" t="s">
-        <v>984</v>
-      </c>
-      <c r="BQ18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR18" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="BS18" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT18" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="BU18" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="BV18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW18" s="1" t="s">
-        <v>988</v>
-      </c>
-      <c r="BX18" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="BY18" s="20" t="s">
-        <v>990</v>
-      </c>
-      <c r="BZ18" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="CA18" s="20" t="s">
-        <v>991</v>
-      </c>
-      <c r="CB18" s="20" t="s">
-        <v>992</v>
-      </c>
-      <c r="CC18" s="20" t="s">
-        <v>993</v>
-      </c>
-      <c r="CD18" s="20" t="s">
-        <v>994</v>
-      </c>
-      <c r="CE18" s="1" t="s">
-        <v>995</v>
+      <c r="CB18" s="19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="CC18" s="19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="CD18" s="19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="CE18" s="19" t="s">
+        <v>1030</v>
       </c>
       <c r="CF18" s="1" t="s">
-        <v>996</v>
+        <v>1031</v>
       </c>
       <c r="CG18" s="1" t="s">
-        <v>997</v>
+        <v>1032</v>
       </c>
       <c r="CH18" s="1" t="s">
-        <v>85</v>
+        <v>1033</v>
       </c>
       <c r="CI18" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="CJ18" s="0" t="s">
-        <v>999</v>
-      </c>
-      <c r="CK18" s="0" t="s">
-        <v>1000</v>
-      </c>
-      <c r="CL18" s="0" t="s">
-        <v>1001</v>
-      </c>
-      <c r="CM18" s="0" t="s">
-        <v>1002</v>
+        <v>86</v>
+      </c>
+      <c r="CJ18" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="CK18" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="CL18" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="CM18" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="CN18" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="CO18" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP18" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="CQ18" s="1" t="s">
+        <v>1040</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>848</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>929</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>930</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="20" t="s">
+      <c r="A19" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>881</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>965</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>966</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="24" t="s">
-        <v>931</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>932</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>932</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>933</v>
-      </c>
-      <c r="L19" s="22" t="s">
-        <v>934</v>
-      </c>
-      <c r="M19" s="20" t="s">
-        <v>1005</v>
-      </c>
-      <c r="N19" s="20" t="s">
+      <c r="H19" s="23" t="s">
+        <v>967</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>968</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>968</v>
+      </c>
+      <c r="K19" s="21" t="s">
+        <v>969</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>970</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N19" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="O19" s="20" t="s">
+      <c r="O19" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q19" s="20" t="s">
+      <c r="P19" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q19" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="R19" s="20" t="s">
+      <c r="R19" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="S19" s="20" t="s">
+      <c r="S19" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="T19" s="20" t="s">
+      <c r="T19" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="20" t="s">
+      <c r="U19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="V19" s="20" t="s">
+      <c r="V19" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="W19" s="20" t="s">
+      <c r="W19" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="X19" s="20" t="s">
-        <v>1006</v>
-      </c>
-      <c r="Y19" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z19" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="AA19" s="20" t="s">
-        <v>1007</v>
-      </c>
-      <c r="AB19" s="20" t="s">
+      <c r="X19" s="19" t="s">
+        <v>1044</v>
+      </c>
+      <c r="Y19" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z19" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="AA19" s="19" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AB19" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="AC19" s="20" t="s">
+      <c r="AC19" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="AD19" s="20" t="s">
-        <v>1008</v>
-      </c>
-      <c r="AE19" s="20" t="s">
-        <v>1009</v>
-      </c>
-      <c r="AF19" s="21" t="s">
+      <c r="AD19" s="19" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AE19" s="19" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AF19" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="AG19" s="21" t="s">
+      <c r="AG19" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="AH19" s="21" t="s">
+      <c r="AH19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="AI19" s="21" t="s">
-        <v>1010</v>
-      </c>
-      <c r="AJ19" s="21" t="s">
+      <c r="AI19" s="20" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AJ19" s="20" t="s">
         <v>35</v>
       </c>
       <c r="AK19" s="1" t="s">
         <v>34</v>
       </c>
       <c r="AL19" s="1" t="s">
-        <v>1011</v>
+        <v>1049</v>
       </c>
       <c r="AM19" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>1012</v>
+        <v>1050</v>
       </c>
       <c r="AO19" s="1" t="s">
         <v>40</v>
@@ -11151,13 +11520,13 @@
       <c r="AP19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ19" s="21" t="s">
+      <c r="AQ19" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="AR19" s="21" t="s">
+      <c r="AR19" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="AS19" s="21" t="s">
+      <c r="AS19" s="20" t="s">
         <v>44</v>
       </c>
       <c r="AT19" s="1" t="s">
@@ -11170,7 +11539,7 @@
         <v>46</v>
       </c>
       <c r="AW19" s="1" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="AX19" s="1" t="s">
         <v>49</v>
@@ -11200,13 +11569,13 @@
         <v>57</v>
       </c>
       <c r="BG19" s="1" t="s">
-        <v>1013</v>
+        <v>1051</v>
       </c>
       <c r="BH19" s="1" t="s">
-        <v>1013</v>
+        <v>1051</v>
       </c>
       <c r="BI19" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="BJ19" s="1" t="s">
         <v>61</v>
@@ -11215,361 +11584,385 @@
         <v>62</v>
       </c>
       <c r="BL19" s="1" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="BM19" s="1" t="s">
-        <v>1014</v>
+        <v>308</v>
       </c>
       <c r="BN19" s="1" t="s">
-        <v>65</v>
+        <v>1052</v>
       </c>
       <c r="BO19" s="1" t="s">
         <v>66</v>
       </c>
       <c r="BP19" s="1" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="BQ19" s="1" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="BR19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BS19" s="21" t="s">
+      <c r="BS19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BT19" s="1" t="s">
-        <v>1015</v>
+      <c r="BT19" s="20" t="s">
+        <v>71</v>
       </c>
       <c r="BU19" s="1" t="s">
-        <v>1016</v>
+        <v>1053</v>
       </c>
       <c r="BV19" s="1" t="s">
-        <v>1017</v>
+        <v>1054</v>
       </c>
       <c r="BW19" s="1" t="s">
-        <v>1018</v>
+        <v>1055</v>
       </c>
       <c r="BX19" s="1" t="s">
-        <v>1019</v>
-      </c>
-      <c r="BY19" s="21" t="s">
-        <v>1020</v>
-      </c>
-      <c r="BZ19" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="CA19" s="20" t="s">
-        <v>1021</v>
-      </c>
-      <c r="CB19" s="21" t="s">
-        <v>1022</v>
-      </c>
-      <c r="CC19" s="21" t="s">
-        <v>1023</v>
+        <v>1056</v>
+      </c>
+      <c r="BY19" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="BZ19" s="20" t="s">
+        <v>1058</v>
+      </c>
+      <c r="CA19" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="CB19" s="19" t="s">
+        <v>1059</v>
+      </c>
+      <c r="CC19" s="20" t="s">
+        <v>1060</v>
       </c>
       <c r="CD19" s="20" t="s">
-        <v>1024</v>
-      </c>
-      <c r="CE19" s="1" t="s">
-        <v>1025</v>
+        <v>1061</v>
+      </c>
+      <c r="CE19" s="19" t="s">
+        <v>1062</v>
       </c>
       <c r="CF19" s="1" t="s">
-        <v>1026</v>
+        <v>1063</v>
       </c>
       <c r="CG19" s="1" t="s">
-        <v>314</v>
+        <v>1064</v>
       </c>
       <c r="CH19" s="1" t="s">
-        <v>1027</v>
+        <v>324</v>
       </c>
       <c r="CI19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CJ19" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="CK19" s="0" t="s">
-        <v>1028</v>
-      </c>
-      <c r="CL19" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="CM19" s="0" t="s">
+        <v>1065</v>
+      </c>
+      <c r="CJ19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK19" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="CL19" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="CM19" s="1" t="s">
         <v>90</v>
+      </c>
+      <c r="CN19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="CP19" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="CQ19" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>1034</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>1036</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="L20" s="21" t="s">
-        <v>1038</v>
-      </c>
-      <c r="M20" s="21" t="s">
-        <v>1039</v>
-      </c>
-      <c r="N20" s="21" t="s">
-        <v>1040</v>
-      </c>
-      <c r="O20" s="19" t="s">
-        <v>1041</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="Q20" s="21" t="s">
-        <v>1043</v>
-      </c>
-      <c r="R20" s="21" t="s">
-        <v>407</v>
-      </c>
-      <c r="S20" s="21" t="s">
+      <c r="A20" s="19" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>1078</v>
+      </c>
+      <c r="N20" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>1080</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>1081</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>1082</v>
+      </c>
+      <c r="R20" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="S20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="T20" s="21" t="s">
+      <c r="T20" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="U20" s="21" t="s">
-        <v>1044</v>
-      </c>
-      <c r="V20" s="21" t="s">
-        <v>1045</v>
-      </c>
-      <c r="W20" s="21" t="s">
-        <v>1046</v>
-      </c>
-      <c r="X20" s="21" t="s">
-        <v>1047</v>
-      </c>
-      <c r="Y20" s="19" t="s">
-        <v>1048</v>
-      </c>
-      <c r="Z20" s="19" t="s">
-        <v>1049</v>
-      </c>
-      <c r="AA20" s="21" t="s">
-        <v>1050</v>
-      </c>
-      <c r="AB20" s="21" t="s">
-        <v>1051</v>
-      </c>
-      <c r="AC20" s="21" t="s">
-        <v>1052</v>
-      </c>
-      <c r="AD20" s="21" t="s">
-        <v>1053</v>
-      </c>
-      <c r="AE20" s="21" t="s">
-        <v>1054</v>
-      </c>
-      <c r="AF20" s="21" t="s">
-        <v>1055</v>
-      </c>
-      <c r="AG20" s="21" t="s">
+      <c r="U20" s="20" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V20" s="20" t="s">
+        <v>1084</v>
+      </c>
+      <c r="W20" s="20" t="s">
+        <v>1085</v>
+      </c>
+      <c r="X20" s="20" t="s">
+        <v>1086</v>
+      </c>
+      <c r="Y20" s="18" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Z20" s="18" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AA20" s="20" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AB20" s="20" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AC20" s="20" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AD20" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AE20" s="20" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AF20" s="20" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AG20" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="AH20" s="21" t="s">
-        <v>1056</v>
-      </c>
-      <c r="AI20" s="21" t="s">
-        <v>1057</v>
-      </c>
-      <c r="AJ20" s="21" t="s">
-        <v>1058</v>
+      <c r="AH20" s="20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AI20" s="20" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AJ20" s="20" t="s">
+        <v>1097</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>1059</v>
+        <v>1098</v>
       </c>
       <c r="AL20" s="1" t="s">
-        <v>1060</v>
+        <v>1099</v>
       </c>
       <c r="AM20" s="1" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>1062</v>
+        <v>1101</v>
       </c>
       <c r="AO20" s="1" t="s">
-        <v>1063</v>
+        <v>1102</v>
       </c>
       <c r="AP20" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AQ20" s="21" t="s">
-        <v>1065</v>
-      </c>
-      <c r="AR20" s="21" t="s">
-        <v>1066</v>
-      </c>
-      <c r="AS20" s="21" t="s">
-        <v>1067</v>
+        <v>1103</v>
+      </c>
+      <c r="AQ20" s="20" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AR20" s="20" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AS20" s="20" t="s">
+        <v>1106</v>
       </c>
       <c r="AT20" s="1" t="s">
-        <v>1068</v>
+        <v>1107</v>
       </c>
       <c r="AU20" s="1" t="s">
-        <v>1069</v>
+        <v>1108</v>
       </c>
       <c r="AV20" s="1" t="s">
-        <v>1070</v>
+        <v>1109</v>
       </c>
       <c r="AW20" s="1" t="s">
-        <v>1071</v>
+        <v>1110</v>
       </c>
       <c r="AX20" s="1" t="s">
-        <v>1072</v>
+        <v>1111</v>
       </c>
       <c r="AY20" s="1" t="s">
-        <v>1073</v>
+        <v>1112</v>
       </c>
       <c r="AZ20" s="1" t="s">
-        <v>1074</v>
+        <v>1113</v>
       </c>
       <c r="BA20" s="1" t="s">
-        <v>1075</v>
+        <v>1114</v>
       </c>
       <c r="BB20" s="1" t="s">
-        <v>1076</v>
+        <v>1115</v>
       </c>
       <c r="BC20" s="1" t="s">
         <v>54</v>
       </c>
       <c r="BD20" s="1" t="s">
-        <v>1077</v>
+        <v>1116</v>
       </c>
       <c r="BE20" s="1" t="s">
-        <v>1069</v>
+        <v>1108</v>
       </c>
       <c r="BF20" s="1" t="s">
         <v>57</v>
       </c>
       <c r="BG20" s="1" t="s">
-        <v>1078</v>
+        <v>1117</v>
       </c>
       <c r="BH20" s="1" t="s">
-        <v>1079</v>
+        <v>1118</v>
       </c>
       <c r="BI20" s="1" t="s">
-        <v>1080</v>
+        <v>1119</v>
       </c>
       <c r="BJ20" s="1" t="s">
-        <v>1081</v>
+        <v>1120</v>
       </c>
       <c r="BK20" s="1" t="s">
-        <v>1082</v>
+        <v>1121</v>
       </c>
       <c r="BL20" s="1" t="s">
-        <v>1083</v>
+        <v>1122</v>
       </c>
       <c r="BM20" s="1" t="s">
-        <v>1084</v>
+        <v>1123</v>
       </c>
       <c r="BN20" s="1" t="s">
-        <v>1085</v>
+        <v>1124</v>
       </c>
       <c r="BO20" s="1" t="s">
-        <v>1086</v>
+        <v>1125</v>
       </c>
       <c r="BP20" s="1" t="s">
-        <v>1087</v>
+        <v>1126</v>
       </c>
       <c r="BQ20" s="1" t="s">
-        <v>68</v>
+        <v>1127</v>
       </c>
       <c r="BR20" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="BS20" s="21" t="s">
-        <v>1089</v>
-      </c>
-      <c r="BT20" s="1" t="s">
-        <v>1090</v>
+        <v>69</v>
+      </c>
+      <c r="BS20" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="BT20" s="20" t="s">
+        <v>1129</v>
       </c>
       <c r="BU20" s="1" t="s">
-        <v>1091</v>
+        <v>1130</v>
       </c>
       <c r="BV20" s="1" t="s">
-        <v>1092</v>
+        <v>1131</v>
       </c>
       <c r="BW20" s="1" t="s">
-        <v>1093</v>
+        <v>1132</v>
       </c>
       <c r="BX20" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="BY20" s="21" t="s">
-        <v>1095</v>
-      </c>
-      <c r="BZ20" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="CA20" s="22" t="s">
-        <v>1097</v>
+        <v>1133</v>
+      </c>
+      <c r="BY20" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="BZ20" s="20" t="s">
+        <v>1135</v>
+      </c>
+      <c r="CA20" s="1" t="s">
+        <v>1136</v>
       </c>
       <c r="CB20" s="21" t="s">
-        <v>1098</v>
-      </c>
-      <c r="CC20" s="21" t="s">
-        <v>1099</v>
-      </c>
-      <c r="CD20" s="21" t="s">
-        <v>1100</v>
-      </c>
-      <c r="CE20" s="1" t="s">
-        <v>1101</v>
+        <v>1137</v>
+      </c>
+      <c r="CC20" s="20" t="s">
+        <v>1138</v>
+      </c>
+      <c r="CD20" s="20" t="s">
+        <v>1139</v>
+      </c>
+      <c r="CE20" s="20" t="s">
+        <v>1140</v>
       </c>
       <c r="CF20" s="1" t="s">
-        <v>1102</v>
+        <v>1141</v>
       </c>
       <c r="CG20" s="1" t="s">
-        <v>1103</v>
+        <v>1142</v>
       </c>
       <c r="CH20" s="1" t="s">
-        <v>1104</v>
+        <v>1143</v>
       </c>
       <c r="CI20" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="CJ20" s="0" t="s">
-        <v>1106</v>
-      </c>
-      <c r="CK20" s="0" t="s">
+        <v>1144</v>
+      </c>
+      <c r="CJ20" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="CK20" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="CL20" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="CM20" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="CN20" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="CO20" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="CP20" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="CL20" s="0" t="s">
-        <v>1108</v>
-      </c>
-      <c r="CM20" s="0" t="s">
-        <v>1109</v>
+      <c r="CQ20" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11655,6 +12048,7 @@
       <c r="CB21" s="6"/>
       <c r="CC21" s="6"/>
       <c r="CD21" s="6"/>
+      <c r="CE21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
@@ -11739,6 +12133,7 @@
       <c r="CB22" s="6"/>
       <c r="CC22" s="6"/>
       <c r="CD22" s="6"/>
+      <c r="CE22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
@@ -11823,6 +12218,7 @@
       <c r="CB23" s="6"/>
       <c r="CC23" s="6"/>
       <c r="CD23" s="6"/>
+      <c r="CE23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6"/>
@@ -11907,6 +12303,7 @@
       <c r="CB24" s="6"/>
       <c r="CC24" s="6"/>
       <c r="CD24" s="6"/>
+      <c r="CE24" s="6"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6"/>
@@ -11991,6 +12388,7 @@
       <c r="CB25" s="6"/>
       <c r="CC25" s="6"/>
       <c r="CD25" s="6"/>
+      <c r="CE25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -12075,6 +12473,7 @@
       <c r="CB26" s="6"/>
       <c r="CC26" s="6"/>
       <c r="CD26" s="6"/>
+      <c r="CE26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6"/>
@@ -12159,6 +12558,7 @@
       <c r="CB27" s="6"/>
       <c r="CC27" s="6"/>
       <c r="CD27" s="6"/>
+      <c r="CE27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -12243,6 +12643,7 @@
       <c r="CB28" s="6"/>
       <c r="CC28" s="6"/>
       <c r="CD28" s="6"/>
+      <c r="CE28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
@@ -12327,6 +12728,7 @@
       <c r="CB29" s="6"/>
       <c r="CC29" s="6"/>
       <c r="CD29" s="6"/>
+      <c r="CE29" s="6"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -12411,6 +12813,7 @@
       <c r="CB30" s="6"/>
       <c r="CC30" s="6"/>
       <c r="CD30" s="6"/>
+      <c r="CE30" s="6"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6"/>
@@ -12495,6 +12898,7 @@
       <c r="CB31" s="6"/>
       <c r="CC31" s="6"/>
       <c r="CD31" s="6"/>
+      <c r="CE31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -12579,6 +12983,7 @@
       <c r="CB32" s="6"/>
       <c r="CC32" s="6"/>
       <c r="CD32" s="6"/>
+      <c r="CE32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6"/>
@@ -12663,6 +13068,7 @@
       <c r="CB33" s="6"/>
       <c r="CC33" s="6"/>
       <c r="CD33" s="6"/>
+      <c r="CE33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -12747,6 +13153,7 @@
       <c r="CB34" s="6"/>
       <c r="CC34" s="6"/>
       <c r="CD34" s="6"/>
+      <c r="CE34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6"/>
@@ -12831,6 +13238,7 @@
       <c r="CB35" s="6"/>
       <c r="CC35" s="6"/>
       <c r="CD35" s="6"/>
+      <c r="CE35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -12915,6 +13323,7 @@
       <c r="CB36" s="6"/>
       <c r="CC36" s="6"/>
       <c r="CD36" s="6"/>
+      <c r="CE36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6"/>
@@ -12999,6 +13408,7 @@
       <c r="CB37" s="6"/>
       <c r="CC37" s="6"/>
       <c r="CD37" s="6"/>
+      <c r="CE37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -13083,6 +13493,7 @@
       <c r="CB38" s="6"/>
       <c r="CC38" s="6"/>
       <c r="CD38" s="6"/>
+      <c r="CE38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6"/>
@@ -13167,6 +13578,7 @@
       <c r="CB39" s="6"/>
       <c r="CC39" s="6"/>
       <c r="CD39" s="6"/>
+      <c r="CE39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6"/>
@@ -13251,6 +13663,7 @@
       <c r="CB40" s="6"/>
       <c r="CC40" s="6"/>
       <c r="CD40" s="6"/>
+      <c r="CE40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6"/>
@@ -13335,6 +13748,7 @@
       <c r="CB41" s="6"/>
       <c r="CC41" s="6"/>
       <c r="CD41" s="6"/>
+      <c r="CE41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6"/>
@@ -13419,6 +13833,7 @@
       <c r="CB42" s="6"/>
       <c r="CC42" s="6"/>
       <c r="CD42" s="6"/>
+      <c r="CE42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6"/>
@@ -13503,6 +13918,7 @@
       <c r="CB43" s="6"/>
       <c r="CC43" s="6"/>
       <c r="CD43" s="6"/>
+      <c r="CE43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6"/>
@@ -13587,6 +14003,7 @@
       <c r="CB44" s="6"/>
       <c r="CC44" s="6"/>
       <c r="CD44" s="6"/>
+      <c r="CE44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -13671,6 +14088,7 @@
       <c r="CB45" s="6"/>
       <c r="CC45" s="6"/>
       <c r="CD45" s="6"/>
+      <c r="CE45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6"/>
@@ -13755,6 +14173,7 @@
       <c r="CB46" s="6"/>
       <c r="CC46" s="6"/>
       <c r="CD46" s="6"/>
+      <c r="CE46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -13839,6 +14258,7 @@
       <c r="CB47" s="6"/>
       <c r="CC47" s="6"/>
       <c r="CD47" s="6"/>
+      <c r="CE47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6"/>
@@ -13923,6 +14343,7 @@
       <c r="CB48" s="6"/>
       <c r="CC48" s="6"/>
       <c r="CD48" s="6"/>
+      <c r="CE48" s="6"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -14007,6 +14428,7 @@
       <c r="CB49" s="6"/>
       <c r="CC49" s="6"/>
       <c r="CD49" s="6"/>
+      <c r="CE49" s="6"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6"/>
@@ -14091,6 +14513,7 @@
       <c r="CB50" s="6"/>
       <c r="CC50" s="6"/>
       <c r="CD50" s="6"/>
+      <c r="CE50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -14175,6 +14598,7 @@
       <c r="CB51" s="6"/>
       <c r="CC51" s="6"/>
       <c r="CD51" s="6"/>
+      <c r="CE51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6"/>
@@ -14259,6 +14683,7 @@
       <c r="CB52" s="6"/>
       <c r="CC52" s="6"/>
       <c r="CD52" s="6"/>
+      <c r="CE52" s="6"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -14343,6 +14768,7 @@
       <c r="CB53" s="6"/>
       <c r="CC53" s="6"/>
       <c r="CD53" s="6"/>
+      <c r="CE53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6"/>
@@ -14427,6 +14853,7 @@
       <c r="CB54" s="6"/>
       <c r="CC54" s="6"/>
       <c r="CD54" s="6"/>
+      <c r="CE54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -14511,6 +14938,7 @@
       <c r="CB55" s="6"/>
       <c r="CC55" s="6"/>
       <c r="CD55" s="6"/>
+      <c r="CE55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6"/>
@@ -14595,6 +15023,7 @@
       <c r="CB56" s="6"/>
       <c r="CC56" s="6"/>
       <c r="CD56" s="6"/>
+      <c r="CE56" s="6"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -14679,6 +15108,7 @@
       <c r="CB57" s="6"/>
       <c r="CC57" s="6"/>
       <c r="CD57" s="6"/>
+      <c r="CE57" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6"/>
@@ -14763,6 +15193,7 @@
       <c r="CB58" s="6"/>
       <c r="CC58" s="6"/>
       <c r="CD58" s="6"/>
+      <c r="CE58" s="6"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6"/>
@@ -14847,6 +15278,7 @@
       <c r="CB59" s="6"/>
       <c r="CC59" s="6"/>
       <c r="CD59" s="6"/>
+      <c r="CE59" s="6"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6"/>
@@ -14931,6 +15363,7 @@
       <c r="CB60" s="6"/>
       <c r="CC60" s="6"/>
       <c r="CD60" s="6"/>
+      <c r="CE60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6"/>
@@ -15015,6 +15448,7 @@
       <c r="CB61" s="6"/>
       <c r="CC61" s="6"/>
       <c r="CD61" s="6"/>
+      <c r="CE61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6"/>
@@ -15099,6 +15533,7 @@
       <c r="CB62" s="6"/>
       <c r="CC62" s="6"/>
       <c r="CD62" s="6"/>
+      <c r="CE62" s="6"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6"/>
@@ -15183,6 +15618,7 @@
       <c r="CB63" s="6"/>
       <c r="CC63" s="6"/>
       <c r="CD63" s="6"/>
+      <c r="CE63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -15267,6 +15703,7 @@
       <c r="CB64" s="6"/>
       <c r="CC64" s="6"/>
       <c r="CD64" s="6"/>
+      <c r="CE64" s="6"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6"/>
@@ -15351,6 +15788,7 @@
       <c r="CB65" s="6"/>
       <c r="CC65" s="6"/>
       <c r="CD65" s="6"/>
+      <c r="CE65" s="6"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -15435,6 +15873,7 @@
       <c r="CB66" s="6"/>
       <c r="CC66" s="6"/>
       <c r="CD66" s="6"/>
+      <c r="CE66" s="6"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6"/>
@@ -15519,6 +15958,7 @@
       <c r="CB67" s="6"/>
       <c r="CC67" s="6"/>
       <c r="CD67" s="6"/>
+      <c r="CE67" s="6"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -15603,6 +16043,7 @@
       <c r="CB68" s="6"/>
       <c r="CC68" s="6"/>
       <c r="CD68" s="6"/>
+      <c r="CE68" s="6"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6"/>
@@ -15687,6 +16128,7 @@
       <c r="CB69" s="6"/>
       <c r="CC69" s="6"/>
       <c r="CD69" s="6"/>
+      <c r="CE69" s="6"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -15771,6 +16213,7 @@
       <c r="CB70" s="6"/>
       <c r="CC70" s="6"/>
       <c r="CD70" s="6"/>
+      <c r="CE70" s="6"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6"/>
@@ -15855,6 +16298,7 @@
       <c r="CB71" s="6"/>
       <c r="CC71" s="6"/>
       <c r="CD71" s="6"/>
+      <c r="CE71" s="6"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -15939,6 +16383,7 @@
       <c r="CB72" s="6"/>
       <c r="CC72" s="6"/>
       <c r="CD72" s="6"/>
+      <c r="CE72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6"/>
@@ -16023,6 +16468,7 @@
       <c r="CB73" s="6"/>
       <c r="CC73" s="6"/>
       <c r="CD73" s="6"/>
+      <c r="CE73" s="6"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -16107,6 +16553,7 @@
       <c r="CB74" s="6"/>
       <c r="CC74" s="6"/>
       <c r="CD74" s="6"/>
+      <c r="CE74" s="6"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6"/>
@@ -16191,6 +16638,7 @@
       <c r="CB75" s="6"/>
       <c r="CC75" s="6"/>
       <c r="CD75" s="6"/>
+      <c r="CE75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -16275,6 +16723,7 @@
       <c r="CB76" s="6"/>
       <c r="CC76" s="6"/>
       <c r="CD76" s="6"/>
+      <c r="CE76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6"/>
@@ -16359,6 +16808,7 @@
       <c r="CB77" s="6"/>
       <c r="CC77" s="6"/>
       <c r="CD77" s="6"/>
+      <c r="CE77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="6"/>
@@ -16443,6 +16893,7 @@
       <c r="CB78" s="6"/>
       <c r="CC78" s="6"/>
       <c r="CD78" s="6"/>
+      <c r="CE78" s="6"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="6"/>
@@ -16527,6 +16978,7 @@
       <c r="CB79" s="6"/>
       <c r="CC79" s="6"/>
       <c r="CD79" s="6"/>
+      <c r="CE79" s="6"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="6"/>
@@ -16611,6 +17063,7 @@
       <c r="CB80" s="6"/>
       <c r="CC80" s="6"/>
       <c r="CD80" s="6"/>
+      <c r="CE80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="6"/>
@@ -16695,6 +17148,7 @@
       <c r="CB81" s="6"/>
       <c r="CC81" s="6"/>
       <c r="CD81" s="6"/>
+      <c r="CE81" s="6"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6"/>
@@ -16779,6 +17233,7 @@
       <c r="CB82" s="6"/>
       <c r="CC82" s="6"/>
       <c r="CD82" s="6"/>
+      <c r="CE82" s="6"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="6"/>
@@ -16863,6 +17318,7 @@
       <c r="CB83" s="6"/>
       <c r="CC83" s="6"/>
       <c r="CD83" s="6"/>
+      <c r="CE83" s="6"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6"/>
@@ -16947,6 +17403,7 @@
       <c r="CB84" s="6"/>
       <c r="CC84" s="6"/>
       <c r="CD84" s="6"/>
+      <c r="CE84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="6"/>
@@ -17031,6 +17488,7 @@
       <c r="CB85" s="6"/>
       <c r="CC85" s="6"/>
       <c r="CD85" s="6"/>
+      <c r="CE85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="6"/>
@@ -17115,6 +17573,7 @@
       <c r="CB86" s="6"/>
       <c r="CC86" s="6"/>
       <c r="CD86" s="6"/>
+      <c r="CE86" s="6"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="6"/>
@@ -17199,6 +17658,7 @@
       <c r="CB87" s="6"/>
       <c r="CC87" s="6"/>
       <c r="CD87" s="6"/>
+      <c r="CE87" s="6"/>
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="6"/>
@@ -17283,6 +17743,7 @@
       <c r="CB88" s="6"/>
       <c r="CC88" s="6"/>
       <c r="CD88" s="6"/>
+      <c r="CE88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6"/>
@@ -17367,6 +17828,7 @@
       <c r="CB89" s="6"/>
       <c r="CC89" s="6"/>
       <c r="CD89" s="6"/>
+      <c r="CE89" s="6"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="6"/>
@@ -17451,6 +17913,7 @@
       <c r="CB90" s="6"/>
       <c r="CC90" s="6"/>
       <c r="CD90" s="6"/>
+      <c r="CE90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6"/>
@@ -17535,6 +17998,7 @@
       <c r="CB91" s="6"/>
       <c r="CC91" s="6"/>
       <c r="CD91" s="6"/>
+      <c r="CE91" s="6"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="6"/>
@@ -17619,6 +18083,7 @@
       <c r="CB92" s="6"/>
       <c r="CC92" s="6"/>
       <c r="CD92" s="6"/>
+      <c r="CE92" s="6"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="6"/>
@@ -17703,6 +18168,7 @@
       <c r="CB93" s="6"/>
       <c r="CC93" s="6"/>
       <c r="CD93" s="6"/>
+      <c r="CE93" s="6"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="6"/>
@@ -17787,6 +18253,7 @@
       <c r="CB94" s="6"/>
       <c r="CC94" s="6"/>
       <c r="CD94" s="6"/>
+      <c r="CE94" s="6"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="6"/>
@@ -17871,6 +18338,7 @@
       <c r="CB95" s="6"/>
       <c r="CC95" s="6"/>
       <c r="CD95" s="6"/>
+      <c r="CE95" s="6"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="6"/>
@@ -17955,6 +18423,7 @@
       <c r="CB96" s="6"/>
       <c r="CC96" s="6"/>
       <c r="CD96" s="6"/>
+      <c r="CE96" s="6"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="6"/>
@@ -18039,6 +18508,7 @@
       <c r="CB97" s="6"/>
       <c r="CC97" s="6"/>
       <c r="CD97" s="6"/>
+      <c r="CE97" s="6"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="6"/>
@@ -18123,6 +18593,7 @@
       <c r="CB98" s="6"/>
       <c r="CC98" s="6"/>
       <c r="CD98" s="6"/>
+      <c r="CE98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="6"/>
@@ -18207,6 +18678,7 @@
       <c r="CB99" s="6"/>
       <c r="CC99" s="6"/>
       <c r="CD99" s="6"/>
+      <c r="CE99" s="6"/>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="6"/>
@@ -18291,6 +18763,7 @@
       <c r="CB100" s="6"/>
       <c r="CC100" s="6"/>
       <c r="CD100" s="6"/>
+      <c r="CE100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="6"/>
@@ -18375,6 +18848,7 @@
       <c r="CB101" s="6"/>
       <c r="CC101" s="6"/>
       <c r="CD101" s="6"/>
+      <c r="CE101" s="6"/>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="6"/>
@@ -18459,6 +18933,7 @@
       <c r="CB102" s="6"/>
       <c r="CC102" s="6"/>
       <c r="CD102" s="6"/>
+      <c r="CE102" s="6"/>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="6"/>
@@ -18543,6 +19018,7 @@
       <c r="CB103" s="6"/>
       <c r="CC103" s="6"/>
       <c r="CD103" s="6"/>
+      <c r="CE103" s="6"/>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6"/>
@@ -18627,6 +19103,7 @@
       <c r="CB104" s="6"/>
       <c r="CC104" s="6"/>
       <c r="CD104" s="6"/>
+      <c r="CE104" s="6"/>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="6"/>
@@ -18711,6 +19188,7 @@
       <c r="CB105" s="6"/>
       <c r="CC105" s="6"/>
       <c r="CD105" s="6"/>
+      <c r="CE105" s="6"/>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="6"/>
@@ -18795,6 +19273,7 @@
       <c r="CB106" s="6"/>
       <c r="CC106" s="6"/>
       <c r="CD106" s="6"/>
+      <c r="CE106" s="6"/>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="6"/>
@@ -18879,6 +19358,7 @@
       <c r="CB107" s="6"/>
       <c r="CC107" s="6"/>
       <c r="CD107" s="6"/>
+      <c r="CE107" s="6"/>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="6"/>
@@ -18963,6 +19443,7 @@
       <c r="CB108" s="6"/>
       <c r="CC108" s="6"/>
       <c r="CD108" s="6"/>
+      <c r="CE108" s="6"/>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="6"/>
@@ -19047,6 +19528,7 @@
       <c r="CB109" s="6"/>
       <c r="CC109" s="6"/>
       <c r="CD109" s="6"/>
+      <c r="CE109" s="6"/>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="6"/>
@@ -19131,6 +19613,7 @@
       <c r="CB110" s="6"/>
       <c r="CC110" s="6"/>
       <c r="CD110" s="6"/>
+      <c r="CE110" s="6"/>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="6"/>
@@ -19215,6 +19698,7 @@
       <c r="CB111" s="6"/>
       <c r="CC111" s="6"/>
       <c r="CD111" s="6"/>
+      <c r="CE111" s="6"/>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6"/>
@@ -19299,6 +19783,7 @@
       <c r="CB112" s="6"/>
       <c r="CC112" s="6"/>
       <c r="CD112" s="6"/>
+      <c r="CE112" s="6"/>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="6"/>
@@ -19383,6 +19868,7 @@
       <c r="CB113" s="6"/>
       <c r="CC113" s="6"/>
       <c r="CD113" s="6"/>
+      <c r="CE113" s="6"/>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6"/>
@@ -19467,6 +19953,7 @@
       <c r="CB114" s="6"/>
       <c r="CC114" s="6"/>
       <c r="CD114" s="6"/>
+      <c r="CE114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="6"/>
@@ -19551,6 +20038,7 @@
       <c r="CB115" s="6"/>
       <c r="CC115" s="6"/>
       <c r="CD115" s="6"/>
+      <c r="CE115" s="6"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6"/>
@@ -19635,6 +20123,7 @@
       <c r="CB116" s="6"/>
       <c r="CC116" s="6"/>
       <c r="CD116" s="6"/>
+      <c r="CE116" s="6"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="6"/>
@@ -19719,6 +20208,7 @@
       <c r="CB117" s="6"/>
       <c r="CC117" s="6"/>
       <c r="CD117" s="6"/>
+      <c r="CE117" s="6"/>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="6"/>
@@ -19803,6 +20293,7 @@
       <c r="CB118" s="6"/>
       <c r="CC118" s="6"/>
       <c r="CD118" s="6"/>
+      <c r="CE118" s="6"/>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="6"/>
@@ -19887,6 +20378,7 @@
       <c r="CB119" s="6"/>
       <c r="CC119" s="6"/>
       <c r="CD119" s="6"/>
+      <c r="CE119" s="6"/>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6"/>
@@ -19971,6 +20463,7 @@
       <c r="CB120" s="6"/>
       <c r="CC120" s="6"/>
       <c r="CD120" s="6"/>
+      <c r="CE120" s="6"/>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="6"/>
@@ -20055,6 +20548,7 @@
       <c r="CB121" s="6"/>
       <c r="CC121" s="6"/>
       <c r="CD121" s="6"/>
+      <c r="CE121" s="6"/>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="6"/>
@@ -20139,6 +20633,7 @@
       <c r="CB122" s="6"/>
       <c r="CC122" s="6"/>
       <c r="CD122" s="6"/>
+      <c r="CE122" s="6"/>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="6"/>
@@ -20223,6 +20718,7 @@
       <c r="CB123" s="6"/>
       <c r="CC123" s="6"/>
       <c r="CD123" s="6"/>
+      <c r="CE123" s="6"/>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6"/>
@@ -20307,6 +20803,7 @@
       <c r="CB124" s="6"/>
       <c r="CC124" s="6"/>
       <c r="CD124" s="6"/>
+      <c r="CE124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="6"/>
@@ -20391,6 +20888,7 @@
       <c r="CB125" s="6"/>
       <c r="CC125" s="6"/>
       <c r="CD125" s="6"/>
+      <c r="CE125" s="6"/>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6"/>
@@ -20475,6 +20973,7 @@
       <c r="CB126" s="6"/>
       <c r="CC126" s="6"/>
       <c r="CD126" s="6"/>
+      <c r="CE126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="6"/>
@@ -20559,6 +21058,7 @@
       <c r="CB127" s="6"/>
       <c r="CC127" s="6"/>
       <c r="CD127" s="6"/>
+      <c r="CE127" s="6"/>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6"/>
@@ -20643,6 +21143,7 @@
       <c r="CB128" s="6"/>
       <c r="CC128" s="6"/>
       <c r="CD128" s="6"/>
+      <c r="CE128" s="6"/>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="6"/>
@@ -20727,6 +21228,7 @@
       <c r="CB129" s="6"/>
       <c r="CC129" s="6"/>
       <c r="CD129" s="6"/>
+      <c r="CE129" s="6"/>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6"/>
@@ -20811,6 +21313,7 @@
       <c r="CB130" s="6"/>
       <c r="CC130" s="6"/>
       <c r="CD130" s="6"/>
+      <c r="CE130" s="6"/>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="6"/>
@@ -20895,6 +21398,7 @@
       <c r="CB131" s="6"/>
       <c r="CC131" s="6"/>
       <c r="CD131" s="6"/>
+      <c r="CE131" s="6"/>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6"/>
@@ -20979,6 +21483,7 @@
       <c r="CB132" s="6"/>
       <c r="CC132" s="6"/>
       <c r="CD132" s="6"/>
+      <c r="CE132" s="6"/>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="6"/>
@@ -21063,6 +21568,7 @@
       <c r="CB133" s="6"/>
       <c r="CC133" s="6"/>
       <c r="CD133" s="6"/>
+      <c r="CE133" s="6"/>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6"/>
@@ -21147,6 +21653,7 @@
       <c r="CB134" s="6"/>
       <c r="CC134" s="6"/>
       <c r="CD134" s="6"/>
+      <c r="CE134" s="6"/>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="6"/>
@@ -21231,6 +21738,7 @@
       <c r="CB135" s="6"/>
       <c r="CC135" s="6"/>
       <c r="CD135" s="6"/>
+      <c r="CE135" s="6"/>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6"/>
@@ -21315,6 +21823,7 @@
       <c r="CB136" s="6"/>
       <c r="CC136" s="6"/>
       <c r="CD136" s="6"/>
+      <c r="CE136" s="6"/>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="6"/>
@@ -21399,6 +21908,7 @@
       <c r="CB137" s="6"/>
       <c r="CC137" s="6"/>
       <c r="CD137" s="6"/>
+      <c r="CE137" s="6"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6"/>
@@ -21483,6 +21993,7 @@
       <c r="CB138" s="6"/>
       <c r="CC138" s="6"/>
       <c r="CD138" s="6"/>
+      <c r="CE138" s="6"/>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="6"/>
@@ -21567,6 +22078,7 @@
       <c r="CB139" s="6"/>
       <c r="CC139" s="6"/>
       <c r="CD139" s="6"/>
+      <c r="CE139" s="6"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6"/>
@@ -21651,6 +22163,7 @@
       <c r="CB140" s="6"/>
       <c r="CC140" s="6"/>
       <c r="CD140" s="6"/>
+      <c r="CE140" s="6"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="6"/>
@@ -21735,6 +22248,7 @@
       <c r="CB141" s="6"/>
       <c r="CC141" s="6"/>
       <c r="CD141" s="6"/>
+      <c r="CE141" s="6"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6"/>
@@ -21819,6 +22333,7 @@
       <c r="CB142" s="6"/>
       <c r="CC142" s="6"/>
       <c r="CD142" s="6"/>
+      <c r="CE142" s="6"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="6"/>
@@ -21903,6 +22418,7 @@
       <c r="CB143" s="6"/>
       <c r="CC143" s="6"/>
       <c r="CD143" s="6"/>
+      <c r="CE143" s="6"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6"/>
@@ -21987,6 +22503,7 @@
       <c r="CB144" s="6"/>
       <c r="CC144" s="6"/>
       <c r="CD144" s="6"/>
+      <c r="CE144" s="6"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="6"/>
@@ -22071,6 +22588,7 @@
       <c r="CB145" s="6"/>
       <c r="CC145" s="6"/>
       <c r="CD145" s="6"/>
+      <c r="CE145" s="6"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6"/>
@@ -22155,6 +22673,7 @@
       <c r="CB146" s="6"/>
       <c r="CC146" s="6"/>
       <c r="CD146" s="6"/>
+      <c r="CE146" s="6"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="6"/>
@@ -22239,6 +22758,7 @@
       <c r="CB147" s="6"/>
       <c r="CC147" s="6"/>
       <c r="CD147" s="6"/>
+      <c r="CE147" s="6"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6"/>
@@ -22323,6 +22843,7 @@
       <c r="CB148" s="6"/>
       <c r="CC148" s="6"/>
       <c r="CD148" s="6"/>
+      <c r="CE148" s="6"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="6"/>
@@ -22407,6 +22928,7 @@
       <c r="CB149" s="6"/>
       <c r="CC149" s="6"/>
       <c r="CD149" s="6"/>
+      <c r="CE149" s="6"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6"/>
@@ -22491,6 +23013,7 @@
       <c r="CB150" s="6"/>
       <c r="CC150" s="6"/>
       <c r="CD150" s="6"/>
+      <c r="CE150" s="6"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="6"/>
@@ -22575,6 +23098,7 @@
       <c r="CB151" s="6"/>
       <c r="CC151" s="6"/>
       <c r="CD151" s="6"/>
+      <c r="CE151" s="6"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6"/>
@@ -22659,6 +23183,7 @@
       <c r="CB152" s="6"/>
       <c r="CC152" s="6"/>
       <c r="CD152" s="6"/>
+      <c r="CE152" s="6"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="6"/>
@@ -22743,6 +23268,7 @@
       <c r="CB153" s="6"/>
       <c r="CC153" s="6"/>
       <c r="CD153" s="6"/>
+      <c r="CE153" s="6"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6"/>
@@ -22827,6 +23353,7 @@
       <c r="CB154" s="6"/>
       <c r="CC154" s="6"/>
       <c r="CD154" s="6"/>
+      <c r="CE154" s="6"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="6"/>
@@ -22911,6 +23438,7 @@
       <c r="CB155" s="6"/>
       <c r="CC155" s="6"/>
       <c r="CD155" s="6"/>
+      <c r="CE155" s="6"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6"/>
@@ -22995,6 +23523,7 @@
       <c r="CB156" s="6"/>
       <c r="CC156" s="6"/>
       <c r="CD156" s="6"/>
+      <c r="CE156" s="6"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="6"/>
@@ -23079,6 +23608,7 @@
       <c r="CB157" s="6"/>
       <c r="CC157" s="6"/>
       <c r="CD157" s="6"/>
+      <c r="CE157" s="6"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6"/>
@@ -23163,6 +23693,7 @@
       <c r="CB158" s="6"/>
       <c r="CC158" s="6"/>
       <c r="CD158" s="6"/>
+      <c r="CE158" s="6"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="6"/>
@@ -23247,6 +23778,7 @@
       <c r="CB159" s="6"/>
       <c r="CC159" s="6"/>
       <c r="CD159" s="6"/>
+      <c r="CE159" s="6"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6"/>
@@ -23331,6 +23863,7 @@
       <c r="CB160" s="6"/>
       <c r="CC160" s="6"/>
       <c r="CD160" s="6"/>
+      <c r="CE160" s="6"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="6"/>
@@ -23415,6 +23948,7 @@
       <c r="CB161" s="6"/>
       <c r="CC161" s="6"/>
       <c r="CD161" s="6"/>
+      <c r="CE161" s="6"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6"/>
@@ -23499,6 +24033,7 @@
       <c r="CB162" s="6"/>
       <c r="CC162" s="6"/>
       <c r="CD162" s="6"/>
+      <c r="CE162" s="6"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="6"/>
@@ -23583,6 +24118,7 @@
       <c r="CB163" s="6"/>
       <c r="CC163" s="6"/>
       <c r="CD163" s="6"/>
+      <c r="CE163" s="6"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6"/>
@@ -23667,6 +24203,7 @@
       <c r="CB164" s="6"/>
       <c r="CC164" s="6"/>
       <c r="CD164" s="6"/>
+      <c r="CE164" s="6"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="6"/>
@@ -23751,6 +24288,7 @@
       <c r="CB165" s="6"/>
       <c r="CC165" s="6"/>
       <c r="CD165" s="6"/>
+      <c r="CE165" s="6"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6"/>
@@ -23835,6 +24373,7 @@
       <c r="CB166" s="6"/>
       <c r="CC166" s="6"/>
       <c r="CD166" s="6"/>
+      <c r="CE166" s="6"/>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="6"/>
@@ -23919,6 +24458,7 @@
       <c r="CB167" s="6"/>
       <c r="CC167" s="6"/>
       <c r="CD167" s="6"/>
+      <c r="CE167" s="6"/>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6"/>
@@ -24003,6 +24543,7 @@
       <c r="CB168" s="6"/>
       <c r="CC168" s="6"/>
       <c r="CD168" s="6"/>
+      <c r="CE168" s="6"/>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="6"/>
@@ -24087,6 +24628,7 @@
       <c r="CB169" s="6"/>
       <c r="CC169" s="6"/>
       <c r="CD169" s="6"/>
+      <c r="CE169" s="6"/>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6"/>
@@ -24171,6 +24713,7 @@
       <c r="CB170" s="6"/>
       <c r="CC170" s="6"/>
       <c r="CD170" s="6"/>
+      <c r="CE170" s="6"/>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="6"/>
@@ -24255,6 +24798,7 @@
       <c r="CB171" s="6"/>
       <c r="CC171" s="6"/>
       <c r="CD171" s="6"/>
+      <c r="CE171" s="6"/>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6"/>
@@ -24339,6 +24883,7 @@
       <c r="CB172" s="6"/>
       <c r="CC172" s="6"/>
       <c r="CD172" s="6"/>
+      <c r="CE172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="6"/>
@@ -24423,6 +24968,7 @@
       <c r="CB173" s="6"/>
       <c r="CC173" s="6"/>
       <c r="CD173" s="6"/>
+      <c r="CE173" s="6"/>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6"/>
@@ -24507,6 +25053,7 @@
       <c r="CB174" s="6"/>
       <c r="CC174" s="6"/>
       <c r="CD174" s="6"/>
+      <c r="CE174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="6"/>
@@ -24591,6 +25138,7 @@
       <c r="CB175" s="6"/>
       <c r="CC175" s="6"/>
       <c r="CD175" s="6"/>
+      <c r="CE175" s="6"/>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6"/>
@@ -24675,6 +25223,7 @@
       <c r="CB176" s="6"/>
       <c r="CC176" s="6"/>
       <c r="CD176" s="6"/>
+      <c r="CE176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="6"/>
@@ -24759,6 +25308,7 @@
       <c r="CB177" s="6"/>
       <c r="CC177" s="6"/>
       <c r="CD177" s="6"/>
+      <c r="CE177" s="6"/>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6"/>
@@ -24843,6 +25393,7 @@
       <c r="CB178" s="6"/>
       <c r="CC178" s="6"/>
       <c r="CD178" s="6"/>
+      <c r="CE178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="6"/>
@@ -24927,6 +25478,7 @@
       <c r="CB179" s="6"/>
       <c r="CC179" s="6"/>
       <c r="CD179" s="6"/>
+      <c r="CE179" s="6"/>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6"/>
@@ -25011,6 +25563,7 @@
       <c r="CB180" s="6"/>
       <c r="CC180" s="6"/>
       <c r="CD180" s="6"/>
+      <c r="CE180" s="6"/>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="6"/>
@@ -25095,6 +25648,7 @@
       <c r="CB181" s="6"/>
       <c r="CC181" s="6"/>
       <c r="CD181" s="6"/>
+      <c r="CE181" s="6"/>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6"/>
@@ -25179,6 +25733,7 @@
       <c r="CB182" s="6"/>
       <c r="CC182" s="6"/>
       <c r="CD182" s="6"/>
+      <c r="CE182" s="6"/>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="6"/>
@@ -25263,6 +25818,7 @@
       <c r="CB183" s="6"/>
       <c r="CC183" s="6"/>
       <c r="CD183" s="6"/>
+      <c r="CE183" s="6"/>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6"/>
@@ -25347,6 +25903,7 @@
       <c r="CB184" s="6"/>
       <c r="CC184" s="6"/>
       <c r="CD184" s="6"/>
+      <c r="CE184" s="6"/>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="6"/>
@@ -25431,6 +25988,7 @@
       <c r="CB185" s="6"/>
       <c r="CC185" s="6"/>
       <c r="CD185" s="6"/>
+      <c r="CE185" s="6"/>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6"/>
@@ -25515,6 +26073,7 @@
       <c r="CB186" s="6"/>
       <c r="CC186" s="6"/>
       <c r="CD186" s="6"/>
+      <c r="CE186" s="6"/>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="6"/>
@@ -25599,6 +26158,7 @@
       <c r="CB187" s="6"/>
       <c r="CC187" s="6"/>
       <c r="CD187" s="6"/>
+      <c r="CE187" s="6"/>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6"/>
@@ -25683,6 +26243,7 @@
       <c r="CB188" s="6"/>
       <c r="CC188" s="6"/>
       <c r="CD188" s="6"/>
+      <c r="CE188" s="6"/>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="6"/>
@@ -25767,6 +26328,7 @@
       <c r="CB189" s="6"/>
       <c r="CC189" s="6"/>
       <c r="CD189" s="6"/>
+      <c r="CE189" s="6"/>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6"/>
@@ -25851,6 +26413,7 @@
       <c r="CB190" s="6"/>
       <c r="CC190" s="6"/>
       <c r="CD190" s="6"/>
+      <c r="CE190" s="6"/>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="6"/>
@@ -25935,6 +26498,7 @@
       <c r="CB191" s="6"/>
       <c r="CC191" s="6"/>
       <c r="CD191" s="6"/>
+      <c r="CE191" s="6"/>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6"/>
@@ -26019,6 +26583,7 @@
       <c r="CB192" s="6"/>
       <c r="CC192" s="6"/>
       <c r="CD192" s="6"/>
+      <c r="CE192" s="6"/>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="6"/>
@@ -26103,6 +26668,7 @@
       <c r="CB193" s="6"/>
       <c r="CC193" s="6"/>
       <c r="CD193" s="6"/>
+      <c r="CE193" s="6"/>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6"/>
@@ -26187,6 +26753,7 @@
       <c r="CB194" s="6"/>
       <c r="CC194" s="6"/>
       <c r="CD194" s="6"/>
+      <c r="CE194" s="6"/>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="6"/>
@@ -26271,6 +26838,7 @@
       <c r="CB195" s="6"/>
       <c r="CC195" s="6"/>
       <c r="CD195" s="6"/>
+      <c r="CE195" s="6"/>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="6"/>
@@ -26355,6 +26923,7 @@
       <c r="CB196" s="6"/>
       <c r="CC196" s="6"/>
       <c r="CD196" s="6"/>
+      <c r="CE196" s="6"/>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="6"/>
@@ -26439,6 +27008,7 @@
       <c r="CB197" s="6"/>
       <c r="CC197" s="6"/>
       <c r="CD197" s="6"/>
+      <c r="CE197" s="6"/>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="6"/>
@@ -26523,6 +27093,7 @@
       <c r="CB198" s="6"/>
       <c r="CC198" s="6"/>
       <c r="CD198" s="6"/>
+      <c r="CE198" s="6"/>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="6"/>
@@ -26607,6 +27178,7 @@
       <c r="CB199" s="6"/>
       <c r="CC199" s="6"/>
       <c r="CD199" s="6"/>
+      <c r="CE199" s="6"/>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="6"/>
@@ -26691,6 +27263,7 @@
       <c r="CB200" s="6"/>
       <c r="CC200" s="6"/>
       <c r="CD200" s="6"/>
+      <c r="CE200" s="6"/>
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="6"/>
@@ -26775,6 +27348,7 @@
       <c r="CB201" s="6"/>
       <c r="CC201" s="6"/>
       <c r="CD201" s="6"/>
+      <c r="CE201" s="6"/>
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="6"/>
@@ -26859,6 +27433,7 @@
       <c r="CB202" s="6"/>
       <c r="CC202" s="6"/>
       <c r="CD202" s="6"/>
+      <c r="CE202" s="6"/>
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="6"/>
@@ -26943,6 +27518,7 @@
       <c r="CB203" s="6"/>
       <c r="CC203" s="6"/>
       <c r="CD203" s="6"/>
+      <c r="CE203" s="6"/>
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="6"/>
@@ -27027,6 +27603,7 @@
       <c r="CB204" s="6"/>
       <c r="CC204" s="6"/>
       <c r="CD204" s="6"/>
+      <c r="CE204" s="6"/>
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="6"/>
@@ -27111,6 +27688,7 @@
       <c r="CB205" s="6"/>
       <c r="CC205" s="6"/>
       <c r="CD205" s="6"/>
+      <c r="CE205" s="6"/>
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="6"/>
@@ -27195,6 +27773,7 @@
       <c r="CB206" s="6"/>
       <c r="CC206" s="6"/>
       <c r="CD206" s="6"/>
+      <c r="CE206" s="6"/>
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="6"/>
@@ -27279,6 +27858,7 @@
       <c r="CB207" s="6"/>
       <c r="CC207" s="6"/>
       <c r="CD207" s="6"/>
+      <c r="CE207" s="6"/>
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="6"/>
@@ -27363,6 +27943,7 @@
       <c r="CB208" s="6"/>
       <c r="CC208" s="6"/>
       <c r="CD208" s="6"/>
+      <c r="CE208" s="6"/>
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="6"/>
@@ -27447,6 +28028,7 @@
       <c r="CB209" s="6"/>
       <c r="CC209" s="6"/>
       <c r="CD209" s="6"/>
+      <c r="CE209" s="6"/>
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="6"/>
@@ -27531,6 +28113,7 @@
       <c r="CB210" s="6"/>
       <c r="CC210" s="6"/>
       <c r="CD210" s="6"/>
+      <c r="CE210" s="6"/>
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="6"/>
@@ -27615,6 +28198,7 @@
       <c r="CB211" s="6"/>
       <c r="CC211" s="6"/>
       <c r="CD211" s="6"/>
+      <c r="CE211" s="6"/>
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6"/>
@@ -27699,6 +28283,7 @@
       <c r="CB212" s="6"/>
       <c r="CC212" s="6"/>
       <c r="CD212" s="6"/>
+      <c r="CE212" s="6"/>
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="6"/>
@@ -27783,6 +28368,7 @@
       <c r="CB213" s="6"/>
       <c r="CC213" s="6"/>
       <c r="CD213" s="6"/>
+      <c r="CE213" s="6"/>
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6"/>
@@ -27867,6 +28453,7 @@
       <c r="CB214" s="6"/>
       <c r="CC214" s="6"/>
       <c r="CD214" s="6"/>
+      <c r="CE214" s="6"/>
     </row>
     <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="6"/>
@@ -27951,6 +28538,7 @@
       <c r="CB215" s="6"/>
       <c r="CC215" s="6"/>
       <c r="CD215" s="6"/>
+      <c r="CE215" s="6"/>
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="6"/>
@@ -28035,6 +28623,7 @@
       <c r="CB216" s="6"/>
       <c r="CC216" s="6"/>
       <c r="CD216" s="6"/>
+      <c r="CE216" s="6"/>
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="6"/>
@@ -28119,6 +28708,7 @@
       <c r="CB217" s="6"/>
       <c r="CC217" s="6"/>
       <c r="CD217" s="6"/>
+      <c r="CE217" s="6"/>
     </row>
     <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="6"/>
@@ -28203,6 +28793,7 @@
       <c r="CB218" s="6"/>
       <c r="CC218" s="6"/>
       <c r="CD218" s="6"/>
+      <c r="CE218" s="6"/>
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="6"/>
@@ -28287,6 +28878,7 @@
       <c r="CB219" s="6"/>
       <c r="CC219" s="6"/>
       <c r="CD219" s="6"/>
+      <c r="CE219" s="6"/>
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="6"/>
@@ -28371,6 +28963,7 @@
       <c r="CB220" s="6"/>
       <c r="CC220" s="6"/>
       <c r="CD220" s="6"/>
+      <c r="CE220" s="6"/>
     </row>
     <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
